--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6625A5E9-AEB0-4E12-B51B-78F3669ADF23}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0051DF64-2F4A-42AA-8AAF-D06272DD0553}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="622">
   <si>
     <t>No.</t>
   </si>
@@ -1894,9 +1894,6 @@
   </si>
   <si>
     <t>2020/E/115</t>
-  </si>
-  <si>
-    <t>Jayakodi J.A.N.P.</t>
   </si>
   <si>
     <t>Wijayawardhane W.A.T.S.</t>
@@ -2594,6 +2591,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -20188,12 +20189,12 @@
       </c>
       <c r="I168" s="83"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="69">
         <v>168</v>
       </c>
-      <c r="B169" s="16" t="s">
-        <v>619</v>
+      <c r="B169" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="C169" s="20" t="s">
         <v>167</v>
@@ -20247,7 +20248,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C171" s="20" t="s">
         <v>173</v>
@@ -20274,7 +20275,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="16" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C172" s="20" t="s">
         <v>174</v>
@@ -20301,7 +20302,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C173" s="20" t="s">
         <v>176</v>
@@ -20586,15 +20587,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
@@ -20603,6 +20595,15 @@
     <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20625,14 +20626,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -20647,4 +20640,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0051DF64-2F4A-42AA-8AAF-D06272DD0553}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{132177E6-1EE6-4006-AA2F-88DF4B138208}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2334,7 +2334,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2570,6 +2570,10 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2589,10 +2593,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15699,10 +15699,10 @@
       <c r="F2" s="18">
         <v>80</v>
       </c>
-      <c r="G2" s="83">
+      <c r="G2" s="85">
         <v>91</v>
       </c>
-      <c r="H2" s="83">
+      <c r="H2" s="85">
         <v>88</v>
       </c>
       <c r="I2" s="83"/>
@@ -15726,10 +15726,10 @@
       <c r="F3" s="18">
         <v>65</v>
       </c>
-      <c r="G3" s="83">
+      <c r="G3" s="85">
         <v>89</v>
       </c>
-      <c r="H3" s="83">
+      <c r="H3" s="85">
         <v>71</v>
       </c>
       <c r="I3" s="83"/>
@@ -15753,10 +15753,10 @@
       <c r="F4" s="18">
         <v>75</v>
       </c>
-      <c r="G4" s="83">
+      <c r="G4" s="85">
         <v>88</v>
       </c>
-      <c r="H4" s="83">
+      <c r="H4" s="85">
         <v>83</v>
       </c>
       <c r="I4" s="83"/>
@@ -15780,10 +15780,10 @@
       <c r="F5" s="18">
         <v>85</v>
       </c>
-      <c r="G5" s="83">
+      <c r="G5" s="85">
         <v>86</v>
       </c>
-      <c r="H5" s="83">
+      <c r="H5" s="85">
         <v>81</v>
       </c>
       <c r="I5" s="83"/>
@@ -15807,10 +15807,10 @@
       <c r="F6" s="18">
         <v>80</v>
       </c>
-      <c r="G6" s="83">
+      <c r="G6" s="85">
         <v>88</v>
       </c>
-      <c r="H6" s="83">
+      <c r="H6" s="85">
         <v>89</v>
       </c>
       <c r="I6" s="83"/>
@@ -15834,10 +15834,10 @@
       <c r="F7" s="18">
         <v>75</v>
       </c>
-      <c r="G7" s="83">
+      <c r="G7" s="85">
         <v>88</v>
       </c>
-      <c r="H7" s="83">
+      <c r="H7" s="85">
         <v>89</v>
       </c>
       <c r="I7" s="83"/>
@@ -15861,10 +15861,10 @@
       <c r="F8" s="18">
         <v>85</v>
       </c>
-      <c r="G8" s="83">
+      <c r="G8" s="85">
         <v>84</v>
       </c>
-      <c r="H8" s="83">
+      <c r="H8" s="85">
         <v>70</v>
       </c>
       <c r="I8" s="83"/>
@@ -15888,10 +15888,10 @@
       <c r="F9" s="18">
         <v>80</v>
       </c>
-      <c r="G9" s="83">
+      <c r="G9" s="85">
         <v>88</v>
       </c>
-      <c r="H9" s="83">
+      <c r="H9" s="85">
         <v>83</v>
       </c>
       <c r="I9" s="83"/>
@@ -15915,10 +15915,10 @@
       <c r="F10" s="18">
         <v>70</v>
       </c>
-      <c r="G10" s="83">
+      <c r="G10" s="85">
         <v>89</v>
       </c>
-      <c r="H10" s="83">
+      <c r="H10" s="85">
         <v>71</v>
       </c>
       <c r="I10" s="83"/>
@@ -15942,10 +15942,10 @@
       <c r="F11" s="18">
         <v>80</v>
       </c>
-      <c r="G11" s="83">
+      <c r="G11" s="85">
         <v>84</v>
       </c>
-      <c r="H11" s="83">
+      <c r="H11" s="85">
         <v>70</v>
       </c>
       <c r="I11" s="83"/>
@@ -15969,10 +15969,10 @@
       <c r="F12" s="18">
         <v>75</v>
       </c>
-      <c r="G12" s="83">
+      <c r="G12" s="85">
         <v>86</v>
       </c>
-      <c r="H12" s="83">
+      <c r="H12" s="85">
         <v>70</v>
       </c>
       <c r="I12" s="83"/>
@@ -15996,10 +15996,10 @@
       <c r="F13" s="18">
         <v>80</v>
       </c>
-      <c r="G13" s="83">
+      <c r="G13" s="85">
         <v>84</v>
       </c>
-      <c r="H13" s="83">
+      <c r="H13" s="85">
         <v>70</v>
       </c>
       <c r="I13" s="83"/>
@@ -16023,10 +16023,10 @@
       <c r="F14" s="18">
         <v>75</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="85">
         <v>90</v>
       </c>
-      <c r="H14" s="83">
+      <c r="H14" s="85">
         <v>85</v>
       </c>
       <c r="I14" s="83"/>
@@ -16050,10 +16050,10 @@
       <c r="F15" s="18">
         <v>75</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="85">
         <v>83</v>
       </c>
-      <c r="H15" s="83">
+      <c r="H15" s="85">
         <v>82</v>
       </c>
       <c r="I15" s="83"/>
@@ -16077,10 +16077,10 @@
       <c r="F16" s="18">
         <v>80</v>
       </c>
-      <c r="G16" s="83">
+      <c r="G16" s="85">
         <v>86</v>
       </c>
-      <c r="H16" s="83">
+      <c r="H16" s="85">
         <v>84</v>
       </c>
       <c r="I16" s="83"/>
@@ -16104,10 +16104,10 @@
       <c r="F17" s="18">
         <v>75</v>
       </c>
-      <c r="G17" s="83">
+      <c r="G17" s="85">
         <v>89</v>
       </c>
-      <c r="H17" s="83">
+      <c r="H17" s="85">
         <v>71</v>
       </c>
       <c r="I17" s="83"/>
@@ -16131,10 +16131,10 @@
       <c r="F18" s="18">
         <v>80</v>
       </c>
-      <c r="G18" s="83">
+      <c r="G18" s="85">
         <v>91</v>
       </c>
-      <c r="H18" s="83">
+      <c r="H18" s="85">
         <v>88</v>
       </c>
       <c r="I18" s="83"/>
@@ -16158,10 +16158,10 @@
       <c r="F19" s="18">
         <v>65</v>
       </c>
-      <c r="G19" s="83">
+      <c r="G19" s="85">
         <v>89</v>
       </c>
-      <c r="H19" s="83">
+      <c r="H19" s="85">
         <v>71</v>
       </c>
       <c r="I19" s="83"/>
@@ -16185,10 +16185,10 @@
       <c r="F20" s="18">
         <v>70</v>
       </c>
-      <c r="G20" s="83">
+      <c r="G20" s="85">
         <v>89</v>
       </c>
-      <c r="H20" s="83">
+      <c r="H20" s="85">
         <v>71</v>
       </c>
       <c r="I20" s="83"/>
@@ -16212,10 +16212,10 @@
       <c r="F21" s="18">
         <v>80</v>
       </c>
-      <c r="G21" s="83">
+      <c r="G21" s="85">
         <v>84</v>
       </c>
-      <c r="H21" s="83">
+      <c r="H21" s="85">
         <v>70</v>
       </c>
       <c r="I21" s="83"/>
@@ -16239,10 +16239,10 @@
       <c r="F22" s="18">
         <v>75</v>
       </c>
-      <c r="G22" s="83">
+      <c r="G22" s="85">
         <v>86</v>
       </c>
-      <c r="H22" s="83">
+      <c r="H22" s="85">
         <v>81</v>
       </c>
       <c r="I22" s="83"/>
@@ -16266,10 +16266,10 @@
       <c r="F23" s="18">
         <v>80</v>
       </c>
-      <c r="G23" s="83">
+      <c r="G23" s="85">
         <v>86</v>
       </c>
-      <c r="H23" s="83">
+      <c r="H23" s="85">
         <v>84</v>
       </c>
       <c r="I23" s="83"/>
@@ -16293,10 +16293,10 @@
       <c r="F24" s="18">
         <v>80</v>
       </c>
-      <c r="G24" s="83">
+      <c r="G24" s="85">
         <v>86</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="85">
         <v>81</v>
       </c>
       <c r="I24" s="83"/>
@@ -16320,10 +16320,10 @@
       <c r="F25" s="18">
         <v>75</v>
       </c>
-      <c r="G25" s="83">
+      <c r="G25" s="85">
         <v>83</v>
       </c>
-      <c r="H25" s="83">
+      <c r="H25" s="85">
         <v>82</v>
       </c>
       <c r="I25" s="83"/>
@@ -16347,10 +16347,10 @@
       <c r="F26" s="18">
         <v>80</v>
       </c>
-      <c r="G26" s="83">
+      <c r="G26" s="85">
         <v>83</v>
       </c>
-      <c r="H26" s="83">
+      <c r="H26" s="85">
         <v>82</v>
       </c>
       <c r="I26" s="83"/>
@@ -16374,10 +16374,10 @@
       <c r="F27" s="18">
         <v>80</v>
       </c>
-      <c r="G27" s="83">
+      <c r="G27" s="85">
         <v>86</v>
       </c>
-      <c r="H27" s="83">
+      <c r="H27" s="85">
         <v>84</v>
       </c>
       <c r="I27" s="83"/>
@@ -16401,10 +16401,10 @@
       <c r="F28" s="18">
         <v>70</v>
       </c>
-      <c r="G28" s="83">
+      <c r="G28" s="85">
         <v>86</v>
       </c>
-      <c r="H28" s="83">
+      <c r="H28" s="85">
         <v>81</v>
       </c>
       <c r="I28" s="83"/>
@@ -16428,10 +16428,10 @@
       <c r="F29" s="18">
         <v>85</v>
       </c>
-      <c r="G29" s="83">
+      <c r="G29" s="85">
         <v>83</v>
       </c>
-      <c r="H29" s="83">
+      <c r="H29" s="85">
         <v>82</v>
       </c>
       <c r="I29" s="83"/>
@@ -16455,10 +16455,10 @@
       <c r="F30" s="18">
         <v>75</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="85">
         <v>88</v>
       </c>
-      <c r="H30" s="83">
+      <c r="H30" s="85">
         <v>89</v>
       </c>
       <c r="I30" s="83"/>
@@ -16482,10 +16482,10 @@
       <c r="F31" s="18">
         <v>85</v>
       </c>
-      <c r="G31" s="83">
+      <c r="G31" s="85">
         <v>88</v>
       </c>
-      <c r="H31" s="83">
+      <c r="H31" s="85">
         <v>89</v>
       </c>
       <c r="I31" s="83"/>
@@ -16509,10 +16509,10 @@
       <c r="F32" s="18">
         <v>70</v>
       </c>
-      <c r="G32" s="83">
+      <c r="G32" s="85">
         <v>83</v>
       </c>
-      <c r="H32" s="83">
+      <c r="H32" s="85">
         <v>82</v>
       </c>
       <c r="I32" s="83"/>
@@ -16536,10 +16536,10 @@
       <c r="F33" s="18">
         <v>75</v>
       </c>
-      <c r="G33" s="83">
+      <c r="G33" s="85">
         <v>84</v>
       </c>
-      <c r="H33" s="83">
+      <c r="H33" s="85">
         <v>70</v>
       </c>
       <c r="I33" s="83"/>
@@ -16563,10 +16563,10 @@
       <c r="F34" s="18">
         <v>70</v>
       </c>
-      <c r="G34" s="83">
+      <c r="G34" s="85">
         <v>84</v>
       </c>
-      <c r="H34" s="83">
+      <c r="H34" s="85">
         <v>70</v>
       </c>
       <c r="I34" s="83"/>
@@ -16590,10 +16590,10 @@
       <c r="F35" s="18">
         <v>80</v>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="85">
         <v>83</v>
       </c>
-      <c r="H35" s="83">
+      <c r="H35" s="85">
         <v>82</v>
       </c>
       <c r="I35" s="83"/>
@@ -16617,10 +16617,10 @@
       <c r="F36" s="18">
         <v>80</v>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="85">
         <v>91</v>
       </c>
-      <c r="H36" s="83">
+      <c r="H36" s="85">
         <v>88</v>
       </c>
       <c r="I36" s="83"/>
@@ -16644,10 +16644,10 @@
       <c r="F37" s="18">
         <v>85</v>
       </c>
-      <c r="G37" s="83">
+      <c r="G37" s="85">
         <v>91</v>
       </c>
-      <c r="H37" s="83">
+      <c r="H37" s="85">
         <v>88</v>
       </c>
       <c r="I37" s="83"/>
@@ -16671,10 +16671,10 @@
       <c r="F38" s="18">
         <v>70</v>
       </c>
-      <c r="G38" s="83">
+      <c r="G38" s="85">
         <v>88</v>
       </c>
-      <c r="H38" s="83">
+      <c r="H38" s="85">
         <v>83</v>
       </c>
       <c r="I38" s="83"/>
@@ -16698,10 +16698,10 @@
       <c r="F39" s="18">
         <v>75</v>
       </c>
-      <c r="G39" s="83">
+      <c r="G39" s="85">
         <v>86</v>
       </c>
-      <c r="H39" s="83">
+      <c r="H39" s="85">
         <v>84</v>
       </c>
       <c r="I39" s="83"/>
@@ -16725,10 +16725,10 @@
       <c r="F40" s="18">
         <v>75</v>
       </c>
-      <c r="G40" s="83">
+      <c r="G40" s="85">
         <v>91</v>
       </c>
-      <c r="H40" s="83">
+      <c r="H40" s="85">
         <v>88</v>
       </c>
       <c r="I40" s="83"/>
@@ -16752,10 +16752,10 @@
       <c r="F41" s="18">
         <v>85</v>
       </c>
-      <c r="G41" s="83">
+      <c r="G41" s="85">
         <v>83</v>
       </c>
-      <c r="H41" s="83">
+      <c r="H41" s="85">
         <v>82</v>
       </c>
       <c r="I41" s="83"/>
@@ -16779,10 +16779,10 @@
       <c r="F42" s="18">
         <v>65</v>
       </c>
-      <c r="G42" s="83">
+      <c r="G42" s="85">
         <v>88</v>
       </c>
-      <c r="H42" s="83">
+      <c r="H42" s="85">
         <v>89</v>
       </c>
       <c r="I42" s="83"/>
@@ -16806,10 +16806,10 @@
       <c r="F43" s="18">
         <v>70</v>
       </c>
-      <c r="G43" s="83">
+      <c r="G43" s="85">
         <v>88</v>
       </c>
-      <c r="H43" s="83">
+      <c r="H43" s="85">
         <v>89</v>
       </c>
       <c r="I43" s="83"/>
@@ -16833,10 +16833,10 @@
       <c r="F44" s="18">
         <v>85</v>
       </c>
-      <c r="G44" s="83">
+      <c r="G44" s="85">
         <v>88</v>
       </c>
-      <c r="H44" s="83">
+      <c r="H44" s="85">
         <v>83</v>
       </c>
       <c r="I44" s="83"/>
@@ -16860,10 +16860,10 @@
       <c r="F45" s="18">
         <v>85</v>
       </c>
-      <c r="G45" s="83">
+      <c r="G45" s="85">
         <v>90</v>
       </c>
-      <c r="H45" s="83">
+      <c r="H45" s="85">
         <v>85</v>
       </c>
       <c r="I45" s="83"/>
@@ -16887,10 +16887,10 @@
       <c r="F46" s="18">
         <v>80</v>
       </c>
-      <c r="G46" s="83">
+      <c r="G46" s="85">
         <v>88</v>
       </c>
-      <c r="H46" s="83">
+      <c r="H46" s="85">
         <v>83</v>
       </c>
       <c r="I46" s="83"/>
@@ -16914,10 +16914,10 @@
       <c r="F47" s="18">
         <v>75</v>
       </c>
-      <c r="G47" s="83">
+      <c r="G47" s="85">
         <v>88</v>
       </c>
-      <c r="H47" s="83">
+      <c r="H47" s="85">
         <v>89</v>
       </c>
       <c r="I47" s="83"/>
@@ -16941,10 +16941,10 @@
       <c r="F48" s="18">
         <v>80</v>
       </c>
-      <c r="G48" s="83">
+      <c r="G48" s="85">
         <v>88</v>
       </c>
-      <c r="H48" s="83">
+      <c r="H48" s="85">
         <v>89</v>
       </c>
       <c r="I48" s="83"/>
@@ -16968,10 +16968,10 @@
       <c r="F49" s="18">
         <v>80</v>
       </c>
-      <c r="G49" s="83">
+      <c r="G49" s="85">
         <v>84</v>
       </c>
-      <c r="H49" s="83">
+      <c r="H49" s="85">
         <v>70</v>
       </c>
       <c r="I49" s="83"/>
@@ -16995,10 +16995,10 @@
       <c r="F50" s="18">
         <v>70</v>
       </c>
-      <c r="G50" s="83">
+      <c r="G50" s="85">
         <v>89</v>
       </c>
-      <c r="H50" s="83">
+      <c r="H50" s="85">
         <v>71</v>
       </c>
       <c r="I50" s="83"/>
@@ -17022,10 +17022,10 @@
       <c r="F51" s="18">
         <v>65</v>
       </c>
-      <c r="G51" s="83">
+      <c r="G51" s="85">
         <v>90</v>
       </c>
-      <c r="H51" s="83">
+      <c r="H51" s="85">
         <v>85</v>
       </c>
       <c r="I51" s="83"/>
@@ -17049,10 +17049,10 @@
       <c r="F52" s="18">
         <v>70</v>
       </c>
-      <c r="G52" s="83">
+      <c r="G52" s="85">
         <v>86</v>
       </c>
-      <c r="H52" s="83">
+      <c r="H52" s="85">
         <v>81</v>
       </c>
       <c r="I52" s="83"/>
@@ -17076,10 +17076,10 @@
       <c r="F53" s="18">
         <v>75</v>
       </c>
-      <c r="G53" s="83">
+      <c r="G53" s="85">
         <v>88</v>
       </c>
-      <c r="H53" s="83">
+      <c r="H53" s="85">
         <v>83</v>
       </c>
       <c r="I53" s="83"/>
@@ -17103,10 +17103,10 @@
       <c r="F54" s="18">
         <v>80</v>
       </c>
-      <c r="G54" s="83">
+      <c r="G54" s="85">
         <v>89</v>
       </c>
-      <c r="H54" s="83">
+      <c r="H54" s="85">
         <v>71</v>
       </c>
       <c r="I54" s="83"/>
@@ -17130,10 +17130,10 @@
       <c r="F55" s="18">
         <v>80</v>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="85">
         <v>89</v>
       </c>
-      <c r="H55" s="83">
+      <c r="H55" s="85">
         <v>71</v>
       </c>
       <c r="I55" s="83"/>
@@ -17157,10 +17157,10 @@
       <c r="F56" s="18">
         <v>85</v>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="85">
         <v>89</v>
       </c>
-      <c r="H56" s="83">
+      <c r="H56" s="85">
         <v>71</v>
       </c>
       <c r="I56" s="83"/>
@@ -17184,10 +17184,10 @@
       <c r="F57" s="18">
         <v>80</v>
       </c>
-      <c r="G57" s="83">
+      <c r="G57" s="85">
         <v>90</v>
       </c>
-      <c r="H57" s="83">
+      <c r="H57" s="85">
         <v>85</v>
       </c>
       <c r="I57" s="83"/>
@@ -17211,10 +17211,10 @@
       <c r="F58" s="18">
         <v>75</v>
       </c>
-      <c r="G58" s="83">
+      <c r="G58" s="85">
         <v>91</v>
       </c>
-      <c r="H58" s="83">
+      <c r="H58" s="85">
         <v>88</v>
       </c>
       <c r="I58" s="83"/>
@@ -17238,10 +17238,10 @@
       <c r="F59" s="18">
         <v>80</v>
       </c>
-      <c r="G59" s="83">
+      <c r="G59" s="85">
         <v>90</v>
       </c>
-      <c r="H59" s="83">
+      <c r="H59" s="85">
         <v>85</v>
       </c>
       <c r="I59" s="83"/>
@@ -17265,10 +17265,10 @@
       <c r="F60" s="18">
         <v>85</v>
       </c>
-      <c r="G60" s="83">
+      <c r="G60" s="85">
         <v>83</v>
       </c>
-      <c r="H60" s="83">
+      <c r="H60" s="85">
         <v>82</v>
       </c>
       <c r="I60" s="83"/>
@@ -17292,10 +17292,10 @@
       <c r="F61" s="18">
         <v>80</v>
       </c>
-      <c r="G61" s="83">
+      <c r="G61" s="85">
         <v>89</v>
       </c>
-      <c r="H61" s="83">
+      <c r="H61" s="85">
         <v>71</v>
       </c>
       <c r="I61" s="83"/>
@@ -17319,10 +17319,10 @@
       <c r="F62" s="18">
         <v>80</v>
       </c>
-      <c r="G62" s="83">
+      <c r="G62" s="85">
         <v>86</v>
       </c>
-      <c r="H62" s="83">
+      <c r="H62" s="85">
         <v>70</v>
       </c>
       <c r="I62" s="83"/>
@@ -17346,10 +17346,10 @@
       <c r="F63" s="18">
         <v>75</v>
       </c>
-      <c r="G63" s="83">
+      <c r="G63" s="85">
         <v>83</v>
       </c>
-      <c r="H63" s="83">
+      <c r="H63" s="85">
         <v>82</v>
       </c>
       <c r="I63" s="83"/>
@@ -17373,10 +17373,10 @@
       <c r="F64" s="18">
         <v>85</v>
       </c>
-      <c r="G64" s="83">
+      <c r="G64" s="85">
         <v>89</v>
       </c>
-      <c r="H64" s="83">
+      <c r="H64" s="85">
         <v>71</v>
       </c>
       <c r="I64" s="83"/>
@@ -17400,10 +17400,10 @@
       <c r="F65" s="18">
         <v>75</v>
       </c>
-      <c r="G65" s="83">
+      <c r="G65" s="85">
         <v>86</v>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="85">
         <v>70</v>
       </c>
       <c r="I65" s="83"/>
@@ -17427,10 +17427,10 @@
       <c r="F66" s="18">
         <v>80</v>
       </c>
-      <c r="G66" s="83">
+      <c r="G66" s="85">
         <v>84</v>
       </c>
-      <c r="H66" s="83">
+      <c r="H66" s="85">
         <v>70</v>
       </c>
       <c r="I66" s="83"/>
@@ -17454,10 +17454,10 @@
       <c r="F67" s="18">
         <v>85</v>
       </c>
-      <c r="G67" s="83">
+      <c r="G67" s="85">
         <v>86</v>
       </c>
-      <c r="H67" s="83">
+      <c r="H67" s="85">
         <v>81</v>
       </c>
       <c r="I67" s="83"/>
@@ -17481,10 +17481,10 @@
       <c r="F68" s="18">
         <v>75</v>
       </c>
-      <c r="G68" s="83">
+      <c r="G68" s="85">
         <v>88</v>
       </c>
-      <c r="H68" s="83">
+      <c r="H68" s="85">
         <v>89</v>
       </c>
       <c r="I68" s="83"/>
@@ -17508,10 +17508,10 @@
       <c r="F69" s="18">
         <v>75</v>
       </c>
-      <c r="G69" s="83">
+      <c r="G69" s="85">
         <v>84</v>
       </c>
-      <c r="H69" s="83">
+      <c r="H69" s="85">
         <v>70</v>
       </c>
       <c r="I69" s="83"/>
@@ -17535,10 +17535,10 @@
       <c r="F70" s="18">
         <v>70</v>
       </c>
-      <c r="G70" s="83">
+      <c r="G70" s="85">
         <v>90</v>
       </c>
-      <c r="H70" s="83">
+      <c r="H70" s="85">
         <v>85</v>
       </c>
       <c r="I70" s="83"/>
@@ -17562,10 +17562,10 @@
       <c r="F71" s="18">
         <v>70</v>
       </c>
-      <c r="G71" s="83">
+      <c r="G71" s="85">
         <v>91</v>
       </c>
-      <c r="H71" s="83">
+      <c r="H71" s="85">
         <v>88</v>
       </c>
       <c r="I71" s="83"/>
@@ -17589,10 +17589,10 @@
       <c r="F72" s="18">
         <v>70</v>
       </c>
-      <c r="G72" s="83">
+      <c r="G72" s="85">
         <v>88</v>
       </c>
-      <c r="H72" s="83">
+      <c r="H72" s="85">
         <v>89</v>
       </c>
       <c r="I72" s="83"/>
@@ -17616,10 +17616,10 @@
       <c r="F73" s="18">
         <v>70</v>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="85">
         <v>0</v>
       </c>
-      <c r="H73" s="83">
+      <c r="H73" s="85">
         <v>0</v>
       </c>
       <c r="I73" s="83"/>
@@ -17643,10 +17643,10 @@
       <c r="F74" s="18">
         <v>80</v>
       </c>
-      <c r="G74" s="83">
+      <c r="G74" s="85">
         <v>84</v>
       </c>
-      <c r="H74" s="83">
+      <c r="H74" s="85">
         <v>70</v>
       </c>
       <c r="I74" s="83"/>
@@ -17670,10 +17670,10 @@
       <c r="F75" s="18">
         <v>70</v>
       </c>
-      <c r="G75" s="83">
+      <c r="G75" s="85">
         <v>91</v>
       </c>
-      <c r="H75" s="83">
+      <c r="H75" s="85">
         <v>88</v>
       </c>
       <c r="I75" s="83"/>
@@ -17697,10 +17697,10 @@
       <c r="F76" s="18">
         <v>75</v>
       </c>
-      <c r="G76" s="83">
+      <c r="G76" s="85">
         <v>86</v>
       </c>
-      <c r="H76" s="83">
+      <c r="H76" s="85">
         <v>81</v>
       </c>
       <c r="I76" s="83"/>
@@ -17724,10 +17724,10 @@
       <c r="F77" s="18">
         <v>65</v>
       </c>
-      <c r="G77" s="83">
+      <c r="G77" s="85">
         <v>88</v>
       </c>
-      <c r="H77" s="83">
+      <c r="H77" s="85">
         <v>89</v>
       </c>
       <c r="I77" s="83"/>
@@ -17751,10 +17751,10 @@
       <c r="F78" s="18">
         <v>75</v>
       </c>
-      <c r="G78" s="83">
+      <c r="G78" s="85">
         <v>86</v>
       </c>
-      <c r="H78" s="83">
+      <c r="H78" s="85">
         <v>81</v>
       </c>
       <c r="I78" s="83"/>
@@ -17778,10 +17778,10 @@
       <c r="F79" s="18">
         <v>75</v>
       </c>
-      <c r="G79" s="83">
+      <c r="G79" s="85">
         <v>83</v>
       </c>
-      <c r="H79" s="83">
+      <c r="H79" s="85">
         <v>82</v>
       </c>
       <c r="I79" s="83"/>
@@ -17805,10 +17805,10 @@
       <c r="F80" s="18">
         <v>80</v>
       </c>
-      <c r="G80" s="83">
+      <c r="G80" s="85">
         <v>84</v>
       </c>
-      <c r="H80" s="83">
+      <c r="H80" s="85">
         <v>70</v>
       </c>
       <c r="I80" s="83"/>
@@ -17832,10 +17832,10 @@
       <c r="F81" s="18">
         <v>80</v>
       </c>
-      <c r="G81" s="83">
+      <c r="G81" s="85">
         <v>86</v>
       </c>
-      <c r="H81" s="83">
+      <c r="H81" s="85">
         <v>70</v>
       </c>
       <c r="I81" s="83"/>
@@ -17859,10 +17859,10 @@
       <c r="F82" s="18">
         <v>85</v>
       </c>
-      <c r="G82" s="83">
+      <c r="G82" s="85">
         <v>88</v>
       </c>
-      <c r="H82" s="83">
+      <c r="H82" s="85">
         <v>89</v>
       </c>
       <c r="I82" s="83"/>
@@ -17886,10 +17886,10 @@
       <c r="F83" s="18">
         <v>85</v>
       </c>
-      <c r="G83" s="83">
+      <c r="G83" s="85">
         <v>88</v>
       </c>
-      <c r="H83" s="83">
+      <c r="H83" s="85">
         <v>83</v>
       </c>
       <c r="I83" s="83"/>
@@ -17913,10 +17913,10 @@
       <c r="F84" s="18">
         <v>75</v>
       </c>
-      <c r="G84" s="83">
+      <c r="G84" s="85">
         <v>91</v>
       </c>
-      <c r="H84" s="83">
+      <c r="H84" s="85">
         <v>88</v>
       </c>
       <c r="I84" s="83"/>
@@ -17940,10 +17940,10 @@
       <c r="F85" s="18">
         <v>70</v>
       </c>
-      <c r="G85" s="83">
+      <c r="G85" s="85">
         <v>90</v>
       </c>
-      <c r="H85" s="83">
+      <c r="H85" s="85">
         <v>85</v>
       </c>
       <c r="I85" s="83"/>
@@ -17967,10 +17967,10 @@
       <c r="F86" s="18">
         <v>65</v>
       </c>
-      <c r="G86" s="83">
+      <c r="G86" s="85">
         <v>0</v>
       </c>
-      <c r="H86" s="83">
+      <c r="H86" s="85">
         <v>0</v>
       </c>
       <c r="I86" s="83"/>
@@ -17994,10 +17994,10 @@
       <c r="F87" s="18">
         <v>75</v>
       </c>
-      <c r="G87" s="83">
+      <c r="G87" s="85">
         <v>86</v>
       </c>
-      <c r="H87" s="83">
+      <c r="H87" s="85">
         <v>70</v>
       </c>
       <c r="I87" s="83"/>
@@ -18021,10 +18021,10 @@
       <c r="F88" s="18">
         <v>70</v>
       </c>
-      <c r="G88" s="83">
+      <c r="G88" s="85">
         <v>86</v>
       </c>
-      <c r="H88" s="83">
+      <c r="H88" s="85">
         <v>84</v>
       </c>
       <c r="I88" s="83"/>
@@ -18048,10 +18048,10 @@
       <c r="F89" s="18">
         <v>80</v>
       </c>
-      <c r="G89" s="83">
+      <c r="G89" s="85">
         <v>86</v>
       </c>
-      <c r="H89" s="83">
+      <c r="H89" s="85">
         <v>84</v>
       </c>
       <c r="I89" s="83"/>
@@ -18075,10 +18075,10 @@
       <c r="F90" s="18">
         <v>75</v>
       </c>
-      <c r="G90" s="83">
+      <c r="G90" s="85">
         <v>84</v>
       </c>
-      <c r="H90" s="83">
+      <c r="H90" s="85">
         <v>70</v>
       </c>
       <c r="I90" s="83"/>
@@ -18102,10 +18102,10 @@
       <c r="F91" s="18">
         <v>70</v>
       </c>
-      <c r="G91" s="83">
+      <c r="G91" s="85">
         <v>86</v>
       </c>
-      <c r="H91" s="83">
+      <c r="H91" s="85">
         <v>81</v>
       </c>
       <c r="I91" s="83"/>
@@ -18129,10 +18129,10 @@
       <c r="F92" s="18">
         <v>70</v>
       </c>
-      <c r="G92" s="83">
+      <c r="G92" s="85">
         <v>89</v>
       </c>
-      <c r="H92" s="83">
+      <c r="H92" s="85">
         <v>71</v>
       </c>
       <c r="I92" s="83"/>
@@ -18156,10 +18156,10 @@
       <c r="F93" s="18">
         <v>65</v>
       </c>
-      <c r="G93" s="83">
+      <c r="G93" s="85">
         <v>88</v>
       </c>
-      <c r="H93" s="83">
+      <c r="H93" s="85">
         <v>89</v>
       </c>
       <c r="I93" s="83"/>
@@ -18183,10 +18183,10 @@
       <c r="F94" s="18">
         <v>75</v>
       </c>
-      <c r="G94" s="83">
+      <c r="G94" s="85">
         <v>84</v>
       </c>
-      <c r="H94" s="83">
+      <c r="H94" s="85">
         <v>70</v>
       </c>
       <c r="I94" s="83"/>
@@ -18210,10 +18210,10 @@
       <c r="F95" s="18">
         <v>75</v>
       </c>
-      <c r="G95" s="83">
+      <c r="G95" s="85">
         <v>89</v>
       </c>
-      <c r="H95" s="83">
+      <c r="H95" s="85">
         <v>71</v>
       </c>
       <c r="I95" s="83"/>
@@ -18237,10 +18237,10 @@
       <c r="F96" s="18">
         <v>75</v>
       </c>
-      <c r="G96" s="83">
+      <c r="G96" s="85">
         <v>86</v>
       </c>
-      <c r="H96" s="83">
+      <c r="H96" s="85">
         <v>81</v>
       </c>
       <c r="I96" s="83"/>
@@ -18264,10 +18264,10 @@
       <c r="F97" s="18">
         <v>75</v>
       </c>
-      <c r="G97" s="83">
+      <c r="G97" s="85">
         <v>86</v>
       </c>
-      <c r="H97" s="83">
+      <c r="H97" s="85">
         <v>70</v>
       </c>
       <c r="I97" s="83"/>
@@ -18291,10 +18291,10 @@
       <c r="F98" s="18">
         <v>75</v>
       </c>
-      <c r="G98" s="83">
+      <c r="G98" s="85">
         <v>86</v>
       </c>
-      <c r="H98" s="83">
+      <c r="H98" s="85">
         <v>70</v>
       </c>
       <c r="I98" s="83"/>
@@ -18318,10 +18318,10 @@
       <c r="F99" s="18">
         <v>75</v>
       </c>
-      <c r="G99" s="83">
+      <c r="G99" s="85">
         <v>86</v>
       </c>
-      <c r="H99" s="83">
+      <c r="H99" s="85">
         <v>70</v>
       </c>
       <c r="I99" s="83"/>
@@ -18345,10 +18345,10 @@
       <c r="F100" s="18">
         <v>70</v>
       </c>
-      <c r="G100" s="83">
+      <c r="G100" s="85">
         <v>86</v>
       </c>
-      <c r="H100" s="83">
+      <c r="H100" s="85">
         <v>84</v>
       </c>
       <c r="I100" s="83"/>
@@ -18372,10 +18372,10 @@
       <c r="F101" s="18">
         <v>75</v>
       </c>
-      <c r="G101" s="83">
+      <c r="G101" s="85">
         <v>88</v>
       </c>
-      <c r="H101" s="83">
+      <c r="H101" s="85">
         <v>89</v>
       </c>
       <c r="I101" s="83"/>
@@ -18399,10 +18399,10 @@
       <c r="F102" s="18">
         <v>75</v>
       </c>
-      <c r="G102" s="83">
+      <c r="G102" s="85">
         <v>90</v>
       </c>
-      <c r="H102" s="83">
+      <c r="H102" s="85">
         <v>85</v>
       </c>
       <c r="I102" s="83"/>
@@ -18426,10 +18426,10 @@
       <c r="F103" s="18">
         <v>80</v>
       </c>
-      <c r="G103" s="83">
+      <c r="G103" s="85">
         <v>88</v>
       </c>
-      <c r="H103" s="83">
+      <c r="H103" s="85">
         <v>83</v>
       </c>
       <c r="I103" s="83"/>
@@ -18453,10 +18453,10 @@
       <c r="F104" s="18">
         <v>65</v>
       </c>
-      <c r="G104" s="83">
+      <c r="G104" s="85">
         <v>90</v>
       </c>
-      <c r="H104" s="83">
+      <c r="H104" s="85">
         <v>85</v>
       </c>
       <c r="I104" s="83"/>
@@ -18480,10 +18480,10 @@
       <c r="F105" s="18">
         <v>85</v>
       </c>
-      <c r="G105" s="83">
+      <c r="G105" s="85">
         <v>88</v>
       </c>
-      <c r="H105" s="83">
+      <c r="H105" s="85">
         <v>83</v>
       </c>
       <c r="I105" s="83"/>
@@ -18507,10 +18507,10 @@
       <c r="F106" s="18">
         <v>75</v>
       </c>
-      <c r="G106" s="83">
+      <c r="G106" s="85">
         <v>90</v>
       </c>
-      <c r="H106" s="83">
+      <c r="H106" s="85">
         <v>85</v>
       </c>
       <c r="I106" s="83"/>
@@ -18534,10 +18534,10 @@
       <c r="F107" s="18">
         <v>70</v>
       </c>
-      <c r="G107" s="83">
+      <c r="G107" s="85">
         <v>90</v>
       </c>
-      <c r="H107" s="83">
+      <c r="H107" s="85">
         <v>85</v>
       </c>
       <c r="I107" s="83"/>
@@ -18561,10 +18561,10 @@
       <c r="F108" s="18">
         <v>70</v>
       </c>
-      <c r="G108" s="83">
+      <c r="G108" s="85">
         <v>90</v>
       </c>
-      <c r="H108" s="83">
+      <c r="H108" s="85">
         <v>85</v>
       </c>
       <c r="I108" s="83"/>
@@ -18588,10 +18588,10 @@
       <c r="F109" s="18">
         <v>80</v>
       </c>
-      <c r="G109" s="83">
+      <c r="G109" s="85">
         <v>90</v>
       </c>
-      <c r="H109" s="83">
+      <c r="H109" s="85">
         <v>85</v>
       </c>
       <c r="I109" s="83"/>
@@ -18615,10 +18615,10 @@
       <c r="F110" s="18">
         <v>75</v>
       </c>
-      <c r="G110" s="83">
+      <c r="G110" s="85">
         <v>84</v>
       </c>
-      <c r="H110" s="83">
+      <c r="H110" s="85">
         <v>70</v>
       </c>
       <c r="I110" s="83"/>
@@ -18642,10 +18642,10 @@
       <c r="F111" s="18">
         <v>70</v>
       </c>
-      <c r="G111" s="83">
+      <c r="G111" s="85">
         <v>90</v>
       </c>
-      <c r="H111" s="83">
+      <c r="H111" s="85">
         <v>85</v>
       </c>
       <c r="I111" s="83"/>
@@ -18669,10 +18669,10 @@
       <c r="F112" s="18">
         <v>65</v>
       </c>
-      <c r="G112" s="83">
+      <c r="G112" s="85">
         <v>83</v>
       </c>
-      <c r="H112" s="83">
+      <c r="H112" s="85">
         <v>82</v>
       </c>
       <c r="I112" s="83"/>
@@ -18696,10 +18696,10 @@
       <c r="F113" s="18">
         <v>65</v>
       </c>
-      <c r="G113" s="83">
+      <c r="G113" s="85">
         <v>91</v>
       </c>
-      <c r="H113" s="83">
+      <c r="H113" s="85">
         <v>88</v>
       </c>
       <c r="I113" s="83"/>
@@ -18723,10 +18723,10 @@
       <c r="F114" s="18">
         <v>65</v>
       </c>
-      <c r="G114" s="83">
+      <c r="G114" s="85">
         <v>88</v>
       </c>
-      <c r="H114" s="83">
+      <c r="H114" s="85">
         <v>83</v>
       </c>
       <c r="I114" s="83"/>
@@ -18750,10 +18750,10 @@
       <c r="F115" s="18">
         <v>80</v>
       </c>
-      <c r="G115" s="83">
+      <c r="G115" s="85">
         <v>88</v>
       </c>
-      <c r="H115" s="83">
+      <c r="H115" s="85">
         <v>83</v>
       </c>
       <c r="I115" s="83"/>
@@ -18777,10 +18777,10 @@
       <c r="F116" s="18">
         <v>75</v>
       </c>
-      <c r="G116" s="83">
+      <c r="G116" s="85">
         <v>84</v>
       </c>
-      <c r="H116" s="83">
+      <c r="H116" s="85">
         <v>70</v>
       </c>
       <c r="I116" s="83"/>
@@ -18804,10 +18804,10 @@
       <c r="F117" s="18">
         <v>65</v>
       </c>
-      <c r="G117" s="83">
+      <c r="G117" s="85">
         <v>88</v>
       </c>
-      <c r="H117" s="83">
+      <c r="H117" s="85">
         <v>89</v>
       </c>
       <c r="I117" s="83"/>
@@ -18831,10 +18831,10 @@
       <c r="F118" s="18">
         <v>75</v>
       </c>
-      <c r="G118" s="83">
+      <c r="G118" s="85">
         <v>0</v>
       </c>
-      <c r="H118" s="83">
+      <c r="H118" s="85">
         <v>0</v>
       </c>
       <c r="I118" s="83"/>
@@ -18858,10 +18858,10 @@
       <c r="F119" s="18">
         <v>75</v>
       </c>
-      <c r="G119" s="83">
+      <c r="G119" s="85">
         <v>86</v>
       </c>
-      <c r="H119" s="83">
+      <c r="H119" s="85">
         <v>81</v>
       </c>
       <c r="I119" s="83"/>
@@ -18885,10 +18885,10 @@
       <c r="F120" s="18">
         <v>80</v>
       </c>
-      <c r="G120" s="83">
+      <c r="G120" s="85">
         <v>86</v>
       </c>
-      <c r="H120" s="83">
+      <c r="H120" s="85">
         <v>81</v>
       </c>
       <c r="I120" s="83"/>
@@ -18912,10 +18912,10 @@
       <c r="F121" s="18">
         <v>80</v>
       </c>
-      <c r="G121" s="83">
+      <c r="G121" s="85">
         <v>86</v>
       </c>
-      <c r="H121" s="83">
+      <c r="H121" s="85">
         <v>84</v>
       </c>
       <c r="I121" s="83"/>
@@ -18939,10 +18939,10 @@
       <c r="F122" s="18">
         <v>65</v>
       </c>
-      <c r="G122" s="83">
+      <c r="G122" s="85">
         <v>84</v>
       </c>
-      <c r="H122" s="83">
+      <c r="H122" s="85">
         <v>70</v>
       </c>
       <c r="I122" s="83"/>
@@ -18966,10 +18966,10 @@
       <c r="F123" s="18">
         <v>80</v>
       </c>
-      <c r="G123" s="83">
+      <c r="G123" s="85">
         <v>88</v>
       </c>
-      <c r="H123" s="83">
+      <c r="H123" s="85">
         <v>89</v>
       </c>
       <c r="I123" s="83"/>
@@ -18993,10 +18993,10 @@
       <c r="F124" s="18">
         <v>80</v>
       </c>
-      <c r="G124" s="83">
+      <c r="G124" s="85">
         <v>91</v>
       </c>
-      <c r="H124" s="83">
+      <c r="H124" s="85">
         <v>88</v>
       </c>
       <c r="I124" s="83"/>
@@ -19020,10 +19020,10 @@
       <c r="F125" s="18">
         <v>80</v>
       </c>
-      <c r="G125" s="83">
+      <c r="G125" s="85">
         <v>86</v>
       </c>
-      <c r="H125" s="83">
+      <c r="H125" s="85">
         <v>84</v>
       </c>
       <c r="I125" s="83"/>
@@ -19047,10 +19047,10 @@
       <c r="F126" s="18">
         <v>75</v>
       </c>
-      <c r="G126" s="83">
+      <c r="G126" s="85">
         <v>86</v>
       </c>
-      <c r="H126" s="83">
+      <c r="H126" s="85">
         <v>84</v>
       </c>
       <c r="I126" s="83"/>
@@ -19074,10 +19074,10 @@
       <c r="F127" s="18">
         <v>85</v>
       </c>
-      <c r="G127" s="83">
+      <c r="G127" s="85">
         <v>86</v>
       </c>
-      <c r="H127" s="83">
+      <c r="H127" s="85">
         <v>84</v>
       </c>
       <c r="I127" s="83"/>
@@ -19101,10 +19101,10 @@
       <c r="F128" s="18">
         <v>80</v>
       </c>
-      <c r="G128" s="83">
+      <c r="G128" s="85">
         <v>91</v>
       </c>
-      <c r="H128" s="83">
+      <c r="H128" s="85">
         <v>88</v>
       </c>
       <c r="I128" s="83"/>
@@ -19128,10 +19128,10 @@
       <c r="F129" s="18">
         <v>70</v>
       </c>
-      <c r="G129" s="83">
+      <c r="G129" s="85">
         <v>86</v>
       </c>
-      <c r="H129" s="83">
+      <c r="H129" s="85">
         <v>81</v>
       </c>
       <c r="I129" s="83"/>
@@ -19155,10 +19155,10 @@
       <c r="F130" s="18">
         <v>75</v>
       </c>
-      <c r="G130" s="83">
+      <c r="G130" s="85">
         <v>86</v>
       </c>
-      <c r="H130" s="83">
+      <c r="H130" s="85">
         <v>70</v>
       </c>
       <c r="I130" s="83"/>
@@ -19182,10 +19182,10 @@
       <c r="F131" s="18">
         <v>80</v>
       </c>
-      <c r="G131" s="83">
+      <c r="G131" s="85">
         <v>91</v>
       </c>
-      <c r="H131" s="83">
+      <c r="H131" s="85">
         <v>88</v>
       </c>
       <c r="I131" s="83"/>
@@ -19209,10 +19209,10 @@
       <c r="F132" s="18">
         <v>70</v>
       </c>
-      <c r="G132" s="83">
+      <c r="G132" s="85">
         <v>89</v>
       </c>
-      <c r="H132" s="83">
+      <c r="H132" s="85">
         <v>71</v>
       </c>
       <c r="I132" s="83"/>
@@ -19236,10 +19236,10 @@
       <c r="F133" s="18">
         <v>80</v>
       </c>
-      <c r="G133" s="83">
+      <c r="G133" s="85">
         <v>84</v>
       </c>
-      <c r="H133" s="83">
+      <c r="H133" s="85">
         <v>70</v>
       </c>
       <c r="I133" s="83"/>
@@ -19263,10 +19263,10 @@
       <c r="F134" s="18">
         <v>70</v>
       </c>
-      <c r="G134" s="83">
+      <c r="G134" s="85">
         <v>84</v>
       </c>
-      <c r="H134" s="83">
+      <c r="H134" s="85">
         <v>70</v>
       </c>
       <c r="I134" s="83"/>
@@ -19290,10 +19290,10 @@
       <c r="F135" s="18">
         <v>80</v>
       </c>
-      <c r="G135" s="83">
+      <c r="G135" s="85">
         <v>89</v>
       </c>
-      <c r="H135" s="83">
+      <c r="H135" s="85">
         <v>71</v>
       </c>
       <c r="I135" s="83"/>
@@ -19317,10 +19317,10 @@
       <c r="F136" s="18">
         <v>75</v>
       </c>
-      <c r="G136" s="83">
+      <c r="G136" s="85">
         <v>84</v>
       </c>
-      <c r="H136" s="83">
+      <c r="H136" s="85">
         <v>70</v>
       </c>
       <c r="I136" s="83"/>
@@ -19344,10 +19344,10 @@
       <c r="F137" s="18">
         <v>80</v>
       </c>
-      <c r="G137" s="83">
+      <c r="G137" s="85">
         <v>83</v>
       </c>
-      <c r="H137" s="83">
+      <c r="H137" s="85">
         <v>82</v>
       </c>
       <c r="I137" s="83"/>
@@ -19371,10 +19371,10 @@
       <c r="F138" s="18">
         <v>70</v>
       </c>
-      <c r="G138" s="83">
+      <c r="G138" s="85">
         <v>89</v>
       </c>
-      <c r="H138" s="83">
+      <c r="H138" s="85">
         <v>71</v>
       </c>
       <c r="I138" s="83"/>
@@ -19398,10 +19398,10 @@
       <c r="F139" s="18">
         <v>80</v>
       </c>
-      <c r="G139" s="83">
+      <c r="G139" s="85">
         <v>84</v>
       </c>
-      <c r="H139" s="83">
+      <c r="H139" s="85">
         <v>70</v>
       </c>
       <c r="I139" s="83"/>
@@ -19425,10 +19425,10 @@
       <c r="F140" s="18">
         <v>85</v>
       </c>
-      <c r="G140" s="83">
+      <c r="G140" s="85">
         <v>88</v>
       </c>
-      <c r="H140" s="83">
+      <c r="H140" s="85">
         <v>83</v>
       </c>
       <c r="I140" s="83"/>
@@ -19452,10 +19452,10 @@
       <c r="F141" s="18">
         <v>75</v>
       </c>
-      <c r="G141" s="83">
+      <c r="G141" s="85">
         <v>86</v>
       </c>
-      <c r="H141" s="83">
+      <c r="H141" s="85">
         <v>81</v>
       </c>
       <c r="I141" s="83"/>
@@ -19479,10 +19479,10 @@
       <c r="F142" s="18">
         <v>75</v>
       </c>
-      <c r="G142" s="83">
+      <c r="G142" s="85">
         <v>88</v>
       </c>
-      <c r="H142" s="83">
+      <c r="H142" s="85">
         <v>83</v>
       </c>
       <c r="I142" s="83"/>
@@ -19506,10 +19506,10 @@
       <c r="F143" s="18">
         <v>80</v>
       </c>
-      <c r="G143" s="83">
+      <c r="G143" s="85">
         <v>86</v>
       </c>
-      <c r="H143" s="83">
+      <c r="H143" s="85">
         <v>84</v>
       </c>
       <c r="I143" s="83"/>
@@ -19533,10 +19533,10 @@
       <c r="F144" s="18">
         <v>75</v>
       </c>
-      <c r="G144" s="83">
+      <c r="G144" s="85">
         <v>83</v>
       </c>
-      <c r="H144" s="83">
+      <c r="H144" s="85">
         <v>82</v>
       </c>
       <c r="I144" s="83"/>
@@ -19560,10 +19560,10 @@
       <c r="F145" s="18">
         <v>75</v>
       </c>
-      <c r="G145" s="83">
+      <c r="G145" s="85">
         <v>86</v>
       </c>
-      <c r="H145" s="83">
+      <c r="H145" s="85">
         <v>70</v>
       </c>
       <c r="I145" s="83"/>
@@ -19587,10 +19587,10 @@
       <c r="F146" s="18">
         <v>85</v>
       </c>
-      <c r="G146" s="83">
+      <c r="G146" s="85">
         <v>88</v>
       </c>
-      <c r="H146" s="83">
+      <c r="H146" s="85">
         <v>83</v>
       </c>
       <c r="I146" s="83"/>
@@ -19614,10 +19614,10 @@
       <c r="F147" s="18">
         <v>60</v>
       </c>
-      <c r="G147" s="83">
+      <c r="G147" s="85">
         <v>86</v>
       </c>
-      <c r="H147" s="83">
+      <c r="H147" s="85">
         <v>84</v>
       </c>
       <c r="I147" s="83"/>
@@ -19641,10 +19641,10 @@
       <c r="F148" s="18">
         <v>85</v>
       </c>
-      <c r="G148" s="83">
+      <c r="G148" s="85">
         <v>0</v>
       </c>
-      <c r="H148" s="83">
+      <c r="H148" s="85">
         <v>0</v>
       </c>
       <c r="I148" s="83"/>
@@ -19668,10 +19668,10 @@
       <c r="F149" s="18">
         <v>70</v>
       </c>
-      <c r="G149" s="83">
+      <c r="G149" s="85">
         <v>91</v>
       </c>
-      <c r="H149" s="83">
+      <c r="H149" s="85">
         <v>88</v>
       </c>
       <c r="I149" s="83"/>
@@ -19695,10 +19695,10 @@
       <c r="F150" s="18">
         <v>75</v>
       </c>
-      <c r="G150" s="83">
+      <c r="G150" s="85">
         <v>0</v>
       </c>
-      <c r="H150" s="83">
+      <c r="H150" s="85">
         <v>0</v>
       </c>
       <c r="I150" s="83"/>
@@ -19722,10 +19722,10 @@
       <c r="F151" s="18">
         <v>85</v>
       </c>
-      <c r="G151" s="83">
+      <c r="G151" s="85">
         <v>0</v>
       </c>
-      <c r="H151" s="83">
+      <c r="H151" s="85">
         <v>0</v>
       </c>
       <c r="I151" s="83"/>
@@ -19749,10 +19749,10 @@
       <c r="F152" s="18">
         <v>75</v>
       </c>
-      <c r="G152" s="83">
+      <c r="G152" s="85">
         <v>0</v>
       </c>
-      <c r="H152" s="83">
+      <c r="H152" s="85">
         <v>0</v>
       </c>
       <c r="I152" s="83"/>
@@ -19776,10 +19776,10 @@
       <c r="F153" s="18">
         <v>75</v>
       </c>
-      <c r="G153" s="83">
+      <c r="G153" s="85">
         <v>90</v>
       </c>
-      <c r="H153" s="83">
+      <c r="H153" s="85">
         <v>85</v>
       </c>
       <c r="I153" s="83"/>
@@ -19803,10 +19803,10 @@
       <c r="F154" s="18">
         <v>65</v>
       </c>
-      <c r="G154" s="83">
+      <c r="G154" s="85">
         <v>0</v>
       </c>
-      <c r="H154" s="83">
+      <c r="H154" s="85">
         <v>0</v>
       </c>
       <c r="I154" s="83"/>
@@ -19830,10 +19830,10 @@
       <c r="F155" s="18">
         <v>65</v>
       </c>
-      <c r="G155" s="83">
+      <c r="G155" s="85">
         <v>86</v>
       </c>
-      <c r="H155" s="83">
+      <c r="H155" s="85">
         <v>81</v>
       </c>
       <c r="I155" s="83"/>
@@ -19857,10 +19857,10 @@
       <c r="F156" s="18">
         <v>0</v>
       </c>
-      <c r="G156" s="83">
+      <c r="G156" s="85">
         <v>0</v>
       </c>
-      <c r="H156" s="83">
+      <c r="H156" s="85">
         <v>0</v>
       </c>
       <c r="I156" s="83"/>
@@ -19884,10 +19884,10 @@
       <c r="F157" s="18">
         <v>70</v>
       </c>
-      <c r="G157" s="83">
+      <c r="G157" s="85">
         <v>86</v>
       </c>
-      <c r="H157" s="83">
+      <c r="H157" s="85">
         <v>81</v>
       </c>
       <c r="I157" s="83"/>
@@ -19911,10 +19911,10 @@
       <c r="F158" s="18">
         <v>70</v>
       </c>
-      <c r="G158" s="83">
+      <c r="G158" s="85">
         <v>86</v>
       </c>
-      <c r="H158" s="83">
+      <c r="H158" s="85">
         <v>81</v>
       </c>
       <c r="I158" s="83"/>
@@ -19938,10 +19938,10 @@
       <c r="F159" s="18">
         <v>0</v>
       </c>
-      <c r="G159" s="83">
+      <c r="G159" s="85">
         <v>0</v>
       </c>
-      <c r="H159" s="83">
+      <c r="H159" s="85">
         <v>0</v>
       </c>
       <c r="I159" s="83"/>
@@ -19965,10 +19965,10 @@
       <c r="F160" s="18">
         <v>75</v>
       </c>
-      <c r="G160" s="83">
+      <c r="G160" s="85">
         <v>83</v>
       </c>
-      <c r="H160" s="83">
+      <c r="H160" s="85">
         <v>82</v>
       </c>
       <c r="I160" s="83"/>
@@ -19992,10 +19992,10 @@
       <c r="F161" s="18">
         <v>70</v>
       </c>
-      <c r="G161" s="83">
+      <c r="G161" s="85">
         <v>83</v>
       </c>
-      <c r="H161" s="83">
+      <c r="H161" s="85">
         <v>82</v>
       </c>
       <c r="I161" s="83"/>
@@ -20019,10 +20019,10 @@
       <c r="F162" s="18">
         <v>80</v>
       </c>
-      <c r="G162" s="83">
+      <c r="G162" s="85">
         <v>86</v>
       </c>
-      <c r="H162" s="83">
+      <c r="H162" s="85">
         <v>70</v>
       </c>
       <c r="I162" s="83"/>
@@ -20046,10 +20046,10 @@
       <c r="F163" s="18">
         <v>85</v>
       </c>
-      <c r="G163" s="83">
+      <c r="G163" s="85">
         <v>86</v>
       </c>
-      <c r="H163" s="83">
+      <c r="H163" s="85">
         <v>70</v>
       </c>
       <c r="I163" s="83"/>
@@ -20073,10 +20073,10 @@
       <c r="F164" s="18">
         <v>75</v>
       </c>
-      <c r="G164" s="83">
+      <c r="G164" s="85">
         <v>84</v>
       </c>
-      <c r="H164" s="83">
+      <c r="H164" s="85">
         <v>70</v>
       </c>
       <c r="I164" s="83"/>
@@ -20100,10 +20100,10 @@
       <c r="F165" s="18">
         <v>75</v>
       </c>
-      <c r="G165" s="83">
+      <c r="G165" s="85">
         <v>83</v>
       </c>
-      <c r="H165" s="83">
+      <c r="H165" s="85">
         <v>82</v>
       </c>
       <c r="I165" s="83"/>
@@ -20127,10 +20127,10 @@
       <c r="F166" s="18">
         <v>70</v>
       </c>
-      <c r="G166" s="83">
+      <c r="G166" s="85">
         <v>0</v>
       </c>
-      <c r="H166" s="83">
+      <c r="H166" s="85">
         <v>0</v>
       </c>
       <c r="I166" s="83"/>
@@ -20154,10 +20154,10 @@
       <c r="F167" s="18">
         <v>75</v>
       </c>
-      <c r="G167" s="83">
+      <c r="G167" s="85">
         <v>84</v>
       </c>
-      <c r="H167" s="83">
+      <c r="H167" s="85">
         <v>70</v>
       </c>
       <c r="I167" s="83"/>
@@ -20181,10 +20181,10 @@
       <c r="F168" s="18">
         <v>70</v>
       </c>
-      <c r="G168" s="83">
+      <c r="G168" s="85">
         <v>83</v>
       </c>
-      <c r="H168" s="83">
+      <c r="H168" s="85">
         <v>82</v>
       </c>
       <c r="I168" s="83"/>
@@ -20208,10 +20208,10 @@
       <c r="F169" s="18">
         <v>65</v>
       </c>
-      <c r="G169" s="83">
+      <c r="G169" s="85">
         <v>83</v>
       </c>
-      <c r="H169" s="83">
+      <c r="H169" s="85">
         <v>82</v>
       </c>
       <c r="I169" s="83"/>
@@ -20235,10 +20235,10 @@
       <c r="F170" s="18">
         <v>65</v>
       </c>
-      <c r="G170" s="83">
+      <c r="G170" s="85">
         <v>88</v>
       </c>
-      <c r="H170" s="83">
+      <c r="H170" s="85">
         <v>83</v>
       </c>
       <c r="I170" s="83"/>
@@ -20253,19 +20253,19 @@
       <c r="C171" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D171" s="69">
+      <c r="D171" s="86">
         <v>65</v>
       </c>
-      <c r="E171" s="69">
+      <c r="E171" s="86">
         <v>88</v>
       </c>
-      <c r="F171" s="69">
+      <c r="F171" s="86">
         <v>65</v>
       </c>
-      <c r="G171" s="83">
+      <c r="G171" s="85">
         <v>91</v>
       </c>
-      <c r="H171" s="83">
+      <c r="H171" s="85">
         <v>88</v>
       </c>
       <c r="I171" s="83"/>
@@ -20280,19 +20280,19 @@
       <c r="C172" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D172" s="69">
-        <v>75</v>
-      </c>
-      <c r="E172" s="69">
+      <c r="D172" s="86">
+        <v>75</v>
+      </c>
+      <c r="E172" s="86">
         <v>0</v>
       </c>
-      <c r="F172" s="69">
-        <v>75</v>
-      </c>
-      <c r="G172" s="83">
+      <c r="F172" s="86">
+        <v>75</v>
+      </c>
+      <c r="G172" s="85">
         <v>84</v>
       </c>
-      <c r="H172" s="83">
+      <c r="H172" s="85">
         <v>70</v>
       </c>
       <c r="I172" s="83"/>
@@ -20307,19 +20307,19 @@
       <c r="C173" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="D173" s="69">
+      <c r="D173" s="86">
         <v>65</v>
       </c>
-      <c r="E173" s="69">
+      <c r="E173" s="86">
         <v>88</v>
       </c>
-      <c r="F173" s="69">
+      <c r="F173" s="86">
         <v>65</v>
       </c>
-      <c r="G173" s="83">
+      <c r="G173" s="85">
         <v>84</v>
       </c>
-      <c r="H173" s="83">
+      <c r="H173" s="85">
         <v>70</v>
       </c>
       <c r="I173" s="83"/>
@@ -20332,6 +20332,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20586,17 +20597,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -20607,6 +20607,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20625,23 +20642,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
   <ds:schemaRefs>

--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{132177E6-1EE6-4006-AA2F-88DF4B138208}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{1F4CAF8E-E2DF-43C8-8612-C5746B1CC664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1924A8FC-77F9-491D-83C9-CAA1ADE82180}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2334,7 +2334,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2571,9 +2571,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -20189,11 +20186,11 @@
       </c>
       <c r="I168" s="83"/>
     </row>
-    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="69">
         <v>168</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="16" t="s">
         <v>456</v>
       </c>
       <c r="C169" s="20" t="s">
@@ -20243,7 +20240,7 @@
       </c>
       <c r="I170" s="83"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="69">
         <v>170</v>
       </c>
@@ -20253,13 +20250,13 @@
       <c r="C171" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="D171" s="86">
+      <c r="D171" s="18">
         <v>65</v>
       </c>
-      <c r="E171" s="86">
+      <c r="E171" s="18">
         <v>88</v>
       </c>
-      <c r="F171" s="86">
+      <c r="F171" s="18">
         <v>65</v>
       </c>
       <c r="G171" s="85">
@@ -20270,7 +20267,7 @@
       </c>
       <c r="I171" s="83"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="69">
         <v>171</v>
       </c>
@@ -20280,13 +20277,13 @@
       <c r="C172" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="D172" s="86">
-        <v>75</v>
-      </c>
-      <c r="E172" s="86">
+      <c r="D172" s="18">
+        <v>75</v>
+      </c>
+      <c r="E172" s="18">
         <v>0</v>
       </c>
-      <c r="F172" s="86">
+      <c r="F172" s="18">
         <v>75</v>
       </c>
       <c r="G172" s="85">
@@ -20297,7 +20294,7 @@
       </c>
       <c r="I172" s="83"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="69">
         <v>172</v>
       </c>
@@ -20307,13 +20304,13 @@
       <c r="C173" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="D173" s="86">
+      <c r="D173" s="18">
         <v>65</v>
       </c>
-      <c r="E173" s="86">
+      <c r="E173" s="18">
         <v>88</v>
       </c>
-      <c r="F173" s="86">
+      <c r="F173" s="18">
         <v>65</v>
       </c>
       <c r="G173" s="85">
@@ -20343,6 +20340,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20597,15 +20603,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
@@ -20624,6 +20621,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20640,12 +20645,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="109_{9869BDC9-6CBB-4843-A2C0-112C7B74AE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B92FB554-FBDE-4C65-8AC6-F514C4FB8CBB}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="109_{9869BDC9-6CBB-4843-A2C0-112C7B74AE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B70356AD-B789-4170-8B62-F565B9C3199C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9010" sheetId="2" r:id="rId1"/>
@@ -2443,15 +2443,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2488,6 +2479,15 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2507,6 +2507,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5575,7 +5579,7 @@
         <v>85</v>
       </c>
       <c r="F133" s="18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G133" s="58"/>
     </row>
@@ -6402,10 +6406,10 @@
       <c r="A2" s="69">
         <v>1</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="80" t="s">
         <v>370</v>
       </c>
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="81" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="5">
@@ -6423,10 +6427,10 @@
       <c r="A3" s="69">
         <v>2</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="80" t="s">
         <v>477</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="81" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="5">
@@ -6444,10 +6448,10 @@
       <c r="A4" s="69">
         <v>3</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="80" t="s">
         <v>478</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="81" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="5">
@@ -6465,10 +6469,10 @@
       <c r="A5" s="69">
         <v>4</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="80" t="s">
         <v>479</v>
       </c>
-      <c r="C5" s="84" t="s">
+      <c r="C5" s="81" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="5">
@@ -6486,10 +6490,10 @@
       <c r="A6" s="69">
         <v>5</v>
       </c>
-      <c r="B6" s="85" t="s">
+      <c r="B6" s="82" t="s">
         <v>480</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="81" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5">
@@ -6507,10 +6511,10 @@
       <c r="A7" s="69">
         <v>6</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="82" t="s">
         <v>374</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="81" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="5">
@@ -6528,10 +6532,10 @@
       <c r="A8" s="69">
         <v>7</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="82" t="s">
         <v>481</v>
       </c>
-      <c r="C8" s="84" t="s">
+      <c r="C8" s="81" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="5">
@@ -6549,10 +6553,10 @@
       <c r="A9" s="69">
         <v>8</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="82" t="s">
         <v>482</v>
       </c>
-      <c r="C9" s="84" t="s">
+      <c r="C9" s="81" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="5">
@@ -6570,10 +6574,10 @@
       <c r="A10" s="69">
         <v>9</v>
       </c>
-      <c r="B10" s="85" t="s">
+      <c r="B10" s="82" t="s">
         <v>483</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="81" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="5">
@@ -6591,10 +6595,10 @@
       <c r="A11" s="69">
         <v>10</v>
       </c>
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="82" t="s">
         <v>484</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="81" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5">
@@ -6612,10 +6616,10 @@
       <c r="A12" s="69">
         <v>11</v>
       </c>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="82" t="s">
         <v>485</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="81" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="5">
@@ -6633,10 +6637,10 @@
       <c r="A13" s="69">
         <v>12</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="82" t="s">
         <v>486</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="81" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="5">
@@ -6654,10 +6658,10 @@
       <c r="A14" s="69">
         <v>13</v>
       </c>
-      <c r="B14" s="85" t="s">
+      <c r="B14" s="82" t="s">
         <v>487</v>
       </c>
-      <c r="C14" s="84" t="s">
+      <c r="C14" s="81" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="5">
@@ -6675,10 +6679,10 @@
       <c r="A15" s="69">
         <v>14</v>
       </c>
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="82" t="s">
         <v>488</v>
       </c>
-      <c r="C15" s="84" t="s">
+      <c r="C15" s="81" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="5">
@@ -6696,10 +6700,10 @@
       <c r="A16" s="69">
         <v>15</v>
       </c>
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="82" t="s">
         <v>378</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="81" t="s">
         <v>26</v>
       </c>
       <c r="D16" s="5">
@@ -6717,10 +6721,10 @@
       <c r="A17" s="69">
         <v>16</v>
       </c>
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="82" t="s">
         <v>489</v>
       </c>
-      <c r="C17" s="84" t="s">
+      <c r="C17" s="81" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="5">
@@ -6738,10 +6742,10 @@
       <c r="A18" s="69">
         <v>17</v>
       </c>
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="82" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="84" t="s">
+      <c r="C18" s="81" t="s">
         <v>28</v>
       </c>
       <c r="D18" s="5">
@@ -6759,10 +6763,10 @@
       <c r="A19" s="69">
         <v>18</v>
       </c>
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="82" t="s">
         <v>491</v>
       </c>
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="81" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="5">
@@ -6780,10 +6784,10 @@
       <c r="A20" s="69">
         <v>19</v>
       </c>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="82" t="s">
         <v>379</v>
       </c>
-      <c r="C20" s="84" t="s">
+      <c r="C20" s="81" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="5">
@@ -6801,10 +6805,10 @@
       <c r="A21" s="69">
         <v>20</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="82" t="s">
         <v>492</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="81" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="5">
@@ -6822,10 +6826,10 @@
       <c r="A22" s="69">
         <v>21</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="82" t="s">
         <v>493</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="81" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="5">
@@ -6843,10 +6847,10 @@
       <c r="A23" s="69">
         <v>22</v>
       </c>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="82" t="s">
         <v>494</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="81" t="s">
         <v>33</v>
       </c>
       <c r="D23" s="5">
@@ -6864,10 +6868,10 @@
       <c r="A24" s="69">
         <v>23</v>
       </c>
-      <c r="B24" s="85" t="s">
+      <c r="B24" s="82" t="s">
         <v>495</v>
       </c>
-      <c r="C24" s="84" t="s">
+      <c r="C24" s="81" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="5">
@@ -6885,10 +6889,10 @@
       <c r="A25" s="69">
         <v>24</v>
       </c>
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="82" t="s">
         <v>496</v>
       </c>
-      <c r="C25" s="84" t="s">
+      <c r="C25" s="81" t="s">
         <v>35</v>
       </c>
       <c r="D25" s="5">
@@ -6906,10 +6910,10 @@
       <c r="A26" s="69">
         <v>25</v>
       </c>
-      <c r="B26" s="85" t="s">
+      <c r="B26" s="82" t="s">
         <v>497</v>
       </c>
-      <c r="C26" s="84" t="s">
+      <c r="C26" s="81" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="5">
@@ -6927,10 +6931,10 @@
       <c r="A27" s="69">
         <v>26</v>
       </c>
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="82" t="s">
         <v>380</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="81" t="s">
         <v>37</v>
       </c>
       <c r="D27" s="5">
@@ -6948,10 +6952,10 @@
       <c r="A28" s="69">
         <v>27</v>
       </c>
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="82" t="s">
         <v>498</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="81" t="s">
         <v>39</v>
       </c>
       <c r="D28" s="5">
@@ -6969,10 +6973,10 @@
       <c r="A29" s="69">
         <v>28</v>
       </c>
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="82" t="s">
         <v>382</v>
       </c>
-      <c r="C29" s="84" t="s">
+      <c r="C29" s="81" t="s">
         <v>40</v>
       </c>
       <c r="D29" s="5">
@@ -6990,10 +6994,10 @@
       <c r="A30" s="69">
         <v>29</v>
       </c>
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="82" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="84" t="s">
+      <c r="C30" s="81" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="5">
@@ -7011,10 +7015,10 @@
       <c r="A31" s="69">
         <v>30</v>
       </c>
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="82" t="s">
         <v>384</v>
       </c>
-      <c r="C31" s="84" t="s">
+      <c r="C31" s="81" t="s">
         <v>43</v>
       </c>
       <c r="D31" s="5">
@@ -7032,10 +7036,10 @@
       <c r="A32" s="69">
         <v>31</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="82" t="s">
         <v>386</v>
       </c>
-      <c r="C32" s="84" t="s">
+      <c r="C32" s="81" t="s">
         <v>45</v>
       </c>
       <c r="D32" s="5">
@@ -7053,10 +7057,10 @@
       <c r="A33" s="69">
         <v>32</v>
       </c>
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="82" t="s">
         <v>500</v>
       </c>
-      <c r="C33" s="84" t="s">
+      <c r="C33" s="81" t="s">
         <v>47</v>
       </c>
       <c r="D33" s="5">
@@ -7074,10 +7078,10 @@
       <c r="A34" s="69">
         <v>33</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="82" t="s">
         <v>501</v>
       </c>
-      <c r="C34" s="84" t="s">
+      <c r="C34" s="81" t="s">
         <v>52</v>
       </c>
       <c r="D34" s="5">
@@ -7095,10 +7099,10 @@
       <c r="A35" s="69">
         <v>34</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="82" t="s">
         <v>502</v>
       </c>
-      <c r="C35" s="84" t="s">
+      <c r="C35" s="81" t="s">
         <v>53</v>
       </c>
       <c r="D35" s="5">
@@ -7116,10 +7120,10 @@
       <c r="A36" s="69">
         <v>35</v>
       </c>
-      <c r="B36" s="85" t="s">
+      <c r="B36" s="82" t="s">
         <v>503</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="81" t="s">
         <v>54</v>
       </c>
       <c r="D36" s="5">
@@ -7137,10 +7141,10 @@
       <c r="A37" s="69">
         <v>36</v>
       </c>
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="82" t="s">
         <v>504</v>
       </c>
-      <c r="C37" s="84" t="s">
+      <c r="C37" s="81" t="s">
         <v>55</v>
       </c>
       <c r="D37" s="5">
@@ -7158,10 +7162,10 @@
       <c r="A38" s="69">
         <v>37</v>
       </c>
-      <c r="B38" s="85" t="s">
+      <c r="B38" s="82" t="s">
         <v>505</v>
       </c>
-      <c r="C38" s="84" t="s">
+      <c r="C38" s="81" t="s">
         <v>57</v>
       </c>
       <c r="D38" s="5">
@@ -7179,10 +7183,10 @@
       <c r="A39" s="69">
         <v>38</v>
       </c>
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="82" t="s">
         <v>506</v>
       </c>
-      <c r="C39" s="84" t="s">
+      <c r="C39" s="81" t="s">
         <v>59</v>
       </c>
       <c r="D39" s="5">
@@ -7200,10 +7204,10 @@
       <c r="A40" s="69">
         <v>39</v>
       </c>
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="82" t="s">
         <v>507</v>
       </c>
-      <c r="C40" s="84" t="s">
+      <c r="C40" s="81" t="s">
         <v>60</v>
       </c>
       <c r="D40" s="5">
@@ -7221,10 +7225,10 @@
       <c r="A41" s="69">
         <v>40</v>
       </c>
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="82" t="s">
         <v>508</v>
       </c>
-      <c r="C41" s="84" t="s">
+      <c r="C41" s="81" t="s">
         <v>63</v>
       </c>
       <c r="D41" s="5">
@@ -7242,10 +7246,10 @@
       <c r="A42" s="69">
         <v>41</v>
       </c>
-      <c r="B42" s="85" t="s">
+      <c r="B42" s="82" t="s">
         <v>509</v>
       </c>
-      <c r="C42" s="84" t="s">
+      <c r="C42" s="81" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="5">
@@ -7263,10 +7267,10 @@
       <c r="A43" s="69">
         <v>42</v>
       </c>
-      <c r="B43" s="85" t="s">
+      <c r="B43" s="82" t="s">
         <v>510</v>
       </c>
-      <c r="C43" s="84" t="s">
+      <c r="C43" s="81" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="5">
@@ -7284,10 +7288,10 @@
       <c r="A44" s="69">
         <v>43</v>
       </c>
-      <c r="B44" s="85" t="s">
+      <c r="B44" s="82" t="s">
         <v>511</v>
       </c>
-      <c r="C44" s="84" t="s">
+      <c r="C44" s="81" t="s">
         <v>66</v>
       </c>
       <c r="D44" s="5">
@@ -7305,10 +7309,10 @@
       <c r="A45" s="69">
         <v>44</v>
       </c>
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="82" t="s">
         <v>512</v>
       </c>
-      <c r="C45" s="84" t="s">
+      <c r="C45" s="81" t="s">
         <v>68</v>
       </c>
       <c r="D45" s="5">
@@ -7326,10 +7330,10 @@
       <c r="A46" s="69">
         <v>45</v>
       </c>
-      <c r="B46" s="85" t="s">
+      <c r="B46" s="82" t="s">
         <v>513</v>
       </c>
-      <c r="C46" s="84" t="s">
+      <c r="C46" s="81" t="s">
         <v>71</v>
       </c>
       <c r="D46" s="5">
@@ -7347,10 +7351,10 @@
       <c r="A47" s="69">
         <v>46</v>
       </c>
-      <c r="B47" s="85" t="s">
+      <c r="B47" s="82" t="s">
         <v>514</v>
       </c>
-      <c r="C47" s="84" t="s">
+      <c r="C47" s="81" t="s">
         <v>72</v>
       </c>
       <c r="D47" s="5">
@@ -7368,10 +7372,10 @@
       <c r="A48" s="69">
         <v>47</v>
       </c>
-      <c r="B48" s="85" t="s">
+      <c r="B48" s="82" t="s">
         <v>515</v>
       </c>
-      <c r="C48" s="84" t="s">
+      <c r="C48" s="81" t="s">
         <v>74</v>
       </c>
       <c r="D48" s="5">
@@ -7389,10 +7393,10 @@
       <c r="A49" s="69">
         <v>48</v>
       </c>
-      <c r="B49" s="85" t="s">
+      <c r="B49" s="82" t="s">
         <v>516</v>
       </c>
-      <c r="C49" s="84" t="s">
+      <c r="C49" s="81" t="s">
         <v>75</v>
       </c>
       <c r="D49" s="5">
@@ -7410,10 +7414,10 @@
       <c r="A50" s="69">
         <v>49</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="82" t="s">
         <v>400</v>
       </c>
-      <c r="C50" s="84" t="s">
+      <c r="C50" s="81" t="s">
         <v>76</v>
       </c>
       <c r="D50" s="5">
@@ -7431,10 +7435,10 @@
       <c r="A51" s="69">
         <v>50</v>
       </c>
-      <c r="B51" s="85" t="s">
+      <c r="B51" s="82" t="s">
         <v>401</v>
       </c>
-      <c r="C51" s="84" t="s">
+      <c r="C51" s="81" t="s">
         <v>77</v>
       </c>
       <c r="D51" s="5">
@@ -7452,10 +7456,10 @@
       <c r="A52" s="69">
         <v>51</v>
       </c>
-      <c r="B52" s="85" t="s">
+      <c r="B52" s="82" t="s">
         <v>402</v>
       </c>
-      <c r="C52" s="84" t="s">
+      <c r="C52" s="81" t="s">
         <v>78</v>
       </c>
       <c r="D52" s="5">
@@ -7473,10 +7477,10 @@
       <c r="A53" s="69">
         <v>52</v>
       </c>
-      <c r="B53" s="85" t="s">
+      <c r="B53" s="82" t="s">
         <v>404</v>
       </c>
-      <c r="C53" s="84" t="s">
+      <c r="C53" s="81" t="s">
         <v>80</v>
       </c>
       <c r="D53" s="5">
@@ -7494,10 +7498,10 @@
       <c r="A54" s="69">
         <v>53</v>
       </c>
-      <c r="B54" s="85" t="s">
+      <c r="B54" s="82" t="s">
         <v>517</v>
       </c>
-      <c r="C54" s="84" t="s">
+      <c r="C54" s="81" t="s">
         <v>81</v>
       </c>
       <c r="D54" s="5">
@@ -7515,10 +7519,10 @@
       <c r="A55" s="69">
         <v>54</v>
       </c>
-      <c r="B55" s="85" t="s">
+      <c r="B55" s="82" t="s">
         <v>518</v>
       </c>
-      <c r="C55" s="84" t="s">
+      <c r="C55" s="81" t="s">
         <v>83</v>
       </c>
       <c r="D55" s="5">
@@ -7536,10 +7540,10 @@
       <c r="A56" s="69">
         <v>55</v>
       </c>
-      <c r="B56" s="85" t="s">
+      <c r="B56" s="82" t="s">
         <v>519</v>
       </c>
-      <c r="C56" s="84" t="s">
+      <c r="C56" s="81" t="s">
         <v>85</v>
       </c>
       <c r="D56" s="5">
@@ -7557,10 +7561,10 @@
       <c r="A57" s="69">
         <v>56</v>
       </c>
-      <c r="B57" s="85" t="s">
+      <c r="B57" s="82" t="s">
         <v>520</v>
       </c>
-      <c r="C57" s="84" t="s">
+      <c r="C57" s="81" t="s">
         <v>86</v>
       </c>
       <c r="D57" s="5">
@@ -7578,10 +7582,10 @@
       <c r="A58" s="69">
         <v>57</v>
       </c>
-      <c r="B58" s="85" t="s">
+      <c r="B58" s="82" t="s">
         <v>521</v>
       </c>
-      <c r="C58" s="84" t="s">
+      <c r="C58" s="81" t="s">
         <v>87</v>
       </c>
       <c r="D58" s="5">
@@ -7599,10 +7603,10 @@
       <c r="A59" s="69">
         <v>58</v>
       </c>
-      <c r="B59" s="85" t="s">
+      <c r="B59" s="82" t="s">
         <v>522</v>
       </c>
-      <c r="C59" s="84" t="s">
+      <c r="C59" s="81" t="s">
         <v>88</v>
       </c>
       <c r="D59" s="5">
@@ -7620,10 +7624,10 @@
       <c r="A60" s="69">
         <v>59</v>
       </c>
-      <c r="B60" s="85" t="s">
+      <c r="B60" s="82" t="s">
         <v>523</v>
       </c>
-      <c r="C60" s="84" t="s">
+      <c r="C60" s="81" t="s">
         <v>89</v>
       </c>
       <c r="D60" s="5">
@@ -7641,10 +7645,10 @@
       <c r="A61" s="69">
         <v>60</v>
       </c>
-      <c r="B61" s="85" t="s">
+      <c r="B61" s="82" t="s">
         <v>524</v>
       </c>
-      <c r="C61" s="84" t="s">
+      <c r="C61" s="81" t="s">
         <v>91</v>
       </c>
       <c r="D61" s="5">
@@ -7662,10 +7666,10 @@
       <c r="A62" s="69">
         <v>61</v>
       </c>
-      <c r="B62" s="85" t="s">
+      <c r="B62" s="82" t="s">
         <v>525</v>
       </c>
-      <c r="C62" s="84" t="s">
+      <c r="C62" s="81" t="s">
         <v>93</v>
       </c>
       <c r="D62" s="5">
@@ -7683,10 +7687,10 @@
       <c r="A63" s="69">
         <v>62</v>
       </c>
-      <c r="B63" s="85" t="s">
+      <c r="B63" s="82" t="s">
         <v>526</v>
       </c>
-      <c r="C63" s="84" t="s">
+      <c r="C63" s="81" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="5">
@@ -7704,10 +7708,10 @@
       <c r="A64" s="69">
         <v>63</v>
       </c>
-      <c r="B64" s="85" t="s">
+      <c r="B64" s="82" t="s">
         <v>411</v>
       </c>
-      <c r="C64" s="84" t="s">
+      <c r="C64" s="81" t="s">
         <v>97</v>
       </c>
       <c r="D64" s="5">
@@ -7725,10 +7729,10 @@
       <c r="A65" s="69">
         <v>64</v>
       </c>
-      <c r="B65" s="85" t="s">
+      <c r="B65" s="82" t="s">
         <v>412</v>
       </c>
-      <c r="C65" s="84" t="s">
+      <c r="C65" s="81" t="s">
         <v>98</v>
       </c>
       <c r="D65" s="5">
@@ -7746,10 +7750,10 @@
       <c r="A66" s="69">
         <v>65</v>
       </c>
-      <c r="B66" s="85" t="s">
+      <c r="B66" s="82" t="s">
         <v>527</v>
       </c>
-      <c r="C66" s="84" t="s">
+      <c r="C66" s="81" t="s">
         <v>99</v>
       </c>
       <c r="D66" s="5">
@@ -7767,10 +7771,10 @@
       <c r="A67" s="69">
         <v>66</v>
       </c>
-      <c r="B67" s="85" t="s">
+      <c r="B67" s="82" t="s">
         <v>528</v>
       </c>
-      <c r="C67" s="84" t="s">
+      <c r="C67" s="81" t="s">
         <v>100</v>
       </c>
       <c r="D67" s="5">
@@ -7788,10 +7792,10 @@
       <c r="A68" s="69">
         <v>67</v>
       </c>
-      <c r="B68" s="85" t="s">
+      <c r="B68" s="82" t="s">
         <v>529</v>
       </c>
-      <c r="C68" s="84" t="s">
+      <c r="C68" s="81" t="s">
         <v>102</v>
       </c>
       <c r="D68" s="5">
@@ -7809,10 +7813,10 @@
       <c r="A69" s="69">
         <v>68</v>
       </c>
-      <c r="B69" s="85" t="s">
+      <c r="B69" s="82" t="s">
         <v>414</v>
       </c>
-      <c r="C69" s="84" t="s">
+      <c r="C69" s="81" t="s">
         <v>103</v>
       </c>
       <c r="D69" s="5">
@@ -7830,10 +7834,10 @@
       <c r="A70" s="69">
         <v>69</v>
       </c>
-      <c r="B70" s="85" t="s">
+      <c r="B70" s="82" t="s">
         <v>415</v>
       </c>
-      <c r="C70" s="84" t="s">
+      <c r="C70" s="81" t="s">
         <v>104</v>
       </c>
       <c r="D70" s="5">
@@ -7851,10 +7855,10 @@
       <c r="A71" s="69">
         <v>70</v>
       </c>
-      <c r="B71" s="85" t="s">
+      <c r="B71" s="82" t="s">
         <v>530</v>
       </c>
-      <c r="C71" s="84" t="s">
+      <c r="C71" s="81" t="s">
         <v>105</v>
       </c>
       <c r="D71" s="5">
@@ -7872,10 +7876,10 @@
       <c r="A72" s="69">
         <v>71</v>
       </c>
-      <c r="B72" s="85" t="s">
+      <c r="B72" s="82" t="s">
         <v>531</v>
       </c>
-      <c r="C72" s="84" t="s">
+      <c r="C72" s="81" t="s">
         <v>106</v>
       </c>
       <c r="D72" s="5">
@@ -7893,10 +7897,10 @@
       <c r="A73" s="69">
         <v>72</v>
       </c>
-      <c r="B73" s="85" t="s">
+      <c r="B73" s="82" t="s">
         <v>420</v>
       </c>
-      <c r="C73" s="84" t="s">
+      <c r="C73" s="81" t="s">
         <v>111</v>
       </c>
       <c r="D73" s="5">
@@ -7914,10 +7918,10 @@
       <c r="A74" s="69">
         <v>73</v>
       </c>
-      <c r="B74" s="85" t="s">
+      <c r="B74" s="82" t="s">
         <v>532</v>
       </c>
-      <c r="C74" s="84" t="s">
+      <c r="C74" s="81" t="s">
         <v>112</v>
       </c>
       <c r="D74" s="5">
@@ -7935,10 +7939,10 @@
       <c r="A75" s="69">
         <v>74</v>
       </c>
-      <c r="B75" s="85" t="s">
+      <c r="B75" s="82" t="s">
         <v>533</v>
       </c>
-      <c r="C75" s="84" t="s">
+      <c r="C75" s="81" t="s">
         <v>113</v>
       </c>
       <c r="D75" s="5">
@@ -7956,10 +7960,10 @@
       <c r="A76" s="69">
         <v>75</v>
       </c>
-      <c r="B76" s="85" t="s">
+      <c r="B76" s="82" t="s">
         <v>421</v>
       </c>
-      <c r="C76" s="84" t="s">
+      <c r="C76" s="81" t="s">
         <v>114</v>
       </c>
       <c r="D76" s="5">
@@ -7977,10 +7981,10 @@
       <c r="A77" s="69">
         <v>76</v>
       </c>
-      <c r="B77" s="85" t="s">
+      <c r="B77" s="82" t="s">
         <v>424</v>
       </c>
-      <c r="C77" s="84" t="s">
+      <c r="C77" s="81" t="s">
         <v>117</v>
       </c>
       <c r="D77" s="5">
@@ -7998,10 +8002,10 @@
       <c r="A78" s="69">
         <v>77</v>
       </c>
-      <c r="B78" s="85" t="s">
+      <c r="B78" s="82" t="s">
         <v>428</v>
       </c>
-      <c r="C78" s="84" t="s">
+      <c r="C78" s="81" t="s">
         <v>121</v>
       </c>
       <c r="D78" s="5">
@@ -8019,10 +8023,10 @@
       <c r="A79" s="69">
         <v>78</v>
       </c>
-      <c r="B79" s="85" t="s">
+      <c r="B79" s="82" t="s">
         <v>534</v>
       </c>
-      <c r="C79" s="84" t="s">
+      <c r="C79" s="81" t="s">
         <v>123</v>
       </c>
       <c r="D79" s="5">
@@ -8040,10 +8044,10 @@
       <c r="A80" s="69">
         <v>79</v>
       </c>
-      <c r="B80" s="85" t="s">
+      <c r="B80" s="82" t="s">
         <v>432</v>
       </c>
-      <c r="C80" s="84" t="s">
+      <c r="C80" s="81" t="s">
         <v>126</v>
       </c>
       <c r="D80" s="5">
@@ -8061,10 +8065,10 @@
       <c r="A81" s="69">
         <v>80</v>
       </c>
-      <c r="B81" s="85" t="s">
+      <c r="B81" s="82" t="s">
         <v>535</v>
       </c>
-      <c r="C81" s="84" t="s">
+      <c r="C81" s="81" t="s">
         <v>127</v>
       </c>
       <c r="D81" s="5">
@@ -8082,10 +8086,10 @@
       <c r="A82" s="69">
         <v>81</v>
       </c>
-      <c r="B82" s="85" t="s">
+      <c r="B82" s="82" t="s">
         <v>536</v>
       </c>
-      <c r="C82" s="84" t="s">
+      <c r="C82" s="81" t="s">
         <v>128</v>
       </c>
       <c r="D82" s="5">
@@ -8103,10 +8107,10 @@
       <c r="A83" s="69">
         <v>82</v>
       </c>
-      <c r="B83" s="85" t="s">
+      <c r="B83" s="82" t="s">
         <v>435</v>
       </c>
-      <c r="C83" s="84" t="s">
+      <c r="C83" s="81" t="s">
         <v>131</v>
       </c>
       <c r="D83" s="5">
@@ -8124,10 +8128,10 @@
       <c r="A84" s="69">
         <v>83</v>
       </c>
-      <c r="B84" s="85" t="s">
+      <c r="B84" s="82" t="s">
         <v>537</v>
       </c>
-      <c r="C84" s="84" t="s">
+      <c r="C84" s="81" t="s">
         <v>132</v>
       </c>
       <c r="D84" s="5">
@@ -8145,10 +8149,10 @@
       <c r="A85" s="69">
         <v>84</v>
       </c>
-      <c r="B85" s="85" t="s">
+      <c r="B85" s="82" t="s">
         <v>436</v>
       </c>
-      <c r="C85" s="84" t="s">
+      <c r="C85" s="81" t="s">
         <v>133</v>
       </c>
       <c r="D85" s="5">
@@ -8166,10 +8170,10 @@
       <c r="A86" s="69">
         <v>85</v>
       </c>
-      <c r="B86" s="85" t="s">
+      <c r="B86" s="82" t="s">
         <v>538</v>
       </c>
-      <c r="C86" s="84" t="s">
+      <c r="C86" s="81" t="s">
         <v>134</v>
       </c>
       <c r="D86" s="5">
@@ -8187,10 +8191,10 @@
       <c r="A87" s="69">
         <v>86</v>
       </c>
-      <c r="B87" s="85" t="s">
+      <c r="B87" s="82" t="s">
         <v>437</v>
       </c>
-      <c r="C87" s="84" t="s">
+      <c r="C87" s="81" t="s">
         <v>135</v>
       </c>
       <c r="D87" s="5">
@@ -8208,10 +8212,10 @@
       <c r="A88" s="69">
         <v>87</v>
       </c>
-      <c r="B88" s="85" t="s">
+      <c r="B88" s="82" t="s">
         <v>539</v>
       </c>
-      <c r="C88" s="84" t="s">
+      <c r="C88" s="81" t="s">
         <v>136</v>
       </c>
       <c r="D88" s="5">
@@ -8229,10 +8233,10 @@
       <c r="A89" s="69">
         <v>88</v>
       </c>
-      <c r="B89" s="85" t="s">
+      <c r="B89" s="82" t="s">
         <v>438</v>
       </c>
-      <c r="C89" s="84" t="s">
+      <c r="C89" s="81" t="s">
         <v>137</v>
       </c>
       <c r="D89" s="5">
@@ -8250,10 +8254,10 @@
       <c r="A90" s="69">
         <v>89</v>
       </c>
-      <c r="B90" s="85" t="s">
+      <c r="B90" s="82" t="s">
         <v>540</v>
       </c>
-      <c r="C90" s="84" t="s">
+      <c r="C90" s="81" t="s">
         <v>138</v>
       </c>
       <c r="D90" s="5">
@@ -8271,10 +8275,10 @@
       <c r="A91" s="69">
         <v>90</v>
       </c>
-      <c r="B91" s="85" t="s">
+      <c r="B91" s="82" t="s">
         <v>541</v>
       </c>
-      <c r="C91" s="84" t="s">
+      <c r="C91" s="81" t="s">
         <v>139</v>
       </c>
       <c r="D91" s="5">
@@ -8292,10 +8296,10 @@
       <c r="A92" s="69">
         <v>91</v>
       </c>
-      <c r="B92" s="85" t="s">
+      <c r="B92" s="82" t="s">
         <v>542</v>
       </c>
-      <c r="C92" s="84" t="s">
+      <c r="C92" s="81" t="s">
         <v>140</v>
       </c>
       <c r="D92" s="5">
@@ -8313,10 +8317,10 @@
       <c r="A93" s="69">
         <v>92</v>
       </c>
-      <c r="B93" s="85" t="s">
+      <c r="B93" s="82" t="s">
         <v>439</v>
       </c>
-      <c r="C93" s="84" t="s">
+      <c r="C93" s="81" t="s">
         <v>141</v>
       </c>
       <c r="D93" s="5">
@@ -8334,10 +8338,10 @@
       <c r="A94" s="69">
         <v>93</v>
       </c>
-      <c r="B94" s="85" t="s">
+      <c r="B94" s="82" t="s">
         <v>440</v>
       </c>
-      <c r="C94" s="84" t="s">
+      <c r="C94" s="81" t="s">
         <v>142</v>
       </c>
       <c r="D94" s="5">
@@ -8355,10 +8359,10 @@
       <c r="A95" s="69">
         <v>94</v>
       </c>
-      <c r="B95" s="85" t="s">
+      <c r="B95" s="82" t="s">
         <v>543</v>
       </c>
-      <c r="C95" s="84" t="s">
+      <c r="C95" s="81" t="s">
         <v>145</v>
       </c>
       <c r="D95" s="5">
@@ -8376,10 +8380,10 @@
       <c r="A96" s="69">
         <v>95</v>
       </c>
-      <c r="B96" s="85" t="s">
+      <c r="B96" s="82" t="s">
         <v>444</v>
       </c>
-      <c r="C96" s="84" t="s">
+      <c r="C96" s="81" t="s">
         <v>147</v>
       </c>
       <c r="D96" s="5">
@@ -8397,10 +8401,10 @@
       <c r="A97" s="69">
         <v>96</v>
       </c>
-      <c r="B97" s="85" t="s">
+      <c r="B97" s="82" t="s">
         <v>544</v>
       </c>
-      <c r="C97" s="84" t="s">
+      <c r="C97" s="81" t="s">
         <v>148</v>
       </c>
       <c r="D97" s="5">
@@ -8418,10 +8422,10 @@
       <c r="A98" s="69">
         <v>97</v>
       </c>
-      <c r="B98" s="85" t="s">
+      <c r="B98" s="82" t="s">
         <v>445</v>
       </c>
-      <c r="C98" s="84" t="s">
+      <c r="C98" s="81" t="s">
         <v>149</v>
       </c>
       <c r="D98" s="5">
@@ -8439,10 +8443,10 @@
       <c r="A99" s="69">
         <v>98</v>
       </c>
-      <c r="B99" s="85" t="s">
+      <c r="B99" s="82" t="s">
         <v>446</v>
       </c>
-      <c r="C99" s="84" t="s">
+      <c r="C99" s="81" t="s">
         <v>150</v>
       </c>
       <c r="D99" s="5">
@@ -8460,10 +8464,10 @@
       <c r="A100" s="69">
         <v>99</v>
       </c>
-      <c r="B100" s="85" t="s">
+      <c r="B100" s="82" t="s">
         <v>545</v>
       </c>
-      <c r="C100" s="84" t="s">
+      <c r="C100" s="81" t="s">
         <v>151</v>
       </c>
       <c r="D100" s="5">
@@ -8481,10 +8485,10 @@
       <c r="A101" s="69">
         <v>100</v>
       </c>
-      <c r="B101" s="85" t="s">
+      <c r="B101" s="82" t="s">
         <v>546</v>
       </c>
-      <c r="C101" s="84" t="s">
+      <c r="C101" s="81" t="s">
         <v>153</v>
       </c>
       <c r="D101" s="5">
@@ -8502,10 +8506,10 @@
       <c r="A102" s="69">
         <v>101</v>
       </c>
-      <c r="B102" s="85" t="s">
+      <c r="B102" s="82" t="s">
         <v>547</v>
       </c>
-      <c r="C102" s="84" t="s">
+      <c r="C102" s="81" t="s">
         <v>154</v>
       </c>
       <c r="D102" s="5">
@@ -8523,10 +8527,10 @@
       <c r="A103" s="69">
         <v>102</v>
       </c>
-      <c r="B103" s="85" t="s">
+      <c r="B103" s="82" t="s">
         <v>548</v>
       </c>
-      <c r="C103" s="84" t="s">
+      <c r="C103" s="81" t="s">
         <v>156</v>
       </c>
       <c r="D103" s="5">
@@ -8544,10 +8548,10 @@
       <c r="A104" s="69">
         <v>103</v>
       </c>
-      <c r="B104" s="85" t="s">
+      <c r="B104" s="82" t="s">
         <v>549</v>
       </c>
-      <c r="C104" s="84" t="s">
+      <c r="C104" s="81" t="s">
         <v>157</v>
       </c>
       <c r="D104" s="5">
@@ -8565,10 +8569,10 @@
       <c r="A105" s="69">
         <v>104</v>
       </c>
-      <c r="B105" s="86" t="s">
+      <c r="B105" s="83" t="s">
         <v>550</v>
       </c>
-      <c r="C105" s="84" t="s">
+      <c r="C105" s="81" t="s">
         <v>159</v>
       </c>
       <c r="D105" s="5">
@@ -8586,10 +8590,10 @@
       <c r="A106" s="69">
         <v>105</v>
       </c>
-      <c r="B106" s="85" t="s">
+      <c r="B106" s="82" t="s">
         <v>551</v>
       </c>
-      <c r="C106" s="84" t="s">
+      <c r="C106" s="81" t="s">
         <v>161</v>
       </c>
       <c r="D106" s="5">
@@ -8607,10 +8611,10 @@
       <c r="A107" s="69">
         <v>106</v>
       </c>
-      <c r="B107" s="85" t="s">
+      <c r="B107" s="82" t="s">
         <v>454</v>
       </c>
-      <c r="C107" s="84" t="s">
+      <c r="C107" s="81" t="s">
         <v>165</v>
       </c>
       <c r="D107" s="5">
@@ -8628,10 +8632,10 @@
       <c r="A108" s="69">
         <v>107</v>
       </c>
-      <c r="B108" s="87" t="s">
+      <c r="B108" s="84" t="s">
         <v>455</v>
       </c>
-      <c r="C108" s="84" t="s">
+      <c r="C108" s="81" t="s">
         <v>166</v>
       </c>
       <c r="D108" s="5">
@@ -8649,10 +8653,10 @@
       <c r="A109" s="69">
         <v>108</v>
       </c>
-      <c r="B109" s="85" t="s">
+      <c r="B109" s="82" t="s">
         <v>456</v>
       </c>
-      <c r="C109" s="84" t="s">
+      <c r="C109" s="81" t="s">
         <v>167</v>
       </c>
       <c r="D109" s="5">
@@ -8670,10 +8674,10 @@
       <c r="A110" s="69">
         <v>109</v>
       </c>
-      <c r="B110" s="85" t="s">
+      <c r="B110" s="82" t="s">
         <v>459</v>
       </c>
-      <c r="C110" s="84" t="s">
+      <c r="C110" s="81" t="s">
         <v>170</v>
       </c>
       <c r="D110" s="5">
@@ -8691,10 +8695,10 @@
       <c r="A111" s="69">
         <v>110</v>
       </c>
-      <c r="B111" s="85" t="s">
+      <c r="B111" s="82" t="s">
         <v>552</v>
       </c>
-      <c r="C111" s="84" t="s">
+      <c r="C111" s="81" t="s">
         <v>171</v>
       </c>
       <c r="D111" s="5">
@@ -8712,10 +8716,10 @@
       <c r="A112" s="69">
         <v>111</v>
       </c>
-      <c r="B112" s="86" t="s">
+      <c r="B112" s="83" t="s">
         <v>461</v>
       </c>
-      <c r="C112" s="84" t="s">
+      <c r="C112" s="81" t="s">
         <v>172</v>
       </c>
       <c r="D112" s="5">
@@ -8733,10 +8737,10 @@
       <c r="A113" s="69">
         <v>112</v>
       </c>
-      <c r="B113" s="88" t="s">
+      <c r="B113" s="85" t="s">
         <v>462</v>
       </c>
-      <c r="C113" s="84" t="s">
+      <c r="C113" s="81" t="s">
         <v>173</v>
       </c>
       <c r="D113" s="5">
@@ -8754,10 +8758,10 @@
       <c r="A114" s="69">
         <v>113</v>
       </c>
-      <c r="B114" s="89" t="s">
+      <c r="B114" s="86" t="s">
         <v>463</v>
       </c>
-      <c r="C114" s="84" t="s">
+      <c r="C114" s="81" t="s">
         <v>174</v>
       </c>
       <c r="D114" s="5">
@@ -8775,10 +8779,10 @@
       <c r="A115" s="69">
         <v>114</v>
       </c>
-      <c r="B115" s="89" t="s">
+      <c r="B115" s="86" t="s">
         <v>553</v>
       </c>
-      <c r="C115" s="84" t="s">
+      <c r="C115" s="81" t="s">
         <v>176</v>
       </c>
       <c r="D115" s="5">
@@ -8796,10 +8800,10 @@
       <c r="A116" s="69">
         <v>115</v>
       </c>
-      <c r="B116" s="90" t="s">
+      <c r="B116" s="87" t="s">
         <v>566</v>
       </c>
-      <c r="C116" s="84" t="s">
+      <c r="C116" s="81" t="s">
         <v>564</v>
       </c>
       <c r="D116" s="5">
@@ -8817,10 +8821,10 @@
       <c r="A117" s="69">
         <v>116</v>
       </c>
-      <c r="B117" s="89" t="s">
+      <c r="B117" s="86" t="s">
         <v>567</v>
       </c>
-      <c r="C117" s="84" t="s">
+      <c r="C117" s="81" t="s">
         <v>562</v>
       </c>
       <c r="D117" s="5">
@@ -8838,10 +8842,10 @@
       <c r="A118" s="69">
         <v>117</v>
       </c>
-      <c r="B118" s="89" t="s">
+      <c r="B118" s="86" t="s">
         <v>568</v>
       </c>
-      <c r="C118" s="84" t="s">
+      <c r="C118" s="81" t="s">
         <v>336</v>
       </c>
       <c r="D118" s="5">
@@ -8859,10 +8863,10 @@
       <c r="A119" s="69">
         <v>118</v>
       </c>
-      <c r="B119" s="89" t="s">
+      <c r="B119" s="86" t="s">
         <v>555</v>
       </c>
-      <c r="C119" s="84" t="s">
+      <c r="C119" s="81" t="s">
         <v>337</v>
       </c>
       <c r="D119" s="5">
@@ -8880,10 +8884,10 @@
       <c r="A120" s="69">
         <v>119</v>
       </c>
-      <c r="B120" s="89" t="s">
+      <c r="B120" s="86" t="s">
         <v>556</v>
       </c>
-      <c r="C120" s="84" t="s">
+      <c r="C120" s="81" t="s">
         <v>338</v>
       </c>
       <c r="D120" s="5">
@@ -8901,10 +8905,10 @@
       <c r="A121" s="69">
         <v>120</v>
       </c>
-      <c r="B121" s="89" t="s">
+      <c r="B121" s="86" t="s">
         <v>569</v>
       </c>
-      <c r="C121" s="84" t="s">
+      <c r="C121" s="81" t="s">
         <v>341</v>
       </c>
       <c r="D121" s="5">
@@ -8922,10 +8926,10 @@
       <c r="A122" s="69">
         <v>121</v>
       </c>
-      <c r="B122" s="89" t="s">
+      <c r="B122" s="86" t="s">
         <v>557</v>
       </c>
-      <c r="C122" s="84" t="s">
+      <c r="C122" s="81" t="s">
         <v>342</v>
       </c>
       <c r="D122" s="5">
@@ -8943,10 +8947,10 @@
       <c r="A123" s="69">
         <v>122</v>
       </c>
-      <c r="B123" s="89" t="s">
+      <c r="B123" s="86" t="s">
         <v>570</v>
       </c>
-      <c r="C123" s="84" t="s">
+      <c r="C123" s="81" t="s">
         <v>343</v>
       </c>
       <c r="D123" s="5">
@@ -8964,10 +8968,10 @@
       <c r="A124" s="69">
         <v>123</v>
       </c>
-      <c r="B124" s="89" t="s">
+      <c r="B124" s="86" t="s">
         <v>571</v>
       </c>
-      <c r="C124" s="84" t="s">
+      <c r="C124" s="81" t="s">
         <v>344</v>
       </c>
       <c r="D124" s="5">
@@ -8985,10 +8989,10 @@
       <c r="A125" s="69">
         <v>124</v>
       </c>
-      <c r="B125" s="89" t="s">
+      <c r="B125" s="86" t="s">
         <v>558</v>
       </c>
-      <c r="C125" s="84" t="s">
+      <c r="C125" s="81" t="s">
         <v>345</v>
       </c>
       <c r="D125" s="5">
@@ -9006,10 +9010,10 @@
       <c r="A126" s="69">
         <v>125</v>
       </c>
-      <c r="B126" s="89" t="s">
+      <c r="B126" s="86" t="s">
         <v>572</v>
       </c>
-      <c r="C126" s="84" t="s">
+      <c r="C126" s="81" t="s">
         <v>563</v>
       </c>
       <c r="D126" s="5">
@@ -15974,17 +15978,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="88" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="76"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="90"/>
     </row>
     <row r="2" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
@@ -16025,19 +16029,19 @@
       <c r="C3" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="77">
-        <v>70</v>
-      </c>
-      <c r="E3" s="77">
+      <c r="D3" s="74">
+        <v>70</v>
+      </c>
+      <c r="E3" s="74">
         <v>83</v>
       </c>
-      <c r="F3" s="77">
+      <c r="F3" s="74">
         <v>80</v>
       </c>
-      <c r="G3" s="77">
+      <c r="G3" s="74">
         <v>91</v>
       </c>
-      <c r="H3" s="78">
+      <c r="H3" s="75">
         <v>88</v>
       </c>
       <c r="I3" s="57"/>
@@ -16052,19 +16056,19 @@
       <c r="C4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="76">
         <v>85</v>
       </c>
-      <c r="E4" s="79">
+      <c r="E4" s="76">
         <v>83</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="76">
         <v>65</v>
       </c>
-      <c r="G4" s="79">
+      <c r="G4" s="76">
         <v>89</v>
       </c>
-      <c r="H4" s="80">
+      <c r="H4" s="77">
         <v>71</v>
       </c>
       <c r="I4" s="58"/>
@@ -16079,19 +16083,19 @@
       <c r="C5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="79">
-        <v>70</v>
-      </c>
-      <c r="E5" s="79">
+      <c r="D5" s="76">
+        <v>70</v>
+      </c>
+      <c r="E5" s="76">
         <v>83</v>
       </c>
-      <c r="F5" s="79">
-        <v>75</v>
-      </c>
-      <c r="G5" s="79">
+      <c r="F5" s="76">
+        <v>75</v>
+      </c>
+      <c r="G5" s="76">
         <v>88</v>
       </c>
-      <c r="H5" s="80">
+      <c r="H5" s="77">
         <v>83</v>
       </c>
       <c r="I5" s="58"/>
@@ -16106,19 +16110,19 @@
       <c r="C6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="79">
-        <v>75</v>
-      </c>
-      <c r="E6" s="79">
+      <c r="D6" s="76">
+        <v>75</v>
+      </c>
+      <c r="E6" s="76">
         <v>91</v>
       </c>
-      <c r="F6" s="79">
+      <c r="F6" s="76">
         <v>85</v>
       </c>
-      <c r="G6" s="79">
+      <c r="G6" s="76">
         <v>86</v>
       </c>
-      <c r="H6" s="80">
+      <c r="H6" s="77">
         <v>81</v>
       </c>
       <c r="I6" s="58"/>
@@ -16133,19 +16137,19 @@
       <c r="C7" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="76">
         <v>78</v>
       </c>
-      <c r="E7" s="79">
+      <c r="E7" s="76">
         <v>90</v>
       </c>
-      <c r="F7" s="79">
+      <c r="F7" s="76">
         <v>80</v>
       </c>
-      <c r="G7" s="79">
+      <c r="G7" s="76">
         <v>88</v>
       </c>
-      <c r="H7" s="80">
+      <c r="H7" s="77">
         <v>89</v>
       </c>
       <c r="I7" s="58"/>
@@ -16160,19 +16164,19 @@
       <c r="C8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="79">
-        <v>70</v>
-      </c>
-      <c r="E8" s="79">
+      <c r="D8" s="76">
+        <v>70</v>
+      </c>
+      <c r="E8" s="76">
         <v>90</v>
       </c>
-      <c r="F8" s="79">
-        <v>75</v>
-      </c>
-      <c r="G8" s="79">
+      <c r="F8" s="76">
+        <v>75</v>
+      </c>
+      <c r="G8" s="76">
         <v>88</v>
       </c>
-      <c r="H8" s="80">
+      <c r="H8" s="77">
         <v>89</v>
       </c>
       <c r="I8" s="58"/>
@@ -16187,19 +16191,19 @@
       <c r="C9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="79">
-        <v>75</v>
-      </c>
-      <c r="E9" s="79">
+      <c r="D9" s="76">
+        <v>75</v>
+      </c>
+      <c r="E9" s="76">
         <v>91</v>
       </c>
-      <c r="F9" s="79">
+      <c r="F9" s="76">
         <v>85</v>
       </c>
-      <c r="G9" s="79">
+      <c r="G9" s="76">
         <v>84</v>
       </c>
-      <c r="H9" s="80">
+      <c r="H9" s="77">
         <v>70</v>
       </c>
       <c r="I9" s="58"/>
@@ -16211,22 +16215,22 @@
       <c r="B10" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="79">
-        <v>75</v>
-      </c>
-      <c r="E10" s="79">
+      <c r="D10" s="76">
+        <v>75</v>
+      </c>
+      <c r="E10" s="76">
         <v>90</v>
       </c>
-      <c r="F10" s="79">
+      <c r="F10" s="76">
         <v>80</v>
       </c>
-      <c r="G10" s="79">
+      <c r="G10" s="76">
         <v>88</v>
       </c>
-      <c r="H10" s="80">
+      <c r="H10" s="77">
         <v>83</v>
       </c>
       <c r="I10" s="58"/>
@@ -16238,22 +16242,22 @@
       <c r="B11" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="76">
         <v>80</v>
       </c>
-      <c r="E11" s="79">
+      <c r="E11" s="76">
         <v>90</v>
       </c>
-      <c r="F11" s="79">
-        <v>70</v>
-      </c>
-      <c r="G11" s="79">
+      <c r="F11" s="76">
+        <v>70</v>
+      </c>
+      <c r="G11" s="76">
         <v>89</v>
       </c>
-      <c r="H11" s="80">
+      <c r="H11" s="77">
         <v>71</v>
       </c>
       <c r="I11" s="58"/>
@@ -16265,22 +16269,22 @@
       <c r="B12" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="79">
-        <v>70</v>
-      </c>
-      <c r="E12" s="79">
+      <c r="D12" s="76">
+        <v>70</v>
+      </c>
+      <c r="E12" s="76">
         <v>83</v>
       </c>
-      <c r="F12" s="79">
+      <c r="F12" s="76">
         <v>80</v>
       </c>
-      <c r="G12" s="79">
+      <c r="G12" s="76">
         <v>84</v>
       </c>
-      <c r="H12" s="80">
+      <c r="H12" s="77">
         <v>70</v>
       </c>
       <c r="I12" s="58"/>
@@ -16292,22 +16296,22 @@
       <c r="B13" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="79">
-        <v>70</v>
-      </c>
-      <c r="E13" s="79">
+      <c r="D13" s="76">
+        <v>70</v>
+      </c>
+      <c r="E13" s="76">
         <v>90</v>
       </c>
-      <c r="F13" s="79">
-        <v>75</v>
-      </c>
-      <c r="G13" s="79">
+      <c r="F13" s="76">
+        <v>75</v>
+      </c>
+      <c r="G13" s="76">
         <v>86</v>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="77">
         <v>70</v>
       </c>
       <c r="I13" s="58"/>
@@ -16319,22 +16323,22 @@
       <c r="B14" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="79">
-        <v>75</v>
-      </c>
-      <c r="E14" s="79">
+      <c r="D14" s="76">
+        <v>75</v>
+      </c>
+      <c r="E14" s="76">
         <v>90</v>
       </c>
-      <c r="F14" s="79">
+      <c r="F14" s="76">
         <v>80</v>
       </c>
-      <c r="G14" s="79">
+      <c r="G14" s="76">
         <v>84</v>
       </c>
-      <c r="H14" s="80">
+      <c r="H14" s="77">
         <v>70</v>
       </c>
       <c r="I14" s="58"/>
@@ -16346,22 +16350,22 @@
       <c r="B15" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="79">
-        <v>70</v>
-      </c>
-      <c r="E15" s="79">
+      <c r="D15" s="76">
+        <v>70</v>
+      </c>
+      <c r="E15" s="76">
         <v>83</v>
       </c>
-      <c r="F15" s="79">
-        <v>75</v>
-      </c>
-      <c r="G15" s="79">
+      <c r="F15" s="76">
+        <v>75</v>
+      </c>
+      <c r="G15" s="76">
         <v>90</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="77">
         <v>85</v>
       </c>
       <c r="I15" s="58"/>
@@ -16373,22 +16377,22 @@
       <c r="B16" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="C16" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="79">
-        <v>75</v>
-      </c>
-      <c r="E16" s="79">
+      <c r="D16" s="76">
+        <v>75</v>
+      </c>
+      <c r="E16" s="76">
         <v>92</v>
       </c>
-      <c r="F16" s="79">
-        <v>75</v>
-      </c>
-      <c r="G16" s="79">
+      <c r="F16" s="76">
+        <v>75</v>
+      </c>
+      <c r="G16" s="76">
         <v>83</v>
       </c>
-      <c r="H16" s="80">
+      <c r="H16" s="77">
         <v>82</v>
       </c>
       <c r="I16" s="58"/>
@@ -16400,22 +16404,22 @@
       <c r="B17" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="79">
-        <v>75</v>
-      </c>
-      <c r="E17" s="79">
+      <c r="D17" s="76">
+        <v>75</v>
+      </c>
+      <c r="E17" s="76">
         <v>88</v>
       </c>
-      <c r="F17" s="79">
+      <c r="F17" s="76">
         <v>80</v>
       </c>
-      <c r="G17" s="79">
+      <c r="G17" s="76">
         <v>86</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="77">
         <v>84</v>
       </c>
       <c r="I17" s="58"/>
@@ -16427,22 +16431,22 @@
       <c r="B18" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="79">
-        <v>70</v>
-      </c>
-      <c r="E18" s="79">
+      <c r="D18" s="76">
+        <v>70</v>
+      </c>
+      <c r="E18" s="76">
         <v>88</v>
       </c>
-      <c r="F18" s="79">
-        <v>75</v>
-      </c>
-      <c r="G18" s="79">
+      <c r="F18" s="76">
+        <v>75</v>
+      </c>
+      <c r="G18" s="76">
         <v>89</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="77">
         <v>71</v>
       </c>
       <c r="I18" s="58"/>
@@ -16454,22 +16458,22 @@
       <c r="B19" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="C19" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="79">
-        <v>70</v>
-      </c>
-      <c r="E19" s="79">
+      <c r="D19" s="76">
+        <v>70</v>
+      </c>
+      <c r="E19" s="76">
         <v>92</v>
       </c>
-      <c r="F19" s="79">
+      <c r="F19" s="76">
         <v>80</v>
       </c>
-      <c r="G19" s="79">
+      <c r="G19" s="76">
         <v>91</v>
       </c>
-      <c r="H19" s="80">
+      <c r="H19" s="77">
         <v>88</v>
       </c>
       <c r="I19" s="58"/>
@@ -16481,22 +16485,22 @@
       <c r="B20" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C20" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="79">
+      <c r="D20" s="76">
         <v>85</v>
       </c>
-      <c r="E20" s="79">
+      <c r="E20" s="76">
         <v>90</v>
       </c>
-      <c r="F20" s="79">
+      <c r="F20" s="76">
         <v>65</v>
       </c>
-      <c r="G20" s="79">
+      <c r="G20" s="76">
         <v>89</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="77">
         <v>71</v>
       </c>
       <c r="I20" s="58"/>
@@ -16508,22 +16512,22 @@
       <c r="B21" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C21" s="81" t="s">
+      <c r="C21" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="76">
         <v>80</v>
       </c>
-      <c r="E21" s="79">
+      <c r="E21" s="76">
         <v>90</v>
       </c>
-      <c r="F21" s="79">
-        <v>70</v>
-      </c>
-      <c r="G21" s="79">
+      <c r="F21" s="76">
+        <v>70</v>
+      </c>
+      <c r="G21" s="76">
         <v>89</v>
       </c>
-      <c r="H21" s="80">
+      <c r="H21" s="77">
         <v>71</v>
       </c>
       <c r="I21" s="58"/>
@@ -16535,22 +16539,22 @@
       <c r="B22" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="79">
+      <c r="D22" s="76">
         <v>78</v>
       </c>
-      <c r="E22" s="79">
+      <c r="E22" s="76">
         <v>92</v>
       </c>
-      <c r="F22" s="79">
+      <c r="F22" s="76">
         <v>80</v>
       </c>
-      <c r="G22" s="79">
+      <c r="G22" s="76">
         <v>84</v>
       </c>
-      <c r="H22" s="80">
+      <c r="H22" s="77">
         <v>70</v>
       </c>
       <c r="I22" s="58"/>
@@ -16562,22 +16566,22 @@
       <c r="B23" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C23" s="81" t="s">
+      <c r="C23" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="79">
-        <v>75</v>
-      </c>
-      <c r="E23" s="79">
+      <c r="D23" s="76">
+        <v>75</v>
+      </c>
+      <c r="E23" s="76">
         <v>90</v>
       </c>
-      <c r="F23" s="79">
-        <v>75</v>
-      </c>
-      <c r="G23" s="79">
+      <c r="F23" s="76">
+        <v>75</v>
+      </c>
+      <c r="G23" s="76">
         <v>86</v>
       </c>
-      <c r="H23" s="80">
+      <c r="H23" s="77">
         <v>81</v>
       </c>
       <c r="I23" s="58"/>
@@ -16589,22 +16593,22 @@
       <c r="B24" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="79">
+      <c r="D24" s="76">
         <v>78</v>
       </c>
-      <c r="E24" s="79">
+      <c r="E24" s="76">
         <v>89</v>
       </c>
-      <c r="F24" s="79">
+      <c r="F24" s="76">
         <v>80</v>
       </c>
-      <c r="G24" s="79">
+      <c r="G24" s="76">
         <v>86</v>
       </c>
-      <c r="H24" s="80">
+      <c r="H24" s="77">
         <v>84</v>
       </c>
       <c r="I24" s="58"/>
@@ -16616,22 +16620,22 @@
       <c r="B25" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="79">
+      <c r="D25" s="76">
         <v>78</v>
       </c>
-      <c r="E25" s="79">
+      <c r="E25" s="76">
         <v>92</v>
       </c>
-      <c r="F25" s="79">
+      <c r="F25" s="76">
         <v>80</v>
       </c>
-      <c r="G25" s="79">
+      <c r="G25" s="76">
         <v>86</v>
       </c>
-      <c r="H25" s="80">
+      <c r="H25" s="77">
         <v>81</v>
       </c>
       <c r="I25" s="58"/>
@@ -16643,22 +16647,22 @@
       <c r="B26" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="79">
-        <v>75</v>
-      </c>
-      <c r="E26" s="79">
+      <c r="D26" s="76">
+        <v>75</v>
+      </c>
+      <c r="E26" s="76">
         <v>92</v>
       </c>
-      <c r="F26" s="79">
-        <v>75</v>
-      </c>
-      <c r="G26" s="79">
+      <c r="F26" s="76">
+        <v>75</v>
+      </c>
+      <c r="G26" s="76">
         <v>83</v>
       </c>
-      <c r="H26" s="80">
+      <c r="H26" s="77">
         <v>82</v>
       </c>
       <c r="I26" s="58"/>
@@ -16670,22 +16674,22 @@
       <c r="B27" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="79">
+      <c r="D27" s="76">
         <v>78</v>
       </c>
-      <c r="E27" s="79">
+      <c r="E27" s="76">
         <v>91</v>
       </c>
-      <c r="F27" s="79">
+      <c r="F27" s="76">
         <v>80</v>
       </c>
-      <c r="G27" s="79">
+      <c r="G27" s="76">
         <v>83</v>
       </c>
-      <c r="H27" s="80">
+      <c r="H27" s="77">
         <v>82</v>
       </c>
       <c r="I27" s="58"/>
@@ -16697,22 +16701,22 @@
       <c r="B28" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C28" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="79">
-        <v>70</v>
-      </c>
-      <c r="E28" s="79">
+      <c r="D28" s="76">
+        <v>70</v>
+      </c>
+      <c r="E28" s="76">
         <v>89</v>
       </c>
-      <c r="F28" s="79">
+      <c r="F28" s="76">
         <v>80</v>
       </c>
-      <c r="G28" s="79">
+      <c r="G28" s="76">
         <v>86</v>
       </c>
-      <c r="H28" s="80">
+      <c r="H28" s="77">
         <v>84</v>
       </c>
       <c r="I28" s="58"/>
@@ -16724,22 +16728,22 @@
       <c r="B29" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="81" t="s">
+      <c r="C29" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="79">
-        <v>75</v>
-      </c>
-      <c r="E29" s="79">
+      <c r="D29" s="76">
+        <v>75</v>
+      </c>
+      <c r="E29" s="76">
         <v>91</v>
       </c>
-      <c r="F29" s="79">
-        <v>70</v>
-      </c>
-      <c r="G29" s="79">
+      <c r="F29" s="76">
+        <v>70</v>
+      </c>
+      <c r="G29" s="76">
         <v>86</v>
       </c>
-      <c r="H29" s="80">
+      <c r="H29" s="77">
         <v>81</v>
       </c>
       <c r="I29" s="58"/>
@@ -16751,22 +16755,22 @@
       <c r="B30" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="79">
-        <v>75</v>
-      </c>
-      <c r="E30" s="79">
+      <c r="D30" s="76">
+        <v>75</v>
+      </c>
+      <c r="E30" s="76">
         <v>91</v>
       </c>
-      <c r="F30" s="79">
+      <c r="F30" s="76">
         <v>85</v>
       </c>
-      <c r="G30" s="79">
+      <c r="G30" s="76">
         <v>83</v>
       </c>
-      <c r="H30" s="80">
+      <c r="H30" s="77">
         <v>82</v>
       </c>
       <c r="I30" s="58"/>
@@ -16778,22 +16782,22 @@
       <c r="B31" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C31" s="81" t="s">
+      <c r="C31" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="79">
-        <v>75</v>
-      </c>
-      <c r="E31" s="79">
+      <c r="D31" s="76">
+        <v>75</v>
+      </c>
+      <c r="E31" s="76">
         <v>90</v>
       </c>
-      <c r="F31" s="79">
-        <v>75</v>
-      </c>
-      <c r="G31" s="79">
+      <c r="F31" s="76">
+        <v>75</v>
+      </c>
+      <c r="G31" s="76">
         <v>88</v>
       </c>
-      <c r="H31" s="80">
+      <c r="H31" s="77">
         <v>89</v>
       </c>
       <c r="I31" s="58"/>
@@ -16805,22 +16809,22 @@
       <c r="B32" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="81" t="s">
+      <c r="C32" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="79">
-        <v>75</v>
-      </c>
-      <c r="E32" s="79">
+      <c r="D32" s="76">
+        <v>75</v>
+      </c>
+      <c r="E32" s="76">
         <v>87</v>
       </c>
-      <c r="F32" s="79">
+      <c r="F32" s="76">
         <v>85</v>
       </c>
-      <c r="G32" s="79">
+      <c r="G32" s="76">
         <v>88</v>
       </c>
-      <c r="H32" s="80">
+      <c r="H32" s="77">
         <v>89</v>
       </c>
       <c r="I32" s="58"/>
@@ -16832,22 +16836,22 @@
       <c r="B33" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="79">
-        <v>75</v>
-      </c>
-      <c r="E33" s="79">
+      <c r="D33" s="76">
+        <v>75</v>
+      </c>
+      <c r="E33" s="76">
         <v>90</v>
       </c>
-      <c r="F33" s="79">
-        <v>70</v>
-      </c>
-      <c r="G33" s="79">
+      <c r="F33" s="76">
+        <v>70</v>
+      </c>
+      <c r="G33" s="76">
         <v>83</v>
       </c>
-      <c r="H33" s="80">
+      <c r="H33" s="77">
         <v>82</v>
       </c>
       <c r="I33" s="58"/>
@@ -16859,22 +16863,22 @@
       <c r="B34" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="C34" s="81" t="s">
+      <c r="C34" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="79">
-        <v>75</v>
-      </c>
-      <c r="E34" s="79">
+      <c r="D34" s="76">
+        <v>75</v>
+      </c>
+      <c r="E34" s="76">
         <v>87</v>
       </c>
-      <c r="F34" s="79">
-        <v>75</v>
-      </c>
-      <c r="G34" s="79">
+      <c r="F34" s="76">
+        <v>75</v>
+      </c>
+      <c r="G34" s="76">
         <v>84</v>
       </c>
-      <c r="H34" s="80">
+      <c r="H34" s="77">
         <v>70</v>
       </c>
       <c r="I34" s="58"/>
@@ -16886,22 +16890,22 @@
       <c r="B35" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="76">
         <v>80</v>
       </c>
-      <c r="E35" s="79">
+      <c r="E35" s="76">
         <v>87</v>
       </c>
-      <c r="F35" s="79">
-        <v>70</v>
-      </c>
-      <c r="G35" s="79">
+      <c r="F35" s="76">
+        <v>70</v>
+      </c>
+      <c r="G35" s="76">
         <v>84</v>
       </c>
-      <c r="H35" s="80">
+      <c r="H35" s="77">
         <v>70</v>
       </c>
       <c r="I35" s="58"/>
@@ -16913,22 +16917,22 @@
       <c r="B36" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="C36" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D36" s="79">
-        <v>70</v>
-      </c>
-      <c r="E36" s="79">
+      <c r="D36" s="76">
+        <v>70</v>
+      </c>
+      <c r="E36" s="76">
         <v>91</v>
       </c>
-      <c r="F36" s="79">
+      <c r="F36" s="76">
         <v>80</v>
       </c>
-      <c r="G36" s="79">
+      <c r="G36" s="76">
         <v>83</v>
       </c>
-      <c r="H36" s="80">
+      <c r="H36" s="77">
         <v>82</v>
       </c>
       <c r="I36" s="58"/>
@@ -16940,22 +16944,22 @@
       <c r="B37" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="79">
+      <c r="D37" s="76">
         <v>78</v>
       </c>
-      <c r="E37" s="79">
+      <c r="E37" s="76">
         <v>88</v>
       </c>
-      <c r="F37" s="79">
+      <c r="F37" s="76">
         <v>80</v>
       </c>
-      <c r="G37" s="79">
+      <c r="G37" s="76">
         <v>91</v>
       </c>
-      <c r="H37" s="80">
+      <c r="H37" s="77">
         <v>88</v>
       </c>
       <c r="I37" s="58"/>
@@ -16967,22 +16971,22 @@
       <c r="B38" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C38" s="81" t="s">
+      <c r="C38" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="79">
-        <v>75</v>
-      </c>
-      <c r="E38" s="79">
+      <c r="D38" s="76">
+        <v>75</v>
+      </c>
+      <c r="E38" s="76">
         <v>92</v>
       </c>
-      <c r="F38" s="79">
+      <c r="F38" s="76">
         <v>85</v>
       </c>
-      <c r="G38" s="79">
+      <c r="G38" s="76">
         <v>91</v>
       </c>
-      <c r="H38" s="80">
+      <c r="H38" s="77">
         <v>88</v>
       </c>
       <c r="I38" s="58"/>
@@ -16997,19 +17001,19 @@
       <c r="C39" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="79">
-        <v>75</v>
-      </c>
-      <c r="E39" s="79">
+      <c r="D39" s="76">
+        <v>75</v>
+      </c>
+      <c r="E39" s="76">
         <v>90</v>
       </c>
-      <c r="F39" s="79">
-        <v>70</v>
-      </c>
-      <c r="G39" s="79">
+      <c r="F39" s="76">
+        <v>70</v>
+      </c>
+      <c r="G39" s="76">
         <v>88</v>
       </c>
-      <c r="H39" s="80">
+      <c r="H39" s="77">
         <v>83</v>
       </c>
       <c r="I39" s="58"/>
@@ -17024,19 +17028,19 @@
       <c r="C40" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="79">
-        <v>75</v>
-      </c>
-      <c r="E40" s="79">
+      <c r="D40" s="76">
+        <v>75</v>
+      </c>
+      <c r="E40" s="76">
         <v>90</v>
       </c>
-      <c r="F40" s="79">
-        <v>75</v>
-      </c>
-      <c r="G40" s="79">
+      <c r="F40" s="76">
+        <v>75</v>
+      </c>
+      <c r="G40" s="76">
         <v>86</v>
       </c>
-      <c r="H40" s="80">
+      <c r="H40" s="77">
         <v>84</v>
       </c>
       <c r="I40" s="58"/>
@@ -17051,19 +17055,19 @@
       <c r="C41" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="79">
-        <v>75</v>
-      </c>
-      <c r="E41" s="79">
+      <c r="D41" s="76">
+        <v>75</v>
+      </c>
+      <c r="E41" s="76">
         <v>91</v>
       </c>
-      <c r="F41" s="79">
-        <v>75</v>
-      </c>
-      <c r="G41" s="79">
+      <c r="F41" s="76">
+        <v>75</v>
+      </c>
+      <c r="G41" s="76">
         <v>91</v>
       </c>
-      <c r="H41" s="80">
+      <c r="H41" s="77">
         <v>88</v>
       </c>
       <c r="I41" s="58"/>
@@ -17078,19 +17082,19 @@
       <c r="C42" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="79">
-        <v>75</v>
-      </c>
-      <c r="E42" s="79">
+      <c r="D42" s="76">
+        <v>75</v>
+      </c>
+      <c r="E42" s="76">
         <v>91</v>
       </c>
-      <c r="F42" s="79">
+      <c r="F42" s="76">
         <v>85</v>
       </c>
-      <c r="G42" s="79">
+      <c r="G42" s="76">
         <v>83</v>
       </c>
-      <c r="H42" s="80">
+      <c r="H42" s="77">
         <v>82</v>
       </c>
       <c r="I42" s="58"/>
@@ -17105,19 +17109,19 @@
       <c r="C43" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="79">
+      <c r="D43" s="76">
         <v>85</v>
       </c>
-      <c r="E43" s="79">
+      <c r="E43" s="76">
         <v>90</v>
       </c>
-      <c r="F43" s="79">
+      <c r="F43" s="76">
         <v>65</v>
       </c>
-      <c r="G43" s="79">
+      <c r="G43" s="76">
         <v>88</v>
       </c>
-      <c r="H43" s="80">
+      <c r="H43" s="77">
         <v>89</v>
       </c>
       <c r="I43" s="58"/>
@@ -17132,19 +17136,19 @@
       <c r="C44" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="79">
-        <v>75</v>
-      </c>
-      <c r="E44" s="79">
+      <c r="D44" s="76">
+        <v>75</v>
+      </c>
+      <c r="E44" s="76">
         <v>90</v>
       </c>
-      <c r="F44" s="79">
-        <v>70</v>
-      </c>
-      <c r="G44" s="79">
+      <c r="F44" s="76">
+        <v>70</v>
+      </c>
+      <c r="G44" s="76">
         <v>88</v>
       </c>
-      <c r="H44" s="80">
+      <c r="H44" s="77">
         <v>89</v>
       </c>
       <c r="I44" s="58"/>
@@ -17159,19 +17163,19 @@
       <c r="C45" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D45" s="79">
-        <v>75</v>
-      </c>
-      <c r="E45" s="79">
+      <c r="D45" s="76">
+        <v>75</v>
+      </c>
+      <c r="E45" s="76">
         <v>90</v>
       </c>
-      <c r="F45" s="79">
+      <c r="F45" s="76">
         <v>85</v>
       </c>
-      <c r="G45" s="79">
+      <c r="G45" s="76">
         <v>88</v>
       </c>
-      <c r="H45" s="80">
+      <c r="H45" s="77">
         <v>83</v>
       </c>
       <c r="I45" s="58"/>
@@ -17186,19 +17190,19 @@
       <c r="C46" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="79">
-        <v>75</v>
-      </c>
-      <c r="E46" s="79">
+      <c r="D46" s="76">
+        <v>75</v>
+      </c>
+      <c r="E46" s="76">
         <v>88</v>
       </c>
-      <c r="F46" s="79">
+      <c r="F46" s="76">
         <v>85</v>
       </c>
-      <c r="G46" s="79">
+      <c r="G46" s="76">
         <v>90</v>
       </c>
-      <c r="H46" s="80">
+      <c r="H46" s="77">
         <v>85</v>
       </c>
       <c r="I46" s="58"/>
@@ -17213,19 +17217,19 @@
       <c r="C47" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="79">
-        <v>75</v>
-      </c>
-      <c r="E47" s="79">
+      <c r="D47" s="76">
+        <v>75</v>
+      </c>
+      <c r="E47" s="76">
         <v>90</v>
       </c>
-      <c r="F47" s="79">
+      <c r="F47" s="76">
         <v>80</v>
       </c>
-      <c r="G47" s="79">
+      <c r="G47" s="76">
         <v>88</v>
       </c>
-      <c r="H47" s="80">
+      <c r="H47" s="77">
         <v>83</v>
       </c>
       <c r="I47" s="58"/>
@@ -17240,19 +17244,19 @@
       <c r="C48" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="79">
-        <v>70</v>
-      </c>
-      <c r="E48" s="79">
+      <c r="D48" s="76">
+        <v>70</v>
+      </c>
+      <c r="E48" s="76">
         <v>90</v>
       </c>
-      <c r="F48" s="79">
-        <v>75</v>
-      </c>
-      <c r="G48" s="79">
+      <c r="F48" s="76">
+        <v>75</v>
+      </c>
+      <c r="G48" s="76">
         <v>88</v>
       </c>
-      <c r="H48" s="80">
+      <c r="H48" s="77">
         <v>89</v>
       </c>
       <c r="I48" s="58"/>
@@ -17267,19 +17271,19 @@
       <c r="C49" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="79">
+      <c r="D49" s="76">
         <v>78</v>
       </c>
-      <c r="E49" s="79">
+      <c r="E49" s="76">
         <v>92</v>
       </c>
-      <c r="F49" s="79">
+      <c r="F49" s="76">
         <v>80</v>
       </c>
-      <c r="G49" s="79">
+      <c r="G49" s="76">
         <v>88</v>
       </c>
-      <c r="H49" s="80">
+      <c r="H49" s="77">
         <v>89</v>
       </c>
       <c r="I49" s="58"/>
@@ -17294,19 +17298,19 @@
       <c r="C50" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="79">
-        <v>70</v>
-      </c>
-      <c r="E50" s="79">
+      <c r="D50" s="76">
+        <v>70</v>
+      </c>
+      <c r="E50" s="76">
         <v>91</v>
       </c>
-      <c r="F50" s="79">
+      <c r="F50" s="76">
         <v>80</v>
       </c>
-      <c r="G50" s="79">
+      <c r="G50" s="76">
         <v>84</v>
       </c>
-      <c r="H50" s="80">
+      <c r="H50" s="77">
         <v>70</v>
       </c>
       <c r="I50" s="58"/>
@@ -17321,19 +17325,19 @@
       <c r="C51" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="79">
-        <v>75</v>
-      </c>
-      <c r="E51" s="79">
+      <c r="D51" s="76">
+        <v>75</v>
+      </c>
+      <c r="E51" s="76">
         <v>90</v>
       </c>
-      <c r="F51" s="79">
-        <v>70</v>
-      </c>
-      <c r="G51" s="79">
+      <c r="F51" s="76">
+        <v>70</v>
+      </c>
+      <c r="G51" s="76">
         <v>89</v>
       </c>
-      <c r="H51" s="80">
+      <c r="H51" s="77">
         <v>71</v>
       </c>
       <c r="I51" s="58"/>
@@ -17345,22 +17349,22 @@
       <c r="B52" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="79">
+      <c r="D52" s="76">
         <v>85</v>
       </c>
-      <c r="E52" s="79">
+      <c r="E52" s="76">
         <v>89</v>
       </c>
-      <c r="F52" s="79">
+      <c r="F52" s="76">
         <v>65</v>
       </c>
-      <c r="G52" s="79">
+      <c r="G52" s="76">
         <v>90</v>
       </c>
-      <c r="H52" s="80">
+      <c r="H52" s="77">
         <v>85</v>
       </c>
       <c r="I52" s="58"/>
@@ -17372,22 +17376,22 @@
       <c r="B53" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="79">
-        <v>75</v>
-      </c>
-      <c r="E53" s="79">
+      <c r="D53" s="76">
+        <v>75</v>
+      </c>
+      <c r="E53" s="76">
         <v>92</v>
       </c>
-      <c r="F53" s="79">
-        <v>70</v>
-      </c>
-      <c r="G53" s="79">
+      <c r="F53" s="76">
+        <v>70</v>
+      </c>
+      <c r="G53" s="76">
         <v>86</v>
       </c>
-      <c r="H53" s="80">
+      <c r="H53" s="77">
         <v>81</v>
       </c>
       <c r="I53" s="58"/>
@@ -17399,22 +17403,22 @@
       <c r="B54" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C54" s="81" t="s">
+      <c r="C54" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="D54" s="79">
-        <v>70</v>
-      </c>
-      <c r="E54" s="79">
+      <c r="D54" s="76">
+        <v>70</v>
+      </c>
+      <c r="E54" s="76">
         <v>90</v>
       </c>
-      <c r="F54" s="79">
-        <v>75</v>
-      </c>
-      <c r="G54" s="79">
+      <c r="F54" s="76">
+        <v>75</v>
+      </c>
+      <c r="G54" s="76">
         <v>88</v>
       </c>
-      <c r="H54" s="80">
+      <c r="H54" s="77">
         <v>83</v>
       </c>
       <c r="I54" s="58"/>
@@ -17426,22 +17430,22 @@
       <c r="B55" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C55" s="81" t="s">
+      <c r="C55" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="D55" s="79">
-        <v>70</v>
-      </c>
-      <c r="E55" s="79">
+      <c r="D55" s="76">
+        <v>70</v>
+      </c>
+      <c r="E55" s="76">
         <v>88</v>
       </c>
-      <c r="F55" s="79">
+      <c r="F55" s="76">
         <v>80</v>
       </c>
-      <c r="G55" s="79">
+      <c r="G55" s="76">
         <v>89</v>
       </c>
-      <c r="H55" s="80">
+      <c r="H55" s="77">
         <v>71</v>
       </c>
       <c r="I55" s="58"/>
@@ -17453,22 +17457,22 @@
       <c r="B56" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="C56" s="81" t="s">
+      <c r="C56" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="D56" s="79">
-        <v>70</v>
-      </c>
-      <c r="E56" s="79">
+      <c r="D56" s="76">
+        <v>70</v>
+      </c>
+      <c r="E56" s="76">
         <v>91</v>
       </c>
-      <c r="F56" s="79">
+      <c r="F56" s="76">
         <v>80</v>
       </c>
-      <c r="G56" s="79">
+      <c r="G56" s="76">
         <v>89</v>
       </c>
-      <c r="H56" s="80">
+      <c r="H56" s="77">
         <v>71</v>
       </c>
       <c r="I56" s="58"/>
@@ -17480,22 +17484,22 @@
       <c r="B57" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C57" s="81" t="s">
+      <c r="C57" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="79">
-        <v>75</v>
-      </c>
-      <c r="E57" s="79">
+      <c r="D57" s="76">
+        <v>75</v>
+      </c>
+      <c r="E57" s="76">
         <v>90</v>
       </c>
-      <c r="F57" s="79">
+      <c r="F57" s="76">
         <v>85</v>
       </c>
-      <c r="G57" s="79">
+      <c r="G57" s="76">
         <v>89</v>
       </c>
-      <c r="H57" s="80">
+      <c r="H57" s="77">
         <v>71</v>
       </c>
       <c r="I57" s="58"/>
@@ -17507,22 +17511,22 @@
       <c r="B58" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="C58" s="81" t="s">
+      <c r="C58" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D58" s="79">
-        <v>75</v>
-      </c>
-      <c r="E58" s="79">
+      <c r="D58" s="76">
+        <v>75</v>
+      </c>
+      <c r="E58" s="76">
         <v>90</v>
       </c>
-      <c r="F58" s="79">
+      <c r="F58" s="76">
         <v>80</v>
       </c>
-      <c r="G58" s="79">
+      <c r="G58" s="76">
         <v>90</v>
       </c>
-      <c r="H58" s="80">
+      <c r="H58" s="77">
         <v>85</v>
       </c>
       <c r="I58" s="58"/>
@@ -17534,22 +17538,22 @@
       <c r="B59" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="C59" s="81" t="s">
+      <c r="C59" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="D59" s="79">
-        <v>75</v>
-      </c>
-      <c r="E59" s="79">
+      <c r="D59" s="76">
+        <v>75</v>
+      </c>
+      <c r="E59" s="76">
         <v>91</v>
       </c>
-      <c r="F59" s="79">
-        <v>75</v>
-      </c>
-      <c r="G59" s="79">
+      <c r="F59" s="76">
+        <v>75</v>
+      </c>
+      <c r="G59" s="76">
         <v>91</v>
       </c>
-      <c r="H59" s="80">
+      <c r="H59" s="77">
         <v>88</v>
       </c>
       <c r="I59" s="58"/>
@@ -17561,22 +17565,22 @@
       <c r="B60" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C60" s="81" t="s">
+      <c r="C60" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="D60" s="79">
-        <v>70</v>
-      </c>
-      <c r="E60" s="79">
+      <c r="D60" s="76">
+        <v>70</v>
+      </c>
+      <c r="E60" s="76">
         <v>92</v>
       </c>
-      <c r="F60" s="79">
+      <c r="F60" s="76">
         <v>80</v>
       </c>
-      <c r="G60" s="79">
+      <c r="G60" s="76">
         <v>90</v>
       </c>
-      <c r="H60" s="80">
+      <c r="H60" s="77">
         <v>85</v>
       </c>
       <c r="I60" s="58"/>
@@ -17591,19 +17595,19 @@
       <c r="C61" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D61" s="79">
-        <v>75</v>
-      </c>
-      <c r="E61" s="79">
+      <c r="D61" s="76">
+        <v>75</v>
+      </c>
+      <c r="E61" s="76">
         <v>92</v>
       </c>
-      <c r="F61" s="79">
+      <c r="F61" s="76">
         <v>85</v>
       </c>
-      <c r="G61" s="79">
+      <c r="G61" s="76">
         <v>83</v>
       </c>
-      <c r="H61" s="80">
+      <c r="H61" s="77">
         <v>82</v>
       </c>
       <c r="I61" s="58"/>
@@ -17618,19 +17622,19 @@
       <c r="C62" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D62" s="79">
+      <c r="D62" s="76">
         <v>78</v>
       </c>
-      <c r="E62" s="79">
+      <c r="E62" s="76">
         <v>90</v>
       </c>
-      <c r="F62" s="79">
+      <c r="F62" s="76">
         <v>80</v>
       </c>
-      <c r="G62" s="79">
+      <c r="G62" s="76">
         <v>89</v>
       </c>
-      <c r="H62" s="80">
+      <c r="H62" s="77">
         <v>71</v>
       </c>
       <c r="I62" s="58"/>
@@ -17645,19 +17649,19 @@
       <c r="C63" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D63" s="79">
-        <v>70</v>
-      </c>
-      <c r="E63" s="79">
+      <c r="D63" s="76">
+        <v>70</v>
+      </c>
+      <c r="E63" s="76">
         <v>88</v>
       </c>
-      <c r="F63" s="79">
+      <c r="F63" s="76">
         <v>80</v>
       </c>
-      <c r="G63" s="79">
+      <c r="G63" s="76">
         <v>86</v>
       </c>
-      <c r="H63" s="80">
+      <c r="H63" s="77">
         <v>70</v>
       </c>
       <c r="I63" s="58"/>
@@ -17672,19 +17676,19 @@
       <c r="C64" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="79">
-        <v>70</v>
-      </c>
-      <c r="E64" s="79">
+      <c r="D64" s="76">
+        <v>70</v>
+      </c>
+      <c r="E64" s="76">
         <v>92</v>
       </c>
-      <c r="F64" s="79">
-        <v>75</v>
-      </c>
-      <c r="G64" s="79">
+      <c r="F64" s="76">
+        <v>75</v>
+      </c>
+      <c r="G64" s="76">
         <v>83</v>
       </c>
-      <c r="H64" s="80">
+      <c r="H64" s="77">
         <v>82</v>
       </c>
       <c r="I64" s="58"/>
@@ -17699,19 +17703,19 @@
       <c r="C65" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D65" s="79">
-        <v>75</v>
-      </c>
-      <c r="E65" s="79">
+      <c r="D65" s="76">
+        <v>75</v>
+      </c>
+      <c r="E65" s="76">
         <v>90</v>
       </c>
-      <c r="F65" s="79">
+      <c r="F65" s="76">
         <v>85</v>
       </c>
-      <c r="G65" s="79">
+      <c r="G65" s="76">
         <v>89</v>
       </c>
-      <c r="H65" s="80">
+      <c r="H65" s="77">
         <v>71</v>
       </c>
       <c r="I65" s="58"/>
@@ -17726,19 +17730,19 @@
       <c r="C66" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D66" s="79">
-        <v>70</v>
-      </c>
-      <c r="E66" s="79">
+      <c r="D66" s="76">
+        <v>70</v>
+      </c>
+      <c r="E66" s="76">
         <v>83</v>
       </c>
-      <c r="F66" s="79">
-        <v>75</v>
-      </c>
-      <c r="G66" s="79">
+      <c r="F66" s="76">
+        <v>75</v>
+      </c>
+      <c r="G66" s="76">
         <v>86</v>
       </c>
-      <c r="H66" s="80">
+      <c r="H66" s="77">
         <v>70</v>
       </c>
       <c r="I66" s="58"/>
@@ -17753,19 +17757,19 @@
       <c r="C67" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D67" s="79">
+      <c r="D67" s="76">
         <v>78</v>
       </c>
-      <c r="E67" s="79">
+      <c r="E67" s="76">
         <v>90</v>
       </c>
-      <c r="F67" s="79">
+      <c r="F67" s="76">
         <v>80</v>
       </c>
-      <c r="G67" s="79">
+      <c r="G67" s="76">
         <v>84</v>
       </c>
-      <c r="H67" s="80">
+      <c r="H67" s="77">
         <v>70</v>
       </c>
       <c r="I67" s="58"/>
@@ -17780,19 +17784,19 @@
       <c r="C68" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D68" s="79">
-        <v>75</v>
-      </c>
-      <c r="E68" s="79">
+      <c r="D68" s="76">
+        <v>75</v>
+      </c>
+      <c r="E68" s="76">
         <v>90</v>
       </c>
-      <c r="F68" s="79">
+      <c r="F68" s="76">
         <v>85</v>
       </c>
-      <c r="G68" s="79">
+      <c r="G68" s="76">
         <v>86</v>
       </c>
-      <c r="H68" s="80">
+      <c r="H68" s="77">
         <v>81</v>
       </c>
       <c r="I68" s="58"/>
@@ -17807,19 +17811,19 @@
       <c r="C69" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D69" s="79">
-        <v>70</v>
-      </c>
-      <c r="E69" s="79">
+      <c r="D69" s="76">
+        <v>70</v>
+      </c>
+      <c r="E69" s="76">
         <v>90</v>
       </c>
-      <c r="F69" s="79">
-        <v>75</v>
-      </c>
-      <c r="G69" s="79">
+      <c r="F69" s="76">
+        <v>75</v>
+      </c>
+      <c r="G69" s="76">
         <v>88</v>
       </c>
-      <c r="H69" s="80">
+      <c r="H69" s="77">
         <v>89</v>
       </c>
       <c r="I69" s="58"/>
@@ -17834,19 +17838,19 @@
       <c r="C70" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D70" s="79">
-        <v>75</v>
-      </c>
-      <c r="E70" s="79">
+      <c r="D70" s="76">
+        <v>75</v>
+      </c>
+      <c r="E70" s="76">
         <v>92</v>
       </c>
-      <c r="F70" s="79">
-        <v>75</v>
-      </c>
-      <c r="G70" s="79">
+      <c r="F70" s="76">
+        <v>75</v>
+      </c>
+      <c r="G70" s="76">
         <v>84</v>
       </c>
-      <c r="H70" s="80">
+      <c r="H70" s="77">
         <v>70</v>
       </c>
       <c r="I70" s="58"/>
@@ -17861,19 +17865,19 @@
       <c r="C71" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D71" s="79">
-        <v>75</v>
-      </c>
-      <c r="E71" s="79">
+      <c r="D71" s="76">
+        <v>75</v>
+      </c>
+      <c r="E71" s="76">
         <v>89</v>
       </c>
-      <c r="F71" s="79">
-        <v>70</v>
-      </c>
-      <c r="G71" s="79">
+      <c r="F71" s="76">
+        <v>70</v>
+      </c>
+      <c r="G71" s="76">
         <v>90</v>
       </c>
-      <c r="H71" s="80">
+      <c r="H71" s="77">
         <v>85</v>
       </c>
       <c r="I71" s="58"/>
@@ -17888,19 +17892,19 @@
       <c r="C72" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D72" s="79">
-        <v>75</v>
-      </c>
-      <c r="E72" s="79">
+      <c r="D72" s="76">
+        <v>75</v>
+      </c>
+      <c r="E72" s="76">
         <v>83</v>
       </c>
-      <c r="F72" s="79">
-        <v>70</v>
-      </c>
-      <c r="G72" s="79">
+      <c r="F72" s="76">
+        <v>70</v>
+      </c>
+      <c r="G72" s="76">
         <v>91</v>
       </c>
-      <c r="H72" s="80">
+      <c r="H72" s="77">
         <v>88</v>
       </c>
       <c r="I72" s="58"/>
@@ -17915,19 +17919,19 @@
       <c r="C73" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D73" s="79">
+      <c r="D73" s="76">
         <v>80</v>
       </c>
-      <c r="E73" s="79">
+      <c r="E73" s="76">
         <v>90</v>
       </c>
-      <c r="F73" s="79">
-        <v>70</v>
-      </c>
-      <c r="G73" s="79">
+      <c r="F73" s="76">
+        <v>70</v>
+      </c>
+      <c r="G73" s="76">
         <v>88</v>
       </c>
-      <c r="H73" s="80">
+      <c r="H73" s="77">
         <v>89</v>
       </c>
       <c r="I73" s="58"/>
@@ -17942,19 +17946,19 @@
       <c r="C74" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D74" s="79">
-        <v>75</v>
-      </c>
-      <c r="E74" s="79">
+      <c r="D74" s="76">
+        <v>75</v>
+      </c>
+      <c r="E74" s="76">
         <v>83</v>
       </c>
-      <c r="F74" s="79">
-        <v>70</v>
-      </c>
-      <c r="G74" s="79">
+      <c r="F74" s="76">
+        <v>70</v>
+      </c>
+      <c r="G74" s="76">
         <v>90</v>
       </c>
-      <c r="H74" s="80">
+      <c r="H74" s="77">
         <v>85</v>
       </c>
       <c r="I74" s="58"/>
@@ -17969,19 +17973,19 @@
       <c r="C75" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D75" s="79">
+      <c r="D75" s="76">
         <v>78</v>
       </c>
-      <c r="E75" s="79">
+      <c r="E75" s="76">
         <v>92</v>
       </c>
-      <c r="F75" s="79">
+      <c r="F75" s="76">
         <v>80</v>
       </c>
-      <c r="G75" s="79">
+      <c r="G75" s="76">
         <v>84</v>
       </c>
-      <c r="H75" s="80">
+      <c r="H75" s="77">
         <v>70</v>
       </c>
       <c r="I75" s="58"/>
@@ -17996,19 +18000,19 @@
       <c r="C76" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D76" s="79">
-        <v>75</v>
-      </c>
-      <c r="E76" s="79">
+      <c r="D76" s="76">
+        <v>75</v>
+      </c>
+      <c r="E76" s="76">
         <v>88</v>
       </c>
-      <c r="F76" s="79">
-        <v>70</v>
-      </c>
-      <c r="G76" s="79">
+      <c r="F76" s="76">
+        <v>70</v>
+      </c>
+      <c r="G76" s="76">
         <v>91</v>
       </c>
-      <c r="H76" s="80">
+      <c r="H76" s="77">
         <v>88</v>
       </c>
       <c r="I76" s="58"/>
@@ -18023,19 +18027,19 @@
       <c r="C77" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="D77" s="79">
-        <v>70</v>
-      </c>
-      <c r="E77" s="79">
+      <c r="D77" s="76">
+        <v>70</v>
+      </c>
+      <c r="E77" s="76">
         <v>92</v>
       </c>
-      <c r="F77" s="79">
-        <v>75</v>
-      </c>
-      <c r="G77" s="79">
+      <c r="F77" s="76">
+        <v>75</v>
+      </c>
+      <c r="G77" s="76">
         <v>86</v>
       </c>
-      <c r="H77" s="80">
+      <c r="H77" s="77">
         <v>81</v>
       </c>
       <c r="I77" s="58"/>
@@ -18047,22 +18051,22 @@
       <c r="B78" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="C78" s="81" t="s">
+      <c r="C78" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="D78" s="79">
+      <c r="D78" s="76">
         <v>85</v>
       </c>
-      <c r="E78" s="79">
+      <c r="E78" s="76">
         <v>92</v>
       </c>
-      <c r="F78" s="79">
+      <c r="F78" s="76">
         <v>65</v>
       </c>
-      <c r="G78" s="79">
+      <c r="G78" s="76">
         <v>88</v>
       </c>
-      <c r="H78" s="80">
+      <c r="H78" s="77">
         <v>89</v>
       </c>
       <c r="I78" s="58"/>
@@ -18074,22 +18078,22 @@
       <c r="B79" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C79" s="81" t="s">
+      <c r="C79" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="D79" s="79">
-        <v>75</v>
-      </c>
-      <c r="E79" s="79">
+      <c r="D79" s="76">
+        <v>75</v>
+      </c>
+      <c r="E79" s="76">
         <v>91</v>
       </c>
-      <c r="F79" s="79">
-        <v>75</v>
-      </c>
-      <c r="G79" s="79">
+      <c r="F79" s="76">
+        <v>75</v>
+      </c>
+      <c r="G79" s="76">
         <v>86</v>
       </c>
-      <c r="H79" s="80">
+      <c r="H79" s="77">
         <v>81</v>
       </c>
       <c r="I79" s="58"/>
@@ -18101,22 +18105,22 @@
       <c r="B80" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="C80" s="81" t="s">
+      <c r="C80" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="D80" s="79">
-        <v>75</v>
-      </c>
-      <c r="E80" s="79">
+      <c r="D80" s="76">
+        <v>75</v>
+      </c>
+      <c r="E80" s="76">
         <v>90</v>
       </c>
-      <c r="F80" s="79">
-        <v>75</v>
-      </c>
-      <c r="G80" s="79">
+      <c r="F80" s="76">
+        <v>75</v>
+      </c>
+      <c r="G80" s="76">
         <v>83</v>
       </c>
-      <c r="H80" s="80">
+      <c r="H80" s="77">
         <v>82</v>
       </c>
       <c r="I80" s="58"/>
@@ -18128,22 +18132,22 @@
       <c r="B81" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="C81" s="81" t="s">
+      <c r="C81" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="D81" s="79">
-        <v>75</v>
-      </c>
-      <c r="E81" s="79">
+      <c r="D81" s="76">
+        <v>75</v>
+      </c>
+      <c r="E81" s="76">
         <v>91</v>
       </c>
-      <c r="F81" s="79">
+      <c r="F81" s="76">
         <v>80</v>
       </c>
-      <c r="G81" s="79">
+      <c r="G81" s="76">
         <v>84</v>
       </c>
-      <c r="H81" s="80">
+      <c r="H81" s="77">
         <v>70</v>
       </c>
       <c r="I81" s="58"/>
@@ -18155,22 +18159,22 @@
       <c r="B82" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C82" s="81" t="s">
+      <c r="C82" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="D82" s="79">
-        <v>75</v>
-      </c>
-      <c r="E82" s="79">
+      <c r="D82" s="76">
+        <v>75</v>
+      </c>
+      <c r="E82" s="76">
         <v>83</v>
       </c>
-      <c r="F82" s="79">
+      <c r="F82" s="76">
         <v>80</v>
       </c>
-      <c r="G82" s="79">
+      <c r="G82" s="76">
         <v>86</v>
       </c>
-      <c r="H82" s="80">
+      <c r="H82" s="77">
         <v>70</v>
       </c>
       <c r="I82" s="58"/>
@@ -18182,22 +18186,22 @@
       <c r="B83" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="C83" s="81" t="s">
+      <c r="C83" s="78" t="s">
         <v>91</v>
       </c>
-      <c r="D83" s="79">
-        <v>75</v>
-      </c>
-      <c r="E83" s="79">
+      <c r="D83" s="76">
+        <v>75</v>
+      </c>
+      <c r="E83" s="76">
         <v>92</v>
       </c>
-      <c r="F83" s="79">
+      <c r="F83" s="76">
         <v>85</v>
       </c>
-      <c r="G83" s="79">
+      <c r="G83" s="76">
         <v>88</v>
       </c>
-      <c r="H83" s="80">
+      <c r="H83" s="77">
         <v>89</v>
       </c>
       <c r="I83" s="58"/>
@@ -18209,22 +18213,22 @@
       <c r="B84" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="C84" s="81" t="s">
+      <c r="C84" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="D84" s="79">
-        <v>75</v>
-      </c>
-      <c r="E84" s="79">
+      <c r="D84" s="76">
+        <v>75</v>
+      </c>
+      <c r="E84" s="76">
         <v>90</v>
       </c>
-      <c r="F84" s="79">
+      <c r="F84" s="76">
         <v>85</v>
       </c>
-      <c r="G84" s="79">
+      <c r="G84" s="76">
         <v>88</v>
       </c>
-      <c r="H84" s="80">
+      <c r="H84" s="77">
         <v>83</v>
       </c>
       <c r="I84" s="58"/>
@@ -18236,22 +18240,22 @@
       <c r="B85" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="81" t="s">
+      <c r="C85" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="D85" s="79">
-        <v>75</v>
-      </c>
-      <c r="E85" s="79">
+      <c r="D85" s="76">
+        <v>75</v>
+      </c>
+      <c r="E85" s="76">
         <v>90</v>
       </c>
-      <c r="F85" s="79">
-        <v>75</v>
-      </c>
-      <c r="G85" s="79">
+      <c r="F85" s="76">
+        <v>75</v>
+      </c>
+      <c r="G85" s="76">
         <v>91</v>
       </c>
-      <c r="H85" s="80">
+      <c r="H85" s="77">
         <v>88</v>
       </c>
       <c r="I85" s="58"/>
@@ -18266,19 +18270,19 @@
       <c r="C86" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D86" s="79">
+      <c r="D86" s="76">
         <v>80</v>
       </c>
-      <c r="E86" s="79">
+      <c r="E86" s="76">
         <v>89</v>
       </c>
-      <c r="F86" s="79">
-        <v>70</v>
-      </c>
-      <c r="G86" s="79">
+      <c r="F86" s="76">
+        <v>70</v>
+      </c>
+      <c r="G86" s="76">
         <v>90</v>
       </c>
-      <c r="H86" s="80">
+      <c r="H86" s="77">
         <v>85</v>
       </c>
       <c r="I86" s="58"/>
@@ -18293,19 +18297,19 @@
       <c r="C87" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D87" s="79">
+      <c r="D87" s="76">
         <v>85</v>
       </c>
-      <c r="E87" s="79">
+      <c r="E87" s="76">
         <v>90</v>
       </c>
-      <c r="F87" s="79">
+      <c r="F87" s="76">
         <v>65</v>
       </c>
-      <c r="G87" s="79">
+      <c r="G87" s="76">
         <v>91</v>
       </c>
-      <c r="H87" s="80">
+      <c r="H87" s="77">
         <v>88</v>
       </c>
       <c r="I87" s="58"/>
@@ -18320,19 +18324,19 @@
       <c r="C88" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D88" s="79">
-        <v>70</v>
-      </c>
-      <c r="E88" s="79">
+      <c r="D88" s="76">
+        <v>70</v>
+      </c>
+      <c r="E88" s="76">
         <v>90</v>
       </c>
-      <c r="F88" s="79">
-        <v>75</v>
-      </c>
-      <c r="G88" s="79">
+      <c r="F88" s="76">
+        <v>75</v>
+      </c>
+      <c r="G88" s="76">
         <v>86</v>
       </c>
-      <c r="H88" s="80">
+      <c r="H88" s="77">
         <v>70</v>
       </c>
       <c r="I88" s="58"/>
@@ -18347,19 +18351,19 @@
       <c r="C89" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D89" s="79">
+      <c r="D89" s="76">
         <v>80</v>
       </c>
-      <c r="E89" s="79">
+      <c r="E89" s="76">
         <v>90</v>
       </c>
-      <c r="F89" s="79">
-        <v>70</v>
-      </c>
-      <c r="G89" s="79">
+      <c r="F89" s="76">
+        <v>70</v>
+      </c>
+      <c r="G89" s="76">
         <v>86</v>
       </c>
-      <c r="H89" s="80">
+      <c r="H89" s="77">
         <v>84</v>
       </c>
       <c r="I89" s="58"/>
@@ -18374,19 +18378,19 @@
       <c r="C90" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D90" s="79">
-        <v>70</v>
-      </c>
-      <c r="E90" s="79">
+      <c r="D90" s="76">
+        <v>70</v>
+      </c>
+      <c r="E90" s="76">
         <v>90</v>
       </c>
-      <c r="F90" s="79">
+      <c r="F90" s="76">
         <v>80</v>
       </c>
-      <c r="G90" s="79">
+      <c r="G90" s="76">
         <v>86</v>
       </c>
-      <c r="H90" s="80">
+      <c r="H90" s="77">
         <v>84</v>
       </c>
       <c r="I90" s="58"/>
@@ -18401,19 +18405,19 @@
       <c r="C91" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D91" s="79">
-        <v>75</v>
-      </c>
-      <c r="E91" s="79">
+      <c r="D91" s="76">
+        <v>75</v>
+      </c>
+      <c r="E91" s="76">
         <v>90</v>
       </c>
-      <c r="F91" s="79">
-        <v>75</v>
-      </c>
-      <c r="G91" s="79">
+      <c r="F91" s="76">
+        <v>75</v>
+      </c>
+      <c r="G91" s="76">
         <v>84</v>
       </c>
-      <c r="H91" s="80">
+      <c r="H91" s="77">
         <v>70</v>
       </c>
       <c r="I91" s="58"/>
@@ -18428,19 +18432,19 @@
       <c r="C92" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D92" s="79">
+      <c r="D92" s="76">
         <v>80</v>
       </c>
-      <c r="E92" s="79">
+      <c r="E92" s="76">
         <v>92</v>
       </c>
-      <c r="F92" s="79">
-        <v>70</v>
-      </c>
-      <c r="G92" s="79">
+      <c r="F92" s="76">
+        <v>70</v>
+      </c>
+      <c r="G92" s="76">
         <v>86</v>
       </c>
-      <c r="H92" s="80">
+      <c r="H92" s="77">
         <v>81</v>
       </c>
       <c r="I92" s="58"/>
@@ -18455,19 +18459,19 @@
       <c r="C93" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D93" s="79">
-        <v>75</v>
-      </c>
-      <c r="E93" s="79">
+      <c r="D93" s="76">
+        <v>75</v>
+      </c>
+      <c r="E93" s="76">
         <v>88</v>
       </c>
-      <c r="F93" s="79">
-        <v>70</v>
-      </c>
-      <c r="G93" s="79">
+      <c r="F93" s="76">
+        <v>70</v>
+      </c>
+      <c r="G93" s="76">
         <v>89</v>
       </c>
-      <c r="H93" s="80">
+      <c r="H93" s="77">
         <v>71</v>
       </c>
       <c r="I93" s="58"/>
@@ -18482,19 +18486,19 @@
       <c r="C94" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D94" s="79">
+      <c r="D94" s="76">
         <v>85</v>
       </c>
-      <c r="E94" s="79">
+      <c r="E94" s="76">
         <v>90</v>
       </c>
-      <c r="F94" s="79">
+      <c r="F94" s="76">
         <v>65</v>
       </c>
-      <c r="G94" s="79">
+      <c r="G94" s="76">
         <v>88</v>
       </c>
-      <c r="H94" s="80">
+      <c r="H94" s="77">
         <v>89</v>
       </c>
       <c r="I94" s="58"/>
@@ -18509,19 +18513,19 @@
       <c r="C95" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D95" s="79">
-        <v>75</v>
-      </c>
-      <c r="E95" s="79">
+      <c r="D95" s="76">
+        <v>75</v>
+      </c>
+      <c r="E95" s="76">
         <v>91</v>
       </c>
-      <c r="F95" s="79">
-        <v>75</v>
-      </c>
-      <c r="G95" s="79">
+      <c r="F95" s="76">
+        <v>75</v>
+      </c>
+      <c r="G95" s="76">
         <v>84</v>
       </c>
-      <c r="H95" s="80">
+      <c r="H95" s="77">
         <v>70</v>
       </c>
       <c r="I95" s="58"/>
@@ -18536,19 +18540,19 @@
       <c r="C96" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D96" s="79">
-        <v>75</v>
-      </c>
-      <c r="E96" s="79">
+      <c r="D96" s="76">
+        <v>75</v>
+      </c>
+      <c r="E96" s="76">
         <v>90</v>
       </c>
-      <c r="F96" s="79">
-        <v>75</v>
-      </c>
-      <c r="G96" s="79">
+      <c r="F96" s="76">
+        <v>75</v>
+      </c>
+      <c r="G96" s="76">
         <v>89</v>
       </c>
-      <c r="H96" s="80">
+      <c r="H96" s="77">
         <v>71</v>
       </c>
       <c r="I96" s="58"/>
@@ -18563,19 +18567,19 @@
       <c r="C97" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D97" s="79">
-        <v>70</v>
-      </c>
-      <c r="E97" s="79">
+      <c r="D97" s="76">
+        <v>70</v>
+      </c>
+      <c r="E97" s="76">
         <v>89</v>
       </c>
-      <c r="F97" s="79">
-        <v>75</v>
-      </c>
-      <c r="G97" s="79">
+      <c r="F97" s="76">
+        <v>75</v>
+      </c>
+      <c r="G97" s="76">
         <v>86</v>
       </c>
-      <c r="H97" s="80">
+      <c r="H97" s="77">
         <v>81</v>
       </c>
       <c r="I97" s="58"/>
@@ -18590,19 +18594,19 @@
       <c r="C98" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D98" s="79">
-        <v>70</v>
-      </c>
-      <c r="E98" s="79">
+      <c r="D98" s="76">
+        <v>70</v>
+      </c>
+      <c r="E98" s="76">
         <v>88</v>
       </c>
-      <c r="F98" s="79">
-        <v>75</v>
-      </c>
-      <c r="G98" s="79">
+      <c r="F98" s="76">
+        <v>75</v>
+      </c>
+      <c r="G98" s="76">
         <v>86</v>
       </c>
-      <c r="H98" s="80">
+      <c r="H98" s="77">
         <v>70</v>
       </c>
       <c r="I98" s="58"/>
@@ -18617,19 +18621,19 @@
       <c r="C99" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D99" s="79">
-        <v>75</v>
-      </c>
-      <c r="E99" s="79">
+      <c r="D99" s="76">
+        <v>75</v>
+      </c>
+      <c r="E99" s="76">
         <v>88</v>
       </c>
-      <c r="F99" s="79">
-        <v>75</v>
-      </c>
-      <c r="G99" s="79">
+      <c r="F99" s="76">
+        <v>75</v>
+      </c>
+      <c r="G99" s="76">
         <v>86</v>
       </c>
-      <c r="H99" s="80">
+      <c r="H99" s="77">
         <v>70</v>
       </c>
       <c r="I99" s="58"/>
@@ -18641,22 +18645,22 @@
       <c r="B100" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="C100" s="81" t="s">
+      <c r="C100" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="D100" s="79">
-        <v>75</v>
-      </c>
-      <c r="E100" s="79">
+      <c r="D100" s="76">
+        <v>75</v>
+      </c>
+      <c r="E100" s="76">
         <v>83</v>
       </c>
-      <c r="F100" s="79">
-        <v>75</v>
-      </c>
-      <c r="G100" s="79">
+      <c r="F100" s="76">
+        <v>75</v>
+      </c>
+      <c r="G100" s="76">
         <v>86</v>
       </c>
-      <c r="H100" s="80">
+      <c r="H100" s="77">
         <v>70</v>
       </c>
       <c r="I100" s="58"/>
@@ -18668,22 +18672,22 @@
       <c r="B101" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="C101" s="81" t="s">
+      <c r="C101" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="D101" s="79">
-        <v>75</v>
-      </c>
-      <c r="E101" s="79">
+      <c r="D101" s="76">
+        <v>75</v>
+      </c>
+      <c r="E101" s="76">
         <v>90</v>
       </c>
-      <c r="F101" s="79">
-        <v>70</v>
-      </c>
-      <c r="G101" s="79">
+      <c r="F101" s="76">
+        <v>70</v>
+      </c>
+      <c r="G101" s="76">
         <v>86</v>
       </c>
-      <c r="H101" s="80">
+      <c r="H101" s="77">
         <v>84</v>
       </c>
       <c r="I101" s="58"/>
@@ -18695,22 +18699,22 @@
       <c r="B102" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C102" s="81" t="s">
+      <c r="C102" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="D102" s="79">
-        <v>75</v>
-      </c>
-      <c r="E102" s="79">
+      <c r="D102" s="76">
+        <v>75</v>
+      </c>
+      <c r="E102" s="76">
         <v>90</v>
       </c>
-      <c r="F102" s="79">
-        <v>75</v>
-      </c>
-      <c r="G102" s="79">
+      <c r="F102" s="76">
+        <v>75</v>
+      </c>
+      <c r="G102" s="76">
         <v>88</v>
       </c>
-      <c r="H102" s="80">
+      <c r="H102" s="77">
         <v>89</v>
       </c>
       <c r="I102" s="58"/>
@@ -18722,22 +18726,22 @@
       <c r="B103" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="C103" s="81" t="s">
+      <c r="C103" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="D103" s="79">
-        <v>70</v>
-      </c>
-      <c r="E103" s="79">
+      <c r="D103" s="76">
+        <v>70</v>
+      </c>
+      <c r="E103" s="76">
         <v>89</v>
       </c>
-      <c r="F103" s="79">
-        <v>75</v>
-      </c>
-      <c r="G103" s="79">
+      <c r="F103" s="76">
+        <v>75</v>
+      </c>
+      <c r="G103" s="76">
         <v>90</v>
       </c>
-      <c r="H103" s="80">
+      <c r="H103" s="77">
         <v>85</v>
       </c>
       <c r="I103" s="58"/>
@@ -18749,22 +18753,22 @@
       <c r="B104" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="C104" s="81" t="s">
+      <c r="C104" s="78" t="s">
         <v>115</v>
       </c>
-      <c r="D104" s="79">
-        <v>70</v>
-      </c>
-      <c r="E104" s="79">
+      <c r="D104" s="76">
+        <v>70</v>
+      </c>
+      <c r="E104" s="76">
         <v>88</v>
       </c>
-      <c r="F104" s="79">
+      <c r="F104" s="76">
         <v>80</v>
       </c>
-      <c r="G104" s="79">
+      <c r="G104" s="76">
         <v>88</v>
       </c>
-      <c r="H104" s="80">
+      <c r="H104" s="77">
         <v>83</v>
       </c>
       <c r="I104" s="58"/>
@@ -18773,25 +18777,25 @@
       <c r="A105" s="22">
         <v>103</v>
       </c>
-      <c r="B105" s="82" t="s">
+      <c r="B105" s="79" t="s">
         <v>279</v>
       </c>
-      <c r="C105" s="81" t="s">
+      <c r="C105" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="D105" s="79">
+      <c r="D105" s="76">
         <v>65</v>
       </c>
-      <c r="E105" s="79">
+      <c r="E105" s="76">
         <v>88</v>
       </c>
-      <c r="F105" s="79">
+      <c r="F105" s="76">
         <v>65</v>
       </c>
-      <c r="G105" s="79">
+      <c r="G105" s="76">
         <v>90</v>
       </c>
-      <c r="H105" s="80">
+      <c r="H105" s="77">
         <v>85</v>
       </c>
       <c r="I105" s="58"/>
@@ -18803,22 +18807,22 @@
       <c r="B106" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C106" s="81" t="s">
+      <c r="C106" s="78" t="s">
         <v>118</v>
       </c>
-      <c r="D106" s="79">
-        <v>75</v>
-      </c>
-      <c r="E106" s="79">
+      <c r="D106" s="76">
+        <v>75</v>
+      </c>
+      <c r="E106" s="76">
         <v>88</v>
       </c>
-      <c r="F106" s="79">
+      <c r="F106" s="76">
         <v>85</v>
       </c>
-      <c r="G106" s="79">
+      <c r="G106" s="76">
         <v>88</v>
       </c>
-      <c r="H106" s="80">
+      <c r="H106" s="77">
         <v>83</v>
       </c>
       <c r="I106" s="58"/>
@@ -18830,22 +18834,22 @@
       <c r="B107" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C107" s="81" t="s">
+      <c r="C107" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="D107" s="79">
-        <v>75</v>
-      </c>
-      <c r="E107" s="79">
+      <c r="D107" s="76">
+        <v>75</v>
+      </c>
+      <c r="E107" s="76">
         <v>83</v>
       </c>
-      <c r="F107" s="79">
-        <v>75</v>
-      </c>
-      <c r="G107" s="79">
+      <c r="F107" s="76">
+        <v>75</v>
+      </c>
+      <c r="G107" s="76">
         <v>90</v>
       </c>
-      <c r="H107" s="80">
+      <c r="H107" s="77">
         <v>85</v>
       </c>
       <c r="I107" s="58"/>
@@ -18857,22 +18861,22 @@
       <c r="B108" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C108" s="81" t="s">
+      <c r="C108" s="78" t="s">
         <v>120</v>
       </c>
-      <c r="D108" s="79">
-        <v>75</v>
-      </c>
-      <c r="E108" s="79">
+      <c r="D108" s="76">
+        <v>75</v>
+      </c>
+      <c r="E108" s="76">
         <v>88</v>
       </c>
-      <c r="F108" s="79">
-        <v>70</v>
-      </c>
-      <c r="G108" s="79">
+      <c r="F108" s="76">
+        <v>70</v>
+      </c>
+      <c r="G108" s="76">
         <v>90</v>
       </c>
-      <c r="H108" s="80">
+      <c r="H108" s="77">
         <v>85</v>
       </c>
       <c r="I108" s="58"/>
@@ -18884,22 +18888,22 @@
       <c r="B109" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="C109" s="81" t="s">
+      <c r="C109" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="D109" s="79">
-        <v>75</v>
-      </c>
-      <c r="E109" s="79">
+      <c r="D109" s="76">
+        <v>75</v>
+      </c>
+      <c r="E109" s="76">
         <v>83</v>
       </c>
-      <c r="F109" s="79">
-        <v>70</v>
-      </c>
-      <c r="G109" s="79">
+      <c r="F109" s="76">
+        <v>70</v>
+      </c>
+      <c r="G109" s="76">
         <v>90</v>
       </c>
-      <c r="H109" s="80">
+      <c r="H109" s="77">
         <v>85</v>
       </c>
       <c r="I109" s="58"/>
@@ -18911,22 +18915,22 @@
       <c r="B110" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="C110" s="81" t="s">
+      <c r="C110" s="78" t="s">
         <v>123</v>
       </c>
-      <c r="D110" s="79">
-        <v>75</v>
-      </c>
-      <c r="E110" s="79">
+      <c r="D110" s="76">
+        <v>75</v>
+      </c>
+      <c r="E110" s="76">
         <v>90</v>
       </c>
-      <c r="F110" s="79">
+      <c r="F110" s="76">
         <v>80</v>
       </c>
-      <c r="G110" s="79">
+      <c r="G110" s="76">
         <v>90</v>
       </c>
-      <c r="H110" s="80">
+      <c r="H110" s="77">
         <v>85</v>
       </c>
       <c r="I110" s="58"/>
@@ -18938,22 +18942,22 @@
       <c r="B111" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C111" s="81" t="s">
+      <c r="C111" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="D111" s="79">
-        <v>75</v>
-      </c>
-      <c r="E111" s="79">
+      <c r="D111" s="76">
+        <v>75</v>
+      </c>
+      <c r="E111" s="76">
         <v>87</v>
       </c>
-      <c r="F111" s="79">
-        <v>75</v>
-      </c>
-      <c r="G111" s="79">
+      <c r="F111" s="76">
+        <v>75</v>
+      </c>
+      <c r="G111" s="76">
         <v>84</v>
       </c>
-      <c r="H111" s="80">
+      <c r="H111" s="77">
         <v>70</v>
       </c>
       <c r="I111" s="58"/>
@@ -18965,22 +18969,22 @@
       <c r="B112" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="C112" s="81" t="s">
+      <c r="C112" s="78" t="s">
         <v>125</v>
       </c>
-      <c r="D112" s="79">
-        <v>75</v>
-      </c>
-      <c r="E112" s="79">
+      <c r="D112" s="76">
+        <v>75</v>
+      </c>
+      <c r="E112" s="76">
         <v>89</v>
       </c>
-      <c r="F112" s="79">
-        <v>70</v>
-      </c>
-      <c r="G112" s="79">
+      <c r="F112" s="76">
+        <v>70</v>
+      </c>
+      <c r="G112" s="76">
         <v>90</v>
       </c>
-      <c r="H112" s="80">
+      <c r="H112" s="77">
         <v>85</v>
       </c>
       <c r="I112" s="58"/>
@@ -18992,22 +18996,22 @@
       <c r="B113" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="C113" s="81" t="s">
+      <c r="C113" s="78" t="s">
         <v>127</v>
       </c>
-      <c r="D113" s="79">
+      <c r="D113" s="76">
         <v>85</v>
       </c>
-      <c r="E113" s="79">
+      <c r="E113" s="76">
         <v>91</v>
       </c>
-      <c r="F113" s="79">
+      <c r="F113" s="76">
         <v>65</v>
       </c>
-      <c r="G113" s="79">
+      <c r="G113" s="76">
         <v>83</v>
       </c>
-      <c r="H113" s="80">
+      <c r="H113" s="77">
         <v>82</v>
       </c>
       <c r="I113" s="58"/>
@@ -19019,22 +19023,22 @@
       <c r="B114" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C114" s="81" t="s">
+      <c r="C114" s="78" t="s">
         <v>128</v>
       </c>
-      <c r="D114" s="79">
+      <c r="D114" s="76">
         <v>85</v>
       </c>
-      <c r="E114" s="79">
+      <c r="E114" s="76">
         <v>91</v>
       </c>
-      <c r="F114" s="79">
+      <c r="F114" s="76">
         <v>65</v>
       </c>
-      <c r="G114" s="79">
+      <c r="G114" s="76">
         <v>91</v>
       </c>
-      <c r="H114" s="80">
+      <c r="H114" s="77">
         <v>88</v>
       </c>
       <c r="I114" s="58"/>
@@ -19046,22 +19050,22 @@
       <c r="B115" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="C115" s="81" t="s">
+      <c r="C115" s="78" t="s">
         <v>129</v>
       </c>
-      <c r="D115" s="79">
+      <c r="D115" s="76">
         <v>85</v>
       </c>
-      <c r="E115" s="79">
+      <c r="E115" s="76">
         <v>90</v>
       </c>
-      <c r="F115" s="79">
+      <c r="F115" s="76">
         <v>65</v>
       </c>
-      <c r="G115" s="79">
+      <c r="G115" s="76">
         <v>88</v>
       </c>
-      <c r="H115" s="80">
+      <c r="H115" s="77">
         <v>83</v>
       </c>
       <c r="I115" s="58"/>
@@ -19073,22 +19077,22 @@
       <c r="B116" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="C116" s="81" t="s">
+      <c r="C116" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="D116" s="79">
-        <v>70</v>
-      </c>
-      <c r="E116" s="79">
+      <c r="D116" s="76">
+        <v>70</v>
+      </c>
+      <c r="E116" s="76">
         <v>90</v>
       </c>
-      <c r="F116" s="79">
+      <c r="F116" s="76">
         <v>80</v>
       </c>
-      <c r="G116" s="79">
+      <c r="G116" s="76">
         <v>88</v>
       </c>
-      <c r="H116" s="80">
+      <c r="H116" s="77">
         <v>83</v>
       </c>
       <c r="I116" s="58"/>
@@ -19100,22 +19104,22 @@
       <c r="B117" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="C117" s="81" t="s">
+      <c r="C117" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="D117" s="79">
-        <v>75</v>
-      </c>
-      <c r="E117" s="79">
+      <c r="D117" s="76">
+        <v>75</v>
+      </c>
+      <c r="E117" s="76">
         <v>91</v>
       </c>
-      <c r="F117" s="79">
-        <v>75</v>
-      </c>
-      <c r="G117" s="79">
+      <c r="F117" s="76">
+        <v>75</v>
+      </c>
+      <c r="G117" s="76">
         <v>84</v>
       </c>
-      <c r="H117" s="79">
+      <c r="H117" s="76">
         <v>70</v>
       </c>
       <c r="I117" s="58"/>
@@ -19127,22 +19131,22 @@
       <c r="B118" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C118" s="81" t="s">
+      <c r="C118" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D118" s="79">
+      <c r="D118" s="76">
         <v>85</v>
       </c>
-      <c r="E118" s="79">
+      <c r="E118" s="76">
         <v>90</v>
       </c>
-      <c r="F118" s="79">
+      <c r="F118" s="76">
         <v>65</v>
       </c>
-      <c r="G118" s="79">
+      <c r="G118" s="76">
         <v>88</v>
       </c>
-      <c r="H118" s="79">
+      <c r="H118" s="76">
         <v>89</v>
       </c>
       <c r="I118" s="58"/>
@@ -19154,22 +19158,22 @@
       <c r="B119" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="C119" s="81" t="s">
+      <c r="C119" s="78" t="s">
         <v>134</v>
       </c>
-      <c r="D119" s="79">
-        <v>75</v>
-      </c>
-      <c r="E119" s="79">
+      <c r="D119" s="76">
+        <v>75</v>
+      </c>
+      <c r="E119" s="76">
         <v>90</v>
       </c>
-      <c r="F119" s="79">
-        <v>75</v>
-      </c>
-      <c r="G119" s="79">
+      <c r="F119" s="76">
+        <v>75</v>
+      </c>
+      <c r="G119" s="76">
         <v>84</v>
       </c>
-      <c r="H119" s="79">
+      <c r="H119" s="76">
         <v>70</v>
       </c>
       <c r="I119" s="58"/>
@@ -19181,22 +19185,22 @@
       <c r="B120" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="C120" s="81" t="s">
+      <c r="C120" s="78" t="s">
         <v>135</v>
       </c>
-      <c r="D120" s="79">
-        <v>70</v>
-      </c>
-      <c r="E120" s="79">
+      <c r="D120" s="76">
+        <v>70</v>
+      </c>
+      <c r="E120" s="76">
         <v>91</v>
       </c>
-      <c r="F120" s="79">
-        <v>75</v>
-      </c>
-      <c r="G120" s="79">
+      <c r="F120" s="76">
+        <v>75</v>
+      </c>
+      <c r="G120" s="76">
         <v>86</v>
       </c>
-      <c r="H120" s="80">
+      <c r="H120" s="77">
         <v>81</v>
       </c>
       <c r="I120" s="58"/>
@@ -19208,22 +19212,22 @@
       <c r="B121" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="C121" s="81" t="s">
+      <c r="C121" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="D121" s="79">
-        <v>70</v>
-      </c>
-      <c r="E121" s="79">
+      <c r="D121" s="76">
+        <v>70</v>
+      </c>
+      <c r="E121" s="76">
         <v>91</v>
       </c>
-      <c r="F121" s="79">
+      <c r="F121" s="76">
         <v>80</v>
       </c>
-      <c r="G121" s="79">
+      <c r="G121" s="76">
         <v>86</v>
       </c>
-      <c r="H121" s="80">
+      <c r="H121" s="77">
         <v>81</v>
       </c>
       <c r="I121" s="58"/>
@@ -19235,22 +19239,22 @@
       <c r="B122" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="C122" s="81" t="s">
+      <c r="C122" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="D122" s="79">
-        <v>70</v>
-      </c>
-      <c r="E122" s="79">
+      <c r="D122" s="76">
+        <v>70</v>
+      </c>
+      <c r="E122" s="76">
         <v>89</v>
       </c>
-      <c r="F122" s="79">
+      <c r="F122" s="76">
         <v>80</v>
       </c>
-      <c r="G122" s="79">
+      <c r="G122" s="76">
         <v>86</v>
       </c>
-      <c r="H122" s="80">
+      <c r="H122" s="77">
         <v>84</v>
       </c>
       <c r="I122" s="58"/>
@@ -19262,22 +19266,22 @@
       <c r="B123" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="C123" s="81" t="s">
+      <c r="C123" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="D123" s="79">
+      <c r="D123" s="76">
         <v>85</v>
       </c>
-      <c r="E123" s="79">
+      <c r="E123" s="76">
         <v>90</v>
       </c>
-      <c r="F123" s="79">
+      <c r="F123" s="76">
         <v>65</v>
       </c>
-      <c r="G123" s="79">
+      <c r="G123" s="76">
         <v>84</v>
       </c>
-      <c r="H123" s="80">
+      <c r="H123" s="77">
         <v>70</v>
       </c>
       <c r="I123" s="58"/>
@@ -19289,22 +19293,22 @@
       <c r="B124" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="C124" s="81" t="s">
+      <c r="C124" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="D124" s="79">
-        <v>70</v>
-      </c>
-      <c r="E124" s="79">
+      <c r="D124" s="76">
+        <v>70</v>
+      </c>
+      <c r="E124" s="76">
         <v>90</v>
       </c>
-      <c r="F124" s="79">
+      <c r="F124" s="76">
         <v>80</v>
       </c>
-      <c r="G124" s="79">
+      <c r="G124" s="76">
         <v>88</v>
       </c>
-      <c r="H124" s="80">
+      <c r="H124" s="77">
         <v>89</v>
       </c>
       <c r="I124" s="58"/>
@@ -19316,22 +19320,22 @@
       <c r="B125" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="C125" s="81" t="s">
+      <c r="C125" s="78" t="s">
         <v>140</v>
       </c>
-      <c r="D125" s="79">
-        <v>70</v>
-      </c>
-      <c r="E125" s="79">
+      <c r="D125" s="76">
+        <v>70</v>
+      </c>
+      <c r="E125" s="76">
         <v>92</v>
       </c>
-      <c r="F125" s="79">
+      <c r="F125" s="76">
         <v>80</v>
       </c>
-      <c r="G125" s="79">
+      <c r="G125" s="76">
         <v>91</v>
       </c>
-      <c r="H125" s="80">
+      <c r="H125" s="77">
         <v>88</v>
       </c>
       <c r="I125" s="58"/>
@@ -19343,22 +19347,22 @@
       <c r="B126" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="C126" s="81" t="s">
+      <c r="C126" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="D126" s="79">
-        <v>70</v>
-      </c>
-      <c r="E126" s="79">
+      <c r="D126" s="76">
+        <v>70</v>
+      </c>
+      <c r="E126" s="76">
         <v>88</v>
       </c>
-      <c r="F126" s="79">
+      <c r="F126" s="76">
         <v>80</v>
       </c>
-      <c r="G126" s="79">
+      <c r="G126" s="76">
         <v>86</v>
       </c>
-      <c r="H126" s="80">
+      <c r="H126" s="77">
         <v>84</v>
       </c>
       <c r="I126" s="58"/>
@@ -19370,22 +19374,22 @@
       <c r="B127" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="C127" s="81" t="s">
+      <c r="C127" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="D127" s="79">
-        <v>75</v>
-      </c>
-      <c r="E127" s="79">
+      <c r="D127" s="76">
+        <v>75</v>
+      </c>
+      <c r="E127" s="76">
         <v>89</v>
       </c>
-      <c r="F127" s="79">
-        <v>75</v>
-      </c>
-      <c r="G127" s="79">
+      <c r="F127" s="76">
+        <v>75</v>
+      </c>
+      <c r="G127" s="76">
         <v>86</v>
       </c>
-      <c r="H127" s="80">
+      <c r="H127" s="77">
         <v>84</v>
       </c>
       <c r="I127" s="58"/>
@@ -19397,22 +19401,22 @@
       <c r="B128" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="C128" s="81" t="s">
+      <c r="C128" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="D128" s="79">
-        <v>75</v>
-      </c>
-      <c r="E128" s="79">
+      <c r="D128" s="76">
+        <v>75</v>
+      </c>
+      <c r="E128" s="76">
         <v>89</v>
       </c>
-      <c r="F128" s="79">
+      <c r="F128" s="76">
         <v>85</v>
       </c>
-      <c r="G128" s="79">
+      <c r="G128" s="76">
         <v>86</v>
       </c>
-      <c r="H128" s="80">
+      <c r="H128" s="77">
         <v>84</v>
       </c>
       <c r="I128" s="58"/>
@@ -19424,22 +19428,22 @@
       <c r="B129" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="C129" s="81" t="s">
+      <c r="C129" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="D129" s="79">
-        <v>75</v>
-      </c>
-      <c r="E129" s="79">
+      <c r="D129" s="76">
+        <v>75</v>
+      </c>
+      <c r="E129" s="76">
         <v>90</v>
       </c>
-      <c r="F129" s="79">
+      <c r="F129" s="76">
         <v>80</v>
       </c>
-      <c r="G129" s="79">
+      <c r="G129" s="76">
         <v>91</v>
       </c>
-      <c r="H129" s="80">
+      <c r="H129" s="77">
         <v>88</v>
       </c>
       <c r="I129" s="58"/>
@@ -19451,22 +19455,22 @@
       <c r="B130" s="13" t="s">
         <v>304</v>
       </c>
-      <c r="C130" s="81" t="s">
+      <c r="C130" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="D130" s="79">
+      <c r="D130" s="76">
         <v>80</v>
       </c>
-      <c r="E130" s="79">
+      <c r="E130" s="76">
         <v>92</v>
       </c>
-      <c r="F130" s="79">
-        <v>70</v>
-      </c>
-      <c r="G130" s="79">
+      <c r="F130" s="76">
+        <v>70</v>
+      </c>
+      <c r="G130" s="76">
         <v>86</v>
       </c>
-      <c r="H130" s="80">
+      <c r="H130" s="77">
         <v>81</v>
       </c>
       <c r="I130" s="58"/>
@@ -19481,19 +19485,19 @@
       <c r="C131" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D131" s="79">
-        <v>75</v>
-      </c>
-      <c r="E131" s="79">
+      <c r="D131" s="76">
+        <v>75</v>
+      </c>
+      <c r="E131" s="76">
         <v>90</v>
       </c>
-      <c r="F131" s="79">
-        <v>75</v>
-      </c>
-      <c r="G131" s="79">
+      <c r="F131" s="76">
+        <v>75</v>
+      </c>
+      <c r="G131" s="76">
         <v>86</v>
       </c>
-      <c r="H131" s="80">
+      <c r="H131" s="77">
         <v>70</v>
       </c>
       <c r="I131" s="58"/>
@@ -19508,19 +19512,19 @@
       <c r="C132" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D132" s="79">
-        <v>75</v>
-      </c>
-      <c r="E132" s="79">
+      <c r="D132" s="76">
+        <v>75</v>
+      </c>
+      <c r="E132" s="76">
         <v>88</v>
       </c>
-      <c r="F132" s="79">
+      <c r="F132" s="76">
         <v>80</v>
       </c>
-      <c r="G132" s="79">
+      <c r="G132" s="76">
         <v>91</v>
       </c>
-      <c r="H132" s="80">
+      <c r="H132" s="77">
         <v>88</v>
       </c>
       <c r="I132" s="58"/>
@@ -19535,19 +19539,19 @@
       <c r="C133" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D133" s="79">
+      <c r="D133" s="76">
         <v>80</v>
       </c>
-      <c r="E133" s="79">
+      <c r="E133" s="76">
         <v>92</v>
       </c>
-      <c r="F133" s="79">
-        <v>70</v>
-      </c>
-      <c r="G133" s="79">
+      <c r="F133" s="76">
+        <v>70</v>
+      </c>
+      <c r="G133" s="76">
         <v>89</v>
       </c>
-      <c r="H133" s="80">
+      <c r="H133" s="77">
         <v>71</v>
       </c>
       <c r="I133" s="58"/>
@@ -19562,19 +19566,19 @@
       <c r="C134" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D134" s="79">
-        <v>70</v>
-      </c>
-      <c r="E134" s="79">
+      <c r="D134" s="76">
+        <v>70</v>
+      </c>
+      <c r="E134" s="76">
         <v>83</v>
       </c>
-      <c r="F134" s="79">
+      <c r="F134" s="76">
         <v>80</v>
       </c>
-      <c r="G134" s="79">
+      <c r="G134" s="76">
         <v>84</v>
       </c>
-      <c r="H134" s="80">
+      <c r="H134" s="77">
         <v>70</v>
       </c>
       <c r="I134" s="58"/>
@@ -19589,19 +19593,19 @@
       <c r="C135" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="D135" s="79">
+      <c r="D135" s="76">
         <v>80</v>
       </c>
-      <c r="E135" s="79">
+      <c r="E135" s="76">
         <v>87</v>
       </c>
-      <c r="F135" s="79">
-        <v>70</v>
-      </c>
-      <c r="G135" s="79">
+      <c r="F135" s="76">
+        <v>70</v>
+      </c>
+      <c r="G135" s="76">
         <v>84</v>
       </c>
-      <c r="H135" s="80">
+      <c r="H135" s="77">
         <v>70</v>
       </c>
       <c r="I135" s="58"/>
@@ -19616,19 +19620,19 @@
       <c r="C136" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D136" s="79">
-        <v>70</v>
-      </c>
-      <c r="E136" s="79">
+      <c r="D136" s="76">
+        <v>70</v>
+      </c>
+      <c r="E136" s="76">
         <v>88</v>
       </c>
-      <c r="F136" s="79">
+      <c r="F136" s="76">
         <v>80</v>
       </c>
-      <c r="G136" s="79">
+      <c r="G136" s="76">
         <v>89</v>
       </c>
-      <c r="H136" s="80">
+      <c r="H136" s="77">
         <v>71</v>
       </c>
       <c r="I136" s="58"/>
@@ -19643,19 +19647,19 @@
       <c r="C137" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D137" s="79">
-        <v>75</v>
-      </c>
-      <c r="E137" s="79">
+      <c r="D137" s="76">
+        <v>75</v>
+      </c>
+      <c r="E137" s="76">
         <v>91</v>
       </c>
-      <c r="F137" s="79">
-        <v>75</v>
-      </c>
-      <c r="G137" s="79">
+      <c r="F137" s="76">
+        <v>75</v>
+      </c>
+      <c r="G137" s="76">
         <v>84</v>
       </c>
-      <c r="H137" s="80">
+      <c r="H137" s="77">
         <v>70</v>
       </c>
       <c r="I137" s="58"/>
@@ -19670,19 +19674,19 @@
       <c r="C138" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="D138" s="79">
+      <c r="D138" s="76">
         <v>78</v>
       </c>
-      <c r="E138" s="79">
+      <c r="E138" s="76">
         <v>83</v>
       </c>
-      <c r="F138" s="79">
+      <c r="F138" s="76">
         <v>80</v>
       </c>
-      <c r="G138" s="79">
+      <c r="G138" s="76">
         <v>83</v>
       </c>
-      <c r="H138" s="80">
+      <c r="H138" s="77">
         <v>82</v>
       </c>
       <c r="I138" s="58"/>
@@ -19697,19 +19701,19 @@
       <c r="C139" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D139" s="79">
-        <v>75</v>
-      </c>
-      <c r="E139" s="79">
+      <c r="D139" s="76">
+        <v>75</v>
+      </c>
+      <c r="E139" s="76">
         <v>90</v>
       </c>
-      <c r="F139" s="79">
-        <v>70</v>
-      </c>
-      <c r="G139" s="79">
+      <c r="F139" s="76">
+        <v>70</v>
+      </c>
+      <c r="G139" s="76">
         <v>89</v>
       </c>
-      <c r="H139" s="80">
+      <c r="H139" s="77">
         <v>71</v>
       </c>
       <c r="I139" s="58"/>
@@ -19724,19 +19728,19 @@
       <c r="C140" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="D140" s="79">
-        <v>75</v>
-      </c>
-      <c r="E140" s="79">
+      <c r="D140" s="76">
+        <v>75</v>
+      </c>
+      <c r="E140" s="76">
         <v>91</v>
       </c>
-      <c r="F140" s="79">
+      <c r="F140" s="76">
         <v>80</v>
       </c>
-      <c r="G140" s="79">
+      <c r="G140" s="76">
         <v>84</v>
       </c>
-      <c r="H140" s="80">
+      <c r="H140" s="77">
         <v>70</v>
       </c>
       <c r="I140" s="58"/>
@@ -19751,19 +19755,19 @@
       <c r="C141" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="D141" s="79">
-        <v>75</v>
-      </c>
-      <c r="E141" s="79">
+      <c r="D141" s="76">
+        <v>75</v>
+      </c>
+      <c r="E141" s="76">
         <v>90</v>
       </c>
-      <c r="F141" s="79">
+      <c r="F141" s="76">
         <v>85</v>
       </c>
-      <c r="G141" s="79">
+      <c r="G141" s="76">
         <v>88</v>
       </c>
-      <c r="H141" s="80">
+      <c r="H141" s="77">
         <v>83</v>
       </c>
       <c r="I141" s="58"/>
@@ -19778,19 +19782,19 @@
       <c r="C142" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D142" s="79">
-        <v>70</v>
-      </c>
-      <c r="E142" s="79">
+      <c r="D142" s="76">
+        <v>70</v>
+      </c>
+      <c r="E142" s="76">
         <v>90</v>
       </c>
-      <c r="F142" s="79">
-        <v>75</v>
-      </c>
-      <c r="G142" s="79">
+      <c r="F142" s="76">
+        <v>75</v>
+      </c>
+      <c r="G142" s="76">
         <v>86</v>
       </c>
-      <c r="H142" s="80">
+      <c r="H142" s="77">
         <v>81</v>
       </c>
       <c r="I142" s="58"/>
@@ -19805,19 +19809,19 @@
       <c r="C143" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="D143" s="79">
-        <v>70</v>
-      </c>
-      <c r="E143" s="79">
+      <c r="D143" s="76">
+        <v>70</v>
+      </c>
+      <c r="E143" s="76">
         <v>90</v>
       </c>
-      <c r="F143" s="79">
-        <v>75</v>
-      </c>
-      <c r="G143" s="79">
+      <c r="F143" s="76">
+        <v>75</v>
+      </c>
+      <c r="G143" s="76">
         <v>88</v>
       </c>
-      <c r="H143" s="80">
+      <c r="H143" s="77">
         <v>83</v>
       </c>
       <c r="I143" s="58"/>
@@ -19832,19 +19836,19 @@
       <c r="C144" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D144" s="79">
+      <c r="D144" s="76">
         <v>78</v>
       </c>
-      <c r="E144" s="79">
+      <c r="E144" s="76">
         <v>90</v>
       </c>
-      <c r="F144" s="79">
+      <c r="F144" s="76">
         <v>80</v>
       </c>
-      <c r="G144" s="79">
+      <c r="G144" s="76">
         <v>86</v>
       </c>
-      <c r="H144" s="80">
+      <c r="H144" s="77">
         <v>84</v>
       </c>
       <c r="I144" s="58"/>
@@ -19859,19 +19863,19 @@
       <c r="C145" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="D145" s="79">
-        <v>70</v>
-      </c>
-      <c r="E145" s="79">
+      <c r="D145" s="76">
+        <v>70</v>
+      </c>
+      <c r="E145" s="76">
         <v>90</v>
       </c>
-      <c r="F145" s="79">
-        <v>75</v>
-      </c>
-      <c r="G145" s="79">
+      <c r="F145" s="76">
+        <v>75</v>
+      </c>
+      <c r="G145" s="76">
         <v>83</v>
       </c>
-      <c r="H145" s="80">
+      <c r="H145" s="77">
         <v>82</v>
       </c>
       <c r="I145" s="58"/>
@@ -19886,19 +19890,19 @@
       <c r="C146" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="D146" s="79">
-        <v>70</v>
-      </c>
-      <c r="E146" s="79">
+      <c r="D146" s="76">
+        <v>70</v>
+      </c>
+      <c r="E146" s="76">
         <v>88</v>
       </c>
-      <c r="F146" s="79">
-        <v>75</v>
-      </c>
-      <c r="G146" s="79">
+      <c r="F146" s="76">
+        <v>75</v>
+      </c>
+      <c r="G146" s="76">
         <v>86</v>
       </c>
-      <c r="H146" s="80">
+      <c r="H146" s="77">
         <v>70</v>
       </c>
       <c r="I146" s="58"/>
@@ -19913,19 +19917,19 @@
       <c r="C147" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="D147" s="79">
-        <v>75</v>
-      </c>
-      <c r="E147" s="79">
+      <c r="D147" s="76">
+        <v>75</v>
+      </c>
+      <c r="E147" s="76">
         <v>83</v>
       </c>
-      <c r="F147" s="79">
+      <c r="F147" s="76">
         <v>85</v>
       </c>
-      <c r="G147" s="79">
+      <c r="G147" s="76">
         <v>88</v>
       </c>
-      <c r="H147" s="80">
+      <c r="H147" s="77">
         <v>83</v>
       </c>
       <c r="I147" s="58"/>
@@ -19934,25 +19938,25 @@
       <c r="A148" s="22">
         <v>146</v>
       </c>
-      <c r="B148" s="82" t="s">
+      <c r="B148" s="79" t="s">
         <v>322</v>
       </c>
       <c r="C148" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="D148" s="79">
+      <c r="D148" s="76">
         <v>65</v>
       </c>
-      <c r="E148" s="79">
+      <c r="E148" s="76">
         <v>89</v>
       </c>
-      <c r="F148" s="79">
+      <c r="F148" s="76">
         <v>60</v>
       </c>
-      <c r="G148" s="79">
+      <c r="G148" s="76">
         <v>86</v>
       </c>
-      <c r="H148" s="80">
+      <c r="H148" s="77">
         <v>84</v>
       </c>
       <c r="I148" s="58"/>
@@ -19967,19 +19971,19 @@
       <c r="C149" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="D149" s="79">
-        <v>75</v>
-      </c>
-      <c r="E149" s="79">
+      <c r="D149" s="76">
+        <v>75</v>
+      </c>
+      <c r="E149" s="76">
         <v>88</v>
       </c>
-      <c r="F149" s="79">
+      <c r="F149" s="76">
         <v>85</v>
       </c>
-      <c r="G149" s="79">
+      <c r="G149" s="76">
         <v>84</v>
       </c>
-      <c r="H149" s="79">
+      <c r="H149" s="76">
         <v>70</v>
       </c>
       <c r="I149" s="58"/>
@@ -19994,19 +19998,19 @@
       <c r="C150" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D150" s="79">
-        <v>75</v>
-      </c>
-      <c r="E150" s="79">
+      <c r="D150" s="76">
+        <v>75</v>
+      </c>
+      <c r="E150" s="76">
         <v>90</v>
       </c>
-      <c r="F150" s="79">
-        <v>70</v>
-      </c>
-      <c r="G150" s="79">
+      <c r="F150" s="76">
+        <v>70</v>
+      </c>
+      <c r="G150" s="76">
         <v>91</v>
       </c>
-      <c r="H150" s="80">
+      <c r="H150" s="77">
         <v>88</v>
       </c>
       <c r="I150" s="58"/>
@@ -20021,19 +20025,19 @@
       <c r="C151" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D151" s="79">
-        <v>70</v>
-      </c>
-      <c r="E151" s="79">
+      <c r="D151" s="76">
+        <v>70</v>
+      </c>
+      <c r="E151" s="76">
         <v>89</v>
       </c>
-      <c r="F151" s="79">
-        <v>75</v>
-      </c>
-      <c r="G151" s="79">
+      <c r="F151" s="76">
+        <v>75</v>
+      </c>
+      <c r="G151" s="76">
         <v>88</v>
       </c>
-      <c r="H151" s="80">
+      <c r="H151" s="77">
         <v>83</v>
       </c>
       <c r="I151" s="58"/>
@@ -20048,19 +20052,19 @@
       <c r="C152" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="D152" s="79">
-        <v>75</v>
-      </c>
-      <c r="E152" s="79">
+      <c r="D152" s="76">
+        <v>75</v>
+      </c>
+      <c r="E152" s="76">
         <v>88</v>
       </c>
-      <c r="F152" s="79">
+      <c r="F152" s="76">
         <v>85</v>
       </c>
-      <c r="G152" s="79">
+      <c r="G152" s="76">
         <v>91</v>
       </c>
-      <c r="H152" s="80">
+      <c r="H152" s="77">
         <v>88</v>
       </c>
       <c r="I152" s="58"/>
@@ -20075,19 +20079,19 @@
       <c r="C153" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D153" s="79">
-        <v>75</v>
-      </c>
-      <c r="E153" s="79">
+      <c r="D153" s="76">
+        <v>75</v>
+      </c>
+      <c r="E153" s="76">
         <v>0</v>
       </c>
-      <c r="F153" s="79">
-        <v>75</v>
-      </c>
-      <c r="G153" s="79">
+      <c r="F153" s="76">
+        <v>75</v>
+      </c>
+      <c r="G153" s="76">
         <v>84</v>
       </c>
-      <c r="H153" s="80">
+      <c r="H153" s="77">
         <v>70</v>
       </c>
       <c r="I153" s="58"/>
@@ -20102,19 +20106,19 @@
       <c r="C154" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D154" s="79">
-        <v>70</v>
-      </c>
-      <c r="E154" s="79">
+      <c r="D154" s="76">
+        <v>70</v>
+      </c>
+      <c r="E154" s="76">
         <v>90</v>
       </c>
-      <c r="F154" s="79">
-        <v>75</v>
-      </c>
-      <c r="G154" s="79">
+      <c r="F154" s="76">
+        <v>75</v>
+      </c>
+      <c r="G154" s="76">
         <v>90</v>
       </c>
-      <c r="H154" s="80">
+      <c r="H154" s="77">
         <v>85</v>
       </c>
       <c r="I154" s="58"/>
@@ -20129,19 +20133,19 @@
       <c r="C155" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="D155" s="79">
-        <v>75</v>
-      </c>
-      <c r="E155" s="79">
+      <c r="D155" s="76">
+        <v>75</v>
+      </c>
+      <c r="E155" s="76">
         <v>90</v>
       </c>
-      <c r="F155" s="79">
+      <c r="F155" s="76">
         <v>65</v>
       </c>
-      <c r="G155" s="79">
+      <c r="G155" s="76">
         <v>84</v>
       </c>
-      <c r="H155" s="80">
+      <c r="H155" s="77">
         <v>70</v>
       </c>
       <c r="I155" s="58"/>
@@ -20156,19 +20160,19 @@
       <c r="C156" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="D156" s="79">
+      <c r="D156" s="76">
         <v>85</v>
       </c>
-      <c r="E156" s="79">
+      <c r="E156" s="76">
         <v>87</v>
       </c>
-      <c r="F156" s="79">
+      <c r="F156" s="76">
         <v>65</v>
       </c>
-      <c r="G156" s="79">
+      <c r="G156" s="76">
         <v>86</v>
       </c>
-      <c r="H156" s="80">
+      <c r="H156" s="77">
         <v>81</v>
       </c>
       <c r="I156" s="58"/>
@@ -20183,19 +20187,19 @@
       <c r="C157" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="D157" s="79">
+      <c r="D157" s="76">
         <v>0</v>
       </c>
-      <c r="E157" s="79">
+      <c r="E157" s="76">
         <v>0</v>
       </c>
-      <c r="F157" s="79">
+      <c r="F157" s="76">
         <v>0</v>
       </c>
-      <c r="G157" s="79">
+      <c r="G157" s="76">
         <v>0</v>
       </c>
-      <c r="H157" s="80">
+      <c r="H157" s="77">
         <v>0</v>
       </c>
       <c r="I157" s="58"/>
@@ -20210,19 +20214,19 @@
       <c r="C158" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="D158" s="79">
-        <v>75</v>
-      </c>
-      <c r="E158" s="79">
+      <c r="D158" s="76">
+        <v>75</v>
+      </c>
+      <c r="E158" s="76">
         <v>87</v>
       </c>
-      <c r="F158" s="79">
-        <v>70</v>
-      </c>
-      <c r="G158" s="79">
+      <c r="F158" s="76">
+        <v>70</v>
+      </c>
+      <c r="G158" s="76">
         <v>86</v>
       </c>
-      <c r="H158" s="80">
+      <c r="H158" s="77">
         <v>81</v>
       </c>
       <c r="I158" s="58"/>
@@ -20237,19 +20241,19 @@
       <c r="C159" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="D159" s="79">
-        <v>75</v>
-      </c>
-      <c r="E159" s="79">
+      <c r="D159" s="76">
+        <v>75</v>
+      </c>
+      <c r="E159" s="76">
         <v>87</v>
       </c>
-      <c r="F159" s="79">
-        <v>70</v>
-      </c>
-      <c r="G159" s="79">
+      <c r="F159" s="76">
+        <v>70</v>
+      </c>
+      <c r="G159" s="76">
         <v>86</v>
       </c>
-      <c r="H159" s="80">
+      <c r="H159" s="77">
         <v>81</v>
       </c>
       <c r="I159" s="58"/>
@@ -20264,19 +20268,19 @@
       <c r="C160" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="D160" s="79">
+      <c r="D160" s="76">
         <v>0</v>
       </c>
-      <c r="E160" s="79">
+      <c r="E160" s="76">
         <v>0</v>
       </c>
-      <c r="F160" s="79">
+      <c r="F160" s="76">
         <v>0</v>
       </c>
-      <c r="G160" s="79">
+      <c r="G160" s="76">
         <v>0</v>
       </c>
-      <c r="H160" s="80">
+      <c r="H160" s="77">
         <v>0</v>
       </c>
       <c r="I160" s="58"/>
@@ -20291,19 +20295,19 @@
       <c r="C161" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="D161" s="79">
-        <v>70</v>
-      </c>
-      <c r="E161" s="79">
+      <c r="D161" s="76">
+        <v>70</v>
+      </c>
+      <c r="E161" s="76">
         <v>87</v>
       </c>
-      <c r="F161" s="79">
-        <v>75</v>
-      </c>
-      <c r="G161" s="79">
+      <c r="F161" s="76">
+        <v>75</v>
+      </c>
+      <c r="G161" s="76">
         <v>83</v>
       </c>
-      <c r="H161" s="80">
+      <c r="H161" s="77">
         <v>82</v>
       </c>
       <c r="I161" s="58"/>
@@ -20318,19 +20322,19 @@
       <c r="C162" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="D162" s="79">
-        <v>75</v>
-      </c>
-      <c r="E162" s="79">
+      <c r="D162" s="76">
+        <v>75</v>
+      </c>
+      <c r="E162" s="76">
         <v>87</v>
       </c>
-      <c r="F162" s="79">
-        <v>70</v>
-      </c>
-      <c r="G162" s="79">
+      <c r="F162" s="76">
+        <v>70</v>
+      </c>
+      <c r="G162" s="76">
         <v>83</v>
       </c>
-      <c r="H162" s="80">
+      <c r="H162" s="77">
         <v>82</v>
       </c>
       <c r="I162" s="58"/>
@@ -20345,19 +20349,19 @@
       <c r="C163" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="D163" s="79">
-        <v>75</v>
-      </c>
-      <c r="E163" s="79">
+      <c r="D163" s="76">
+        <v>75</v>
+      </c>
+      <c r="E163" s="76">
         <v>88</v>
       </c>
-      <c r="F163" s="79">
+      <c r="F163" s="76">
         <v>80</v>
       </c>
-      <c r="G163" s="79">
+      <c r="G163" s="76">
         <v>86</v>
       </c>
-      <c r="H163" s="80">
+      <c r="H163" s="77">
         <v>70</v>
       </c>
       <c r="I163" s="58"/>
@@ -20372,19 +20376,19 @@
       <c r="C164" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="D164" s="79">
-        <v>75</v>
-      </c>
-      <c r="E164" s="79">
+      <c r="D164" s="76">
+        <v>75</v>
+      </c>
+      <c r="E164" s="76">
         <v>88</v>
       </c>
-      <c r="F164" s="79">
+      <c r="F164" s="76">
         <v>85</v>
       </c>
-      <c r="G164" s="79">
+      <c r="G164" s="76">
         <v>86</v>
       </c>
-      <c r="H164" s="80">
+      <c r="H164" s="77">
         <v>70</v>
       </c>
       <c r="I164" s="58"/>
@@ -20399,19 +20403,19 @@
       <c r="C165" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="D165" s="79">
-        <v>70</v>
-      </c>
-      <c r="E165" s="79">
+      <c r="D165" s="76">
+        <v>70</v>
+      </c>
+      <c r="E165" s="76">
         <v>87</v>
       </c>
-      <c r="F165" s="79">
-        <v>75</v>
-      </c>
-      <c r="G165" s="79">
+      <c r="F165" s="76">
+        <v>75</v>
+      </c>
+      <c r="G165" s="76">
         <v>84</v>
       </c>
-      <c r="H165" s="80">
+      <c r="H165" s="77">
         <v>70</v>
       </c>
       <c r="I165" s="58"/>
@@ -20426,19 +20430,19 @@
       <c r="C166" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="D166" s="79">
-        <v>75</v>
-      </c>
-      <c r="E166" s="79">
+      <c r="D166" s="76">
+        <v>75</v>
+      </c>
+      <c r="E166" s="76">
         <v>87</v>
       </c>
-      <c r="F166" s="79">
-        <v>75</v>
-      </c>
-      <c r="G166" s="79">
+      <c r="F166" s="76">
+        <v>75</v>
+      </c>
+      <c r="G166" s="76">
         <v>83</v>
       </c>
-      <c r="H166" s="80">
+      <c r="H166" s="77">
         <v>82</v>
       </c>
       <c r="I166" s="58"/>
@@ -20453,19 +20457,19 @@
       <c r="C167" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="D167" s="79">
-        <v>75</v>
-      </c>
-      <c r="E167" s="79">
+      <c r="D167" s="76">
+        <v>75</v>
+      </c>
+      <c r="E167" s="76">
         <v>87</v>
       </c>
-      <c r="F167" s="79">
-        <v>70</v>
-      </c>
-      <c r="G167" s="79">
+      <c r="F167" s="76">
+        <v>70</v>
+      </c>
+      <c r="G167" s="76">
         <v>84</v>
       </c>
-      <c r="H167" s="80">
+      <c r="H167" s="77">
         <v>70</v>
       </c>
       <c r="I167" s="58"/>
@@ -20480,19 +20484,19 @@
       <c r="C168" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="D168" s="79">
-        <v>75</v>
-      </c>
-      <c r="E168" s="79">
+      <c r="D168" s="76">
+        <v>75</v>
+      </c>
+      <c r="E168" s="76">
         <v>87</v>
       </c>
-      <c r="F168" s="79">
-        <v>75</v>
-      </c>
-      <c r="G168" s="79">
+      <c r="F168" s="76">
+        <v>75</v>
+      </c>
+      <c r="G168" s="76">
         <v>84</v>
       </c>
-      <c r="H168" s="80">
+      <c r="H168" s="77">
         <v>70</v>
       </c>
       <c r="I168" s="58"/>
@@ -20507,19 +20511,19 @@
       <c r="C169" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="D169" s="79">
-        <v>75</v>
-      </c>
-      <c r="E169" s="79">
+      <c r="D169" s="76">
+        <v>75</v>
+      </c>
+      <c r="E169" s="76">
         <v>87</v>
       </c>
-      <c r="F169" s="79">
-        <v>70</v>
-      </c>
-      <c r="G169" s="79">
+      <c r="F169" s="76">
+        <v>70</v>
+      </c>
+      <c r="G169" s="76">
         <v>83</v>
       </c>
-      <c r="H169" s="80">
+      <c r="H169" s="77">
         <v>82</v>
       </c>
       <c r="I169" s="58"/>
@@ -20535,6 +20539,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20789,27 +20813,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20826,29 +20855,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="109_{9869BDC9-6CBB-4843-A2C0-112C7B74AE79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B70356AD-B789-4170-8B62-F565B9C3199C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1271330B-46C0-46A4-ACC4-A2400220E94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC9010" sheetId="2" r:id="rId1"/>
@@ -2236,7 +2236,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2488,6 +2488,9 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2507,10 +2510,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15349,8 +15348,8 @@
       <c r="D164" s="18">
         <v>88</v>
       </c>
-      <c r="E164" s="18">
-        <v>0</v>
+      <c r="E164" s="91">
+        <v>77</v>
       </c>
       <c r="F164" s="18">
         <v>68</v>
@@ -20539,26 +20538,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20813,32 +20792,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="03c84e3c-1549-479a-8619-e0d964aa7481" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20855,4 +20829,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="03c84e3c-1549-479a-8619-e0d964aa7481"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoj-my.sharepoint.com/personal/mayooran_eng_jfn_ac_lk/Documents/Short_Semesters/app/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{1271330B-46C0-46A4-ACC4-A2400220E94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8650D420-E038-4BBB-B8AB-CED52E4C9493}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="MC9010" sheetId="2" r:id="rId1"/>
@@ -22,12 +21,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MC9010'!$A$1:$F$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MC9020'!$A$1:$F$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MC9100'!$A$1:$G$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'MC9100'!$A$1:$G$190</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MC9160'!$A$1:$H$172</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'MC9100'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MC9160'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="573">
   <si>
     <t>No.</t>
   </si>
@@ -1753,12 +1752,15 @@
   </si>
   <si>
     <t>BANDARANAYAKE K.M.R.D.</t>
+  </si>
+  <si>
+    <t>2021/E/033</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2175,7 +2177,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2424,13 +2426,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 15" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 15" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 2 2" xfId="4"/>
+    <cellStyle name="Normal_Sheet1" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2711,7 +2716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6303,7 +6308,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4A1C7F-0F69-4789-A5FA-AC8F6F6D4A56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G150"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8991,7 +8996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11345,8 +11350,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H189"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H190"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -15801,68 +15806,58 @@
       <c r="H185" s="58"/>
     </row>
     <row r="186" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="22">
-        <v>185</v>
-      </c>
-      <c r="B186" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="C186" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="D186" s="18">
-        <v>88</v>
-      </c>
+      <c r="A186" s="22"/>
+      <c r="B186" s="16"/>
+      <c r="C186" s="88" t="s">
+        <v>572</v>
+      </c>
+      <c r="D186" s="18"/>
       <c r="E186" s="18">
-        <v>67</v>
-      </c>
-      <c r="F186" s="18">
-        <v>75</v>
-      </c>
-      <c r="G186" s="53">
-        <v>62</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="F186" s="18"/>
+      <c r="G186" s="53"/>
       <c r="H186" s="58"/>
     </row>
     <row r="187" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="22">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B187" s="16" t="s">
-        <v>472</v>
+        <v>557</v>
       </c>
       <c r="C187" s="20" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D187" s="18">
         <v>88</v>
       </c>
       <c r="E187" s="18">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F187" s="18">
         <v>75</v>
       </c>
       <c r="G187" s="53">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H187" s="58"/>
     </row>
     <row r="188" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="22">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B188" s="16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C188" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188" s="18">
         <v>88</v>
       </c>
       <c r="E188" s="18">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F188" s="18">
         <v>75</v>
@@ -15872,29 +15867,53 @@
       </c>
       <c r="H188" s="58"/>
     </row>
-    <row r="189" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="23">
+    <row r="189" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="22">
+        <v>187</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="C189" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="D189" s="18">
+        <v>88</v>
+      </c>
+      <c r="E189" s="18">
+        <v>87</v>
+      </c>
+      <c r="F189" s="18">
+        <v>75</v>
+      </c>
+      <c r="G189" s="53">
+        <v>61</v>
+      </c>
+      <c r="H189" s="58"/>
+    </row>
+    <row r="190" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="23">
         <v>188</v>
       </c>
-      <c r="B189" s="24" t="s">
+      <c r="B190" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="C189" s="25" t="s">
+      <c r="C190" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="D189" s="26">
+      <c r="D190" s="26">
         <v>88</v>
       </c>
-      <c r="E189" s="26">
-        <v>70</v>
-      </c>
-      <c r="F189" s="26">
-        <v>75</v>
-      </c>
-      <c r="G189" s="54">
+      <c r="E190" s="26">
+        <v>70</v>
+      </c>
+      <c r="F190" s="26">
+        <v>75</v>
+      </c>
+      <c r="G190" s="54">
         <v>64</v>
       </c>
-      <c r="H189" s="59"/>
+      <c r="H190" s="59"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -15904,7 +15923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20459,15 +20478,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2835d969-06cc-46e6-b4cc-c525f784ce43">
@@ -20478,7 +20488,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20733,15 +20743,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -20758,7 +20769,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20775,4 +20786,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Short Semester I (E23 Batch).xlsx
+++ b/Short Semester I (E23 Batch).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="MC9010" sheetId="2" r:id="rId1"/>
@@ -3750,7 +3750,7 @@
         <v>54</v>
       </c>
       <c r="D49" s="18">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E49" s="18">
         <v>76</v>
@@ -20489,6 +20489,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100455C4072EA7E0D46870C67AD0D3E62C3" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6d62d4992a7888825600c982e6c75641">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2835d969-06cc-46e6-b4cc-c525f784ce43" xmlns:ns3="03c84e3c-1549-479a-8619-e0d964aa7481" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9015832621b6abd41b87bce5adc31c29" ns2:_="" ns3:_="">
     <xsd:import namespace="2835d969-06cc-46e6-b4cc-c525f784ce43"/>
@@ -20743,15 +20752,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8EACE5-8C5B-48FA-AFAD-2C86FB600767}">
   <ds:schemaRefs>
@@ -20770,6 +20770,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A244EB-A970-4F2B-8B12-6A24EFA3E1AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20786,12 +20794,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781D7AC4-6CC5-4242-91F0-BEE6E1ED618F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>